--- a/Results/Ammonia/ammonia acidification results.xlsx
+++ b/Results/Ammonia/ammonia acidification results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01370519145606209</v>
+        <v>0.01370519145606197</v>
       </c>
       <c r="C2" t="n">
         <v>0.01180398953512965</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0156777971986109</v>
+        <v>0.01567779719861086</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01193242419364214</v>
+        <v>0.01193242419364211</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01146739430805003</v>
+        <v>0.01146739430805001</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01454404296892954</v>
+        <v>0.0145440429689295</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01709624872921379</v>
+        <v>0.0170962487292138</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01220000579839282</v>
+        <v>0.0122000057983928</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01418480620657232</v>
+        <v>0.01418480620657234</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01389995839755249</v>
+        <v>0.0138999583975525</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02446037087927612</v>
+        <v>0.02446037087927613</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01496453947382704</v>
+        <v>0.01496453947382713</v>
       </c>
       <c r="C3" t="n">
         <v>0.01283673357618647</v>
@@ -564,28 +564,28 @@
         <v>0.01723344470180689</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01296567873896726</v>
+        <v>0.01296567873896725</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01250064885337514</v>
+        <v>0.01250064885337515</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01592939248119219</v>
+        <v>0.01592939248119217</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01886548251136299</v>
+        <v>0.018865482511363</v>
       </c>
       <c r="I3" t="n">
         <v>0.01323182468165857</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01551703866751269</v>
+        <v>0.01551703866751266</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01500264216263351</v>
+        <v>0.01500264216263344</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02733476743916071</v>
+        <v>0.02733476743916072</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01191757876940892</v>
+        <v>0.008692190420483159</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01068664994885856</v>
+        <v>0.007738244084064292</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01309020929695849</v>
+        <v>0.009864820948032772</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0107539285040861</v>
+        <v>0.007750085765902653</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0107539285040861</v>
+        <v>0.007750085765902657</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01239551223766469</v>
+        <v>0.009187203934614634</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01393293526254341</v>
+        <v>0.0107075469136177</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01088445193481476</v>
+        <v>0.00777275510957858</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01220602518006149</v>
+        <v>0.008980636831135777</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01129756660500692</v>
+        <v>0.00807217825608119</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0183091163464245</v>
+        <v>0.01508372799749877</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1937373653218565</v>
+        <v>0.04069247268031605</v>
       </c>
       <c r="C5" t="n">
-        <v>0.104125449503205</v>
+        <v>0.02418347271651899</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3213055812621797</v>
+        <v>0.06411072611997443</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1041254502995427</v>
+        <v>0.02418347351285698</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1041254502995427</v>
+        <v>0.02418347351285698</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2565354448884633</v>
+        <v>0.05215583184832509</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4598988389742912</v>
+        <v>0.08919754554157927</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1041250828480774</v>
+        <v>0.02418310606139156</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2410610416429021</v>
+        <v>0.04925911951034245</v>
       </c>
       <c r="K5" t="n">
-        <v>0.134169801263712</v>
+        <v>0.02969769143883297</v>
       </c>
       <c r="L5" t="n">
-        <v>1.00724297409389</v>
+        <v>0.05654565058485384</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01974162324192761</v>
+        <v>0.009059756121580144</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0127296190818928</v>
+        <v>0.008097806649529998</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01542959571604268</v>
+        <v>0.01027655073264834</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01256510616247153</v>
+        <v>0.008068853032051269</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01295666278856688</v>
+        <v>0.008137766997870579</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02021955671018335</v>
+        <v>0.01056423575431633</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02195021132574761</v>
+        <v>0.01211858749309576</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0187084964073334</v>
+        <v>0.00814032081067555</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01450693349245506</v>
+        <v>0.009385596691922743</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01326624072959788</v>
+        <v>0.008418664900131717</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02066688580769376</v>
+        <v>0.01549869542043363</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01648480158706618</v>
+        <v>0.009496021632035237</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01545204140759951</v>
+        <v>0.008576952976258063</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01765727673237449</v>
+        <v>0.01066862481231049</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01544746079506786</v>
+        <v>0.008576147444639342</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01544746079506786</v>
+        <v>0.008576147444639342</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01696273505532201</v>
+        <v>0.009991035146166683</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01850015808020073</v>
+        <v>0.01151137812516974</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01545167475247205</v>
+        <v>0.008576586321130619</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0167732479977188</v>
+        <v>0.009784468042687821</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01586478942266419</v>
+        <v>0.008876009467633228</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02287633916408182</v>
+        <v>0.01588755920905081</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02528955104254171</v>
+        <v>0.01104565752780205</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03349502194894143</v>
+        <v>0.01175251753432711</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03761888829027139</v>
+        <v>0.01418186842746349</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03096801797301057</v>
+        <v>0.01130776549315569</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02454706428455719</v>
+        <v>0.01017767765011141</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03500809123068908</v>
+        <v>0.0131670178158219</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03654551425556735</v>
+        <v>0.01468736079482488</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03349703092783914</v>
+        <v>0.01175256899078582</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03482042021660706</v>
+        <v>0.01296077033600104</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02449788986423205</v>
+        <v>0.01039543513711599</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05057428174488507</v>
+        <v>0.0207623970768574</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03065068138906757</v>
+        <v>0.01198921646367786</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03512257430006543</v>
+        <v>0.01203896674657279</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03732796667707691</v>
+        <v>0.01413066622381869</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04147482119350363</v>
+        <v>0.01315696284994241</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03512256840725365</v>
+        <v>0.01203896636562039</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03663326794778796</v>
+        <v>0.0134530489164814</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03817069097266669</v>
+        <v>0.01497339189548446</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03512220764493804</v>
+        <v>0.01203860009144535</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03644378089018473</v>
+        <v>0.01324648181300255</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02860398106430729</v>
+        <v>0.01177668586365703</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04254687205654777</v>
+        <v>0.01934957297936555</v>
       </c>
     </row>
   </sheetData>
@@ -923,22 +923,22 @@
         <v>0.01055151844765867</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01021069761814162</v>
+        <v>0.01021069761814161</v>
       </c>
       <c r="G2" t="n">
         <v>0.01102029031688416</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01085388835128797</v>
+        <v>0.01085388835128796</v>
       </c>
       <c r="I2" t="n">
         <v>0.01093984434842619</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01085452924592965</v>
+        <v>0.01085452924592964</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01213091315563782</v>
+        <v>0.01213091315563781</v>
       </c>
       <c r="L2" t="n">
         <v>0.01073393690416562</v>
@@ -963,7 +963,7 @@
         <v>0.01139885935564806</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01105803852613101</v>
+        <v>0.011058038526131</v>
       </c>
       <c r="G3" t="n">
         <v>0.01187966239807515</v>
@@ -972,10 +972,10 @@
         <v>0.01168864990111406</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01178702702915768</v>
+        <v>0.01178702702915767</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01172146636933505</v>
+        <v>0.01172146636933504</v>
       </c>
       <c r="K3" t="n">
         <v>0.01297801203170427</v>
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009242091844520661</v>
+        <v>0.006741070799962355</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009177160387924429</v>
+        <v>0.006871366359934354</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009407326754878615</v>
+        <v>0.006906305710320308</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009221279791084403</v>
+        <v>0.006879132051031797</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009221279791084405</v>
+        <v>0.006879132051031799</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009444242124877975</v>
+        <v>0.006957607683761957</v>
       </c>
       <c r="H4" t="n">
-        <v>0.009362910949021426</v>
+        <v>0.006861889904463123</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009296234586571356</v>
+        <v>0.006892275642373213</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009491640895927703</v>
+        <v>0.006990619851369395</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009413129337229284</v>
+        <v>0.006912108292670977</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009291720373269955</v>
+        <v>0.006790699328711645</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02188635256390387</v>
+        <v>0.008966460674515288</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03677476015685553</v>
+        <v>0.01172854389294711</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03609302510708427</v>
+        <v>0.01160298859485903</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0367747609774664</v>
+        <v>0.01172854471355799</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03677476097746638</v>
+        <v>0.01172854471355799</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04154148150936767</v>
+        <v>0.01260672178482188</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03521513398967174</v>
+        <v>0.01141188113496298</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03677470217577623</v>
+        <v>0.01172848591186774</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04622063283517749</v>
+        <v>0.01345492239764985</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03583193757148162</v>
+        <v>0.01156181851670445</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03013237806488789</v>
+        <v>0.01022949158302068</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01432349387599605</v>
+        <v>0.007635397552656019</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01059379665441102</v>
+        <v>0.007120694341484984</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01073792521688384</v>
+        <v>0.007805098880796091</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0104737687851158</v>
+        <v>0.007099570112786856</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01063483426606548</v>
+        <v>0.007127917637280395</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01452564415635336</v>
+        <v>0.007193209063073053</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01454428882348591</v>
+        <v>0.007773812405427525</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01063487879445614</v>
+        <v>0.007127877021684305</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01459617632676896</v>
+        <v>0.007889018082329389</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01075567466925221</v>
+        <v>0.007148396269826587</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01063104216874455</v>
+        <v>0.007026419963437899</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01233312351715127</v>
+        <v>0.0072850923713975</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01238732424028132</v>
+        <v>0.007436355194887713</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01249823531049694</v>
+        <v>0.00745030561316141</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01238190218025572</v>
+        <v>0.007435401588511741</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01238190218025572</v>
+        <v>0.007435401588511741</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01253527379750858</v>
+        <v>0.007501629255197105</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01245394262165203</v>
+        <v>0.007405911475898271</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01238726625920197</v>
+        <v>0.007436297213808358</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0125826725685583</v>
+        <v>0.007534641422804539</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01250416100985989</v>
+        <v>0.007456129864106122</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01238275204590055</v>
+        <v>0.007334720900146792</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01912542882956584</v>
+        <v>0.008480538099904816</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02592134429230857</v>
+        <v>0.00981834271113746</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02743479646454562</v>
+        <v>0.01007914036202935</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02407689885039245</v>
+        <v>0.009493720991302591</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01939028836143794</v>
+        <v>0.008668877549716092</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02607300403414263</v>
+        <v>0.009884269763934101</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02599167285828637</v>
+        <v>0.009788551984635324</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02592499649583601</v>
+        <v>0.00981893772254536</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02612172847462472</v>
+        <v>0.009917515249360374</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0191711665911884</v>
+        <v>0.008629522840061795</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03296664265928396</v>
+        <v>0.01095748562847193</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01859856112966469</v>
+        <v>0.008387809385224676</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02144302283194982</v>
+        <v>0.009030158138385178</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02155405829647002</v>
+        <v>0.009044130450056361</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02466292594778383</v>
+        <v>0.009596861759884579</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02144302295953884</v>
+        <v>0.009030158837024209</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02159097238917709</v>
+        <v>0.009095432198694575</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02150964121332056</v>
+        <v>0.008999714419395739</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0214429648508705</v>
+        <v>0.009030100157305826</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02163837116022682</v>
+        <v>0.009128444366302012</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01994317196922962</v>
+        <v>0.008765395785860795</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0214384506375691</v>
+        <v>0.008928523843644259</v>
       </c>
     </row>
   </sheetData>
@@ -1316,13 +1316,13 @@
         <v>0.01382507383697777</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01095137637056896</v>
+        <v>0.01095137637056897</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01095137637056896</v>
+        <v>0.01095137637056897</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01283681242306757</v>
+        <v>0.01283681242306756</v>
       </c>
       <c r="H2" t="n">
         <v>0.01286252483702306</v>
@@ -1337,7 +1337,7 @@
         <v>0.01265922516188327</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01374435192202864</v>
+        <v>0.01374435192202865</v>
       </c>
     </row>
     <row r="3">
@@ -1353,7 +1353,7 @@
         <v>0.01401458868994183</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01502828878262493</v>
+        <v>0.01502828878262494</v>
       </c>
       <c r="E3" t="n">
         <v>0.01184444927317918</v>
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01000550607865324</v>
+        <v>0.007100389967753604</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0112813489995747</v>
+        <v>0.008505230148742507</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01141573627150689</v>
+        <v>0.008510620160607218</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009954626193678841</v>
+        <v>0.007242075954449767</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009954626193678845</v>
+        <v>0.007242075954449767</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01080745734487768</v>
+        <v>0.007919479933210169</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01084363505875339</v>
+        <v>0.007938518947853744</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01004885911884323</v>
+        <v>0.007258497688006423</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01157915335553955</v>
+        <v>0.008674037244639901</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01023256006841829</v>
+        <v>0.007327443957518644</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01136778377163802</v>
+        <v>0.008462667660738343</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04028682491485414</v>
+        <v>0.01242990205404643</v>
       </c>
       <c r="C5" t="n">
-        <v>0.187516084199499</v>
+        <v>0.03952254337585854</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1805740541640412</v>
+        <v>0.03828248394837132</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06192862665434441</v>
+        <v>0.01638949998596068</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06192862665434441</v>
+        <v>0.01638949998596068</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1268759513077459</v>
+        <v>0.02834753475998355</v>
       </c>
       <c r="H5" t="n">
-        <v>0.140161166490447</v>
+        <v>0.03069840435650493</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06192842852184178</v>
+        <v>0.01638930185345798</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2061825242636243</v>
+        <v>0.04292423033887463</v>
       </c>
       <c r="K5" t="n">
-        <v>0.06607460523806284</v>
+        <v>0.01715564385412098</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2014705379842068</v>
+        <v>0.04192075222085441</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01630816760831539</v>
+        <v>0.007410413680311988</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01330597433559978</v>
+        <v>0.008861564205952084</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01334111895319632</v>
+        <v>0.008849484971708775</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01153654567316549</v>
+        <v>0.007520493781330785</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01180530002732215</v>
+        <v>0.007567794547406051</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01711011887453984</v>
+        <v>0.00902874835642002</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01735523018399128</v>
+        <v>0.009084559683685671</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01635152064850537</v>
+        <v>0.008367766111216276</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01790880833487379</v>
+        <v>0.009788056514966295</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01192164313166896</v>
+        <v>0.007624722575039909</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01317135012871876</v>
+        <v>0.008780095337864552</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01377051213625172</v>
+        <v>0.007763031030300347</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01520452693911082</v>
+        <v>0.009195709462359423</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01518062339186818</v>
+        <v>0.009173240290200325</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01381343395955285</v>
+        <v>0.007921226117563549</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01381343395955285</v>
+        <v>0.007921226117563549</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01457246340247616</v>
+        <v>0.008582120995756913</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01460864111635185</v>
+        <v>0.008601160010400484</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01381386517644169</v>
+        <v>0.007921138750553162</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01534415941313803</v>
+        <v>0.009336678307186647</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01399756612601676</v>
+        <v>0.007990085020065384</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01513278982923646</v>
+        <v>0.009125308723285092</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02146263044797458</v>
+        <v>0.009116843845827787</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03078942145803524</v>
+        <v>0.01193865088283289</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03240093516318725</v>
+        <v>0.01220401514552991</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02724051216170054</v>
+        <v>0.01028439186833648</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02175603129139293</v>
+        <v>0.009319123240392744</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03015626441832862</v>
+        <v>0.01132486995968506</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03019244213221132</v>
+        <v>0.01134390897432988</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02939766619229408</v>
+        <v>0.01066388771448132</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03092951137039867</v>
+        <v>0.01207970023680116</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02154309237994188</v>
+        <v>0.009318097633560224</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03896011332102105</v>
+        <v>0.01331891763511567</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02294683510978926</v>
+        <v>0.009378063864891732</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02822619540022514</v>
+        <v>0.01148752309909711</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02820241260658913</v>
+        <v>0.01146507517957266</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0312731771364121</v>
+        <v>0.01099414090003986</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0268357290230388</v>
+        <v>0.01021315003631805</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0275941318635905</v>
+        <v>0.0108739346324946</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02763030957746617</v>
+        <v>0.01089297364713817</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02683553363755602</v>
+        <v>0.01021295238729085</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02836582787425235</v>
+        <v>0.01162849194392433</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02217725775576644</v>
+        <v>0.009889769336572792</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02815445829035081</v>
+        <v>0.01141712236002278</v>
       </c>
     </row>
   </sheetData>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01120278275538451</v>
+        <v>0.01120278275538452</v>
       </c>
       <c r="C2" t="n">
         <v>0.01160306136235348</v>
@@ -1727,7 +1727,7 @@
         <v>0.01138581819014848</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0129255602845801</v>
+        <v>0.01292556028458009</v>
       </c>
       <c r="K2" t="n">
         <v>0.01209893221118648</v>
@@ -1761,13 +1761,13 @@
         <v>0.01295723214496571</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01288915964005539</v>
+        <v>0.0128891596400554</v>
       </c>
       <c r="I3" t="n">
         <v>0.01223202509144274</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01398134654387917</v>
+        <v>0.01398134654387916</v>
       </c>
       <c r="K3" t="n">
         <v>0.01292288245727118</v>
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009663935442365421</v>
+        <v>0.006947111712937386</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01035029875988312</v>
+        <v>0.007768165776161692</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01064000951832708</v>
+        <v>0.00792318578889906</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009679981339906472</v>
+        <v>0.007039726238189532</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009679981339906472</v>
+        <v>0.007039726238189534</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0101283121573309</v>
+        <v>0.00742725751687146</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01011213054512741</v>
+        <v>0.007395306815699379</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009644289619618187</v>
+        <v>0.007033333502774016</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0106014113666349</v>
+        <v>0.007884587637206895</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009683900537734189</v>
+        <v>0.006967076808306134</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009980975157441513</v>
+        <v>0.0072641514280135</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03005601494619135</v>
+        <v>0.01053611768616335</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1145569473257199</v>
+        <v>0.02610853582436982</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1233377516891701</v>
+        <v>0.02775798830349048</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04385678752606704</v>
+        <v>0.01305484409436023</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04385678752606704</v>
+        <v>0.01305484409436023</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07999011037387252</v>
+        <v>0.01972293393635733</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08326460718059631</v>
+        <v>0.0202701426337783</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04385665282621427</v>
+        <v>0.01305470939450747</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1255223583386776</v>
+        <v>0.02811067419468925</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03557699633678959</v>
+        <v>0.01152426164424631</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07080631123171578</v>
+        <v>0.01796941051907823</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01528376470459533</v>
+        <v>0.007936201657730384</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01209003064487562</v>
+        <v>0.008074358586261232</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01229506335523469</v>
+        <v>0.008919788373776863</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01097930456448345</v>
+        <v>0.007268407124475949</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0111877716801197</v>
+        <v>0.007305097336629118</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01166599391327691</v>
+        <v>0.007697889504451526</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01596067528366681</v>
+        <v>0.008424650684104716</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01118197137556427</v>
+        <v>0.007303965490354081</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01229789291654852</v>
+        <v>0.008183168388373796</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01116675370392675</v>
+        <v>0.007228058964141873</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01152196139801929</v>
+        <v>0.00753536500488559</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01306215257392589</v>
+        <v>0.007545197924851242</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0139134946085246</v>
+        <v>0.008395288242124462</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01403811873577113</v>
+        <v>0.008521253007928527</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01304964725323385</v>
+        <v>0.007632787435721588</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01304964725323385</v>
+        <v>0.007632787435721588</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01352652928889136</v>
+        <v>0.008025343728785316</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01351034767668792</v>
+        <v>0.007993393027613239</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01304250675117868</v>
+        <v>0.007631419714687874</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01399962849819539</v>
+        <v>0.008482673849120742</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01308211766929469</v>
+        <v>0.007565163020219986</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01337919228900201</v>
+        <v>0.007862237639927362</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02023795551901086</v>
+        <v>0.008808139236342822</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0283697349385843</v>
+        <v>0.01093958652643463</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02999414647325836</v>
+        <v>0.01132951387450942</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02550911037370743</v>
+        <v>0.009825652933042668</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02045320502873918</v>
+        <v>0.00893581359714994</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02797451470338648</v>
+        <v>0.01056818914795779</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02795833309120167</v>
+        <v>0.01053623844678896</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02749049216567387</v>
+        <v>0.01017426513386036</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02844904310442898</v>
+        <v>0.01102577080603782</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02012283609149831</v>
+        <v>0.008804329455813267</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03542358038240608</v>
+        <v>0.01174204992334332</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02034905768088958</v>
+        <v>0.008827693216727512</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0243963672747736</v>
+        <v>0.01024027382138704</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02452110091267818</v>
+        <v>0.0103662578610668</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02721359233888419</v>
+        <v>0.01012564175728825</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0235255125016063</v>
+        <v>0.009476539709444566</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02400940195514035</v>
+        <v>0.009870329308047881</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0239932203429369</v>
+        <v>0.009838378606875822</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02352537941742771</v>
+        <v>0.009476405293950448</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02448250116444443</v>
+        <v>0.01032765942838332</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02171323485165977</v>
+        <v>0.009084239636084965</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02386206495525102</v>
+        <v>0.009707223219189941</v>
       </c>
     </row>
   </sheetData>
@@ -2120,13 +2120,13 @@
         <v>0.01144783574514345</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01088866814818705</v>
+        <v>0.01088866814818704</v>
       </c>
       <c r="J2" t="n">
         <v>0.01161224427552077</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01181984398876877</v>
+        <v>0.01181984398876876</v>
       </c>
       <c r="L2" t="n">
         <v>0.01102209387981605</v>
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01166455666474106</v>
+        <v>0.01166455666474105</v>
       </c>
       <c r="C3" t="n">
         <v>0.01180686627316696</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01300083139277923</v>
+        <v>0.01300083139277921</v>
       </c>
       <c r="E3" t="n">
         <v>0.01099517078104427</v>
@@ -2154,19 +2154,19 @@
         <v>0.01099517078104427</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01226087872013081</v>
+        <v>0.0122608787201308</v>
       </c>
       <c r="H3" t="n">
         <v>0.01233136633375007</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01168767888831292</v>
+        <v>0.01168767888831289</v>
       </c>
       <c r="J3" t="n">
         <v>0.01250243751658786</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01261998310380355</v>
+        <v>0.01261998310380356</v>
       </c>
       <c r="L3" t="n">
         <v>0.01184125750618846</v>
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009360913720539321</v>
+        <v>0.006768531995398325</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00976818916803391</v>
+        <v>0.007313419915145464</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01005153601712848</v>
+        <v>0.00745915429198749</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009302381237424296</v>
+        <v>0.006768255716945831</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009302381237424296</v>
+        <v>0.006768255716945831</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009654383815832574</v>
+        <v>0.007074135484696068</v>
       </c>
       <c r="H4" t="n">
-        <v>0.009705386715057893</v>
+        <v>0.00711300498991688</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009273825741937681</v>
+        <v>0.006763140230141268</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009733450168417554</v>
+        <v>0.007141068443276557</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009377053270988886</v>
+        <v>0.006784671545847896</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009452495731085805</v>
+        <v>0.006860114005944808</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.017498393335548</v>
+        <v>0.008200728399879342</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07600951121595942</v>
+        <v>0.01897189253240771</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08491950799497558</v>
+        <v>0.02063591728868888</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02259097976529476</v>
+        <v>0.009107049045178008</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02259097976529476</v>
+        <v>0.009107049045178008</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05085408827389838</v>
+        <v>0.01432528343002449</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05869051389332069</v>
+        <v>0.01573438732657526</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02259087088225394</v>
+        <v>0.009106940162136687</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0580466237923369</v>
+        <v>0.01564418695501133</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02298732871087349</v>
+        <v>0.009180080010287819</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03282164341862912</v>
+        <v>0.01097308397666587</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01473073662171136</v>
+        <v>0.00701843176707209</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01136787877881346</v>
+        <v>0.007594965285116832</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01155378745295563</v>
+        <v>0.007723550543260121</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01050235538130707</v>
+        <v>0.006979451165124815</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01069679460426255</v>
+        <v>0.007013672468179546</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01107426888985457</v>
+        <v>0.008019224310181282</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01529462415252102</v>
+        <v>0.008096710773580084</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01069371081595968</v>
+        <v>0.007708229055626486</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01128644633087963</v>
+        <v>0.008088519756998447</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01076765136936394</v>
+        <v>0.007029416809835723</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01086685988152048</v>
+        <v>0.007109042095072482</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01262499162992525</v>
+        <v>0.007343009704337382</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01320086684957443</v>
+        <v>0.007917571183822938</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01331550480429204</v>
+        <v>0.008033612795415509</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01254633430353746</v>
+        <v>0.00733919145348807</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01254633430353746</v>
+        <v>0.00733919145348807</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0129184617252185</v>
+        <v>0.007648613193635126</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01296946462444381</v>
+        <v>0.007687482698855936</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01253790365132361</v>
+        <v>0.007337617939080326</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01299752807780347</v>
+        <v>0.00771554615221561</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01264113118037482</v>
+        <v>0.007359149254786952</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01271657364047176</v>
+        <v>0.007434591714883864</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01970968541421873</v>
+        <v>0.008589915803616543</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02740313228627368</v>
+        <v>0.0104171698871308</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02898230160874908</v>
+        <v>0.01079096901805893</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02479525173131234</v>
+        <v>0.009495000909094973</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01985305110447953</v>
+        <v>0.008625173603485643</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02711124147720586</v>
+        <v>0.01014654241644961</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02716224437645052</v>
+        <v>0.01018541192167382</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02673068340331099</v>
+        <v>0.009835547161894807</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02719170477176479</v>
+        <v>0.01021372123681618</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01959378861855867</v>
+        <v>0.008582816957276742</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03433434355370852</v>
+        <v>0.01123931919899723</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01888440698455426</v>
+        <v>0.008444666800782647</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02232586575230575</v>
+        <v>0.009523570982001369</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02244061404452019</v>
+        <v>0.009639632012993277</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02496983352926701</v>
+        <v>0.009525727305368496</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02166301010850779</v>
+        <v>0.008943726386468504</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02204346062794982</v>
+        <v>0.00925461299181355</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02209446352717513</v>
+        <v>0.009293482497034369</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02166290255405492</v>
+        <v>0.00894361773725876</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02212252698053483</v>
+        <v>0.009321545950394044</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02003843850380384</v>
+        <v>0.008330091511194265</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02184157254320305</v>
+        <v>0.009040591513062293</v>
       </c>
     </row>
   </sheetData>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01103700703803392</v>
+        <v>0.01103700703803391</v>
       </c>
       <c r="C2" t="n">
         <v>0.009858786617870589</v>
@@ -2507,10 +2507,10 @@
         <v>0.0103092680153662</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01030926801536621</v>
+        <v>0.0103092680153662</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01202058165695583</v>
+        <v>0.01202058165695582</v>
       </c>
       <c r="H2" t="n">
         <v>0.0123751848667125</v>
@@ -2519,10 +2519,10 @@
         <v>0.01111958625338044</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01393863467602903</v>
+        <v>0.01393863467602902</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01227092556843209</v>
+        <v>0.01227092556843208</v>
       </c>
       <c r="L2" t="n">
         <v>0.01347254438482196</v>
@@ -2553,7 +2553,7 @@
         <v>0.01295341746317764</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01336177288558555</v>
+        <v>0.01336177288558554</v>
       </c>
       <c r="I3" t="n">
         <v>0.01191687404148443</v>
@@ -2562,7 +2562,7 @@
         <v>0.01514468366609814</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01311668043741595</v>
+        <v>0.01311668043741594</v>
       </c>
       <c r="L3" t="n">
         <v>0.01462342120917595</v>
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009382032921656073</v>
+        <v>0.006799421538481405</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009088441910288332</v>
+        <v>0.006716751526611653</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01017754143110776</v>
+        <v>0.007594930047933093</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009253624593520658</v>
+        <v>0.006817384578790458</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009253624593520655</v>
+        <v>0.006817384578790458</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009946324615010745</v>
+        <v>0.007380524265617499</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01017753650715899</v>
+        <v>0.007594925123984311</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009294293970101127</v>
+        <v>0.006824399282777707</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01104799087169784</v>
+        <v>0.008465379488523161</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009622096106248559</v>
+        <v>0.007039484723073888</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01082973182893002</v>
+        <v>0.008247120445755346</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01986105529916743</v>
+        <v>0.00864372946692982</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02062544518865496</v>
+        <v>0.008747264092601641</v>
       </c>
       <c r="D5" t="n">
-        <v>0.101135785632835</v>
+        <v>0.02360358094069257</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02881575205157908</v>
+        <v>0.01026031899275285</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02881575205157908</v>
+        <v>0.01026031899275285</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08268663643122165</v>
+        <v>0.02018281907589999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1130704502917182</v>
+        <v>0.02570407785194039</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02881557837894319</v>
+        <v>0.01026014532011697</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1947473693202996</v>
+        <v>0.04079646992028754</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04742827462437646</v>
+        <v>0.01369337210620958</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1881881707628134</v>
+        <v>0.03946220552897665</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01506837166605801</v>
+        <v>0.007054822760295432</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01065007079305996</v>
+        <v>0.006991598208490175</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01170636734810901</v>
+        <v>0.00786400340786733</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01050808994974162</v>
+        <v>0.007038170480289002</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01074038400438349</v>
+        <v>0.007079054233684433</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01139746792863544</v>
+        <v>0.00763592548743153</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01605186888021934</v>
+        <v>0.008628807616040729</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01498063271450304</v>
+        <v>0.007079800504591735</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01675096012640763</v>
+        <v>0.009469102071913309</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01103393261625423</v>
+        <v>0.007287967947488452</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0123254645256243</v>
+        <v>0.008510369398947098</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01293903303226724</v>
+        <v>0.007425453554556751</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01290016561486225</v>
+        <v>0.007387614894981518</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01373443153338484</v>
+        <v>0.00822094270254174</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0128641823948332</v>
+        <v>0.007452842748378171</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0128641823948332</v>
+        <v>0.007452842748378171</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0135033247256219</v>
+        <v>0.008006556281692846</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01373453661777015</v>
+        <v>0.008220957140059654</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01285129408071228</v>
+        <v>0.00745043129885305</v>
       </c>
       <c r="J7" t="n">
-        <v>0.014604990982309</v>
+        <v>0.009091411504598503</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01317909621685973</v>
+        <v>0.00766551673914923</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01438673193954118</v>
+        <v>0.008873152461830687</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02046756544554387</v>
+        <v>0.008750475252113666</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02805375294696552</v>
+        <v>0.01005464625098011</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03045260266886609</v>
+        <v>0.01116334080644274</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02592196490563144</v>
+        <v>0.009751012457825793</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02062891652215134</v>
+        <v>0.008819435947381132</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02864313732359506</v>
+        <v>0.01067116328449767</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02887434921574797</v>
+        <v>0.0108855641428653</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02799110667868545</v>
+        <v>0.01011503830165787</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02974629941463961</v>
+        <v>0.01175628177424881</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0205662451930909</v>
+        <v>0.008965654951920983</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03747716313508774</v>
+        <v>0.01293706833022613</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02105140685037402</v>
+        <v>0.008853231338806975</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02448683865213719</v>
+        <v>0.009426869338492001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02532121644011384</v>
+        <v>0.01026021683507602</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0284474079836824</v>
+        <v>0.0101954904371543</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02443813909363859</v>
+        <v>0.009489859116330136</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02508999776289686</v>
+        <v>0.01004581072520332</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0253212096550451</v>
+        <v>0.01026021158357012</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02443796711798722</v>
+        <v>0.009489685742363523</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02619166401958396</v>
+        <v>0.01113066594810899</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02039100589462273</v>
+        <v>0.008934812835557705</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02597340497681614</v>
+        <v>0.01091240690534116</v>
       </c>
     </row>
   </sheetData>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01084682749310564</v>
+        <v>0.01084682749310565</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00980406038285613</v>
+        <v>0.009804060382856132</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01092010199889243</v>
+        <v>0.01092010199889244</v>
       </c>
       <c r="E2" t="n">
         <v>0.01019710308786291</v>
@@ -2915,7 +2915,7 @@
         <v>0.01093699869952531</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01178889453861607</v>
+        <v>0.01178889453861608</v>
       </c>
       <c r="K2" t="n">
         <v>0.0117579206521113</v>
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01161256015766828</v>
+        <v>0.01161256015766827</v>
       </c>
       <c r="C3" t="n">
         <v>0.01056950975876712</v>
@@ -2946,7 +2946,7 @@
         <v>0.01097643736851805</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01174180570921493</v>
+        <v>0.01174180570921494</v>
       </c>
       <c r="H3" t="n">
         <v>0.01175614759915207</v>
@@ -2958,10 +2958,10 @@
         <v>0.01267412645700022</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01252820732361273</v>
+        <v>0.01252820732361274</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01195228843292338</v>
+        <v>0.01195228843292337</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009148341321507979</v>
+        <v>0.006698711940845475</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008960181864454055</v>
+        <v>0.006665943111873125</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009191899910294036</v>
+        <v>0.006742270529631532</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009172562083784752</v>
+        <v>0.006747330350597596</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009172562083784756</v>
+        <v>0.006747330350597596</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00919730401287234</v>
+        <v>0.006762370544441593</v>
       </c>
       <c r="H4" t="n">
-        <v>0.009222412872768123</v>
+        <v>0.006772783492105615</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009081887895145805</v>
+        <v>0.006731329708418513</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009621269827768253</v>
+        <v>0.007171640447105746</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009166364193033906</v>
+        <v>0.0067167348123714</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009324049469134458</v>
+        <v>0.006874420088471949</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01506199822855904</v>
+        <v>0.007739515550846757</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01934859758333051</v>
+        <v>0.008494304268488215</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02306520413673461</v>
+        <v>0.00918397206025447</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02402276509698535</v>
+        <v>0.009360966066758646</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02402276509698535</v>
+        <v>0.009360966066758646</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02554402547484349</v>
+        <v>0.009639393506159107</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02786034169661539</v>
+        <v>0.01005305894732823</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02402271414423653</v>
+        <v>0.009360915114009782</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06524841055497371</v>
+        <v>0.01696201716204372</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02075987458457977</v>
+        <v>0.008757192630227039</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03901056707428644</v>
+        <v>0.01209924715866744</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01043588070950638</v>
+        <v>0.006925318871905299</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0103758759498736</v>
+        <v>0.006915105269556855</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01425083304011553</v>
+        <v>0.006968140015444764</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01023386049931733</v>
+        <v>0.006934118870719198</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01038048433669514</v>
+        <v>0.006959924665957859</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01048484340087073</v>
+        <v>0.007651522223979208</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01445250124485155</v>
+        <v>0.007693279040604496</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0103694272831442</v>
+        <v>0.007620481387956124</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01103405912367249</v>
+        <v>0.007420291361837554</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01044559223338148</v>
+        <v>0.006941878946252606</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01061066962008031</v>
+        <v>0.007100865233811398</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01228500152582843</v>
+        <v>0.007250764133814526</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01228662508810386</v>
+        <v>0.007251397116063147</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01232845655571283</v>
+        <v>0.007294304496233985</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01223553330287636</v>
+        <v>0.007286413282236641</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01223553330287636</v>
+        <v>0.007286413282236641</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01233396421719281</v>
+        <v>0.00731442273741064</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01235907307708859</v>
+        <v>0.007324835685074665</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01221854809946626</v>
+        <v>0.007283381901387562</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01275793003208871</v>
+        <v>0.007723692640074796</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01230302439735436</v>
+        <v>0.007268787005340448</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0124607096734549</v>
+        <v>0.007426472281440995</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01924415524500005</v>
+        <v>0.008475575181751953</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02617023028195391</v>
+        <v>0.009694911616940314</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02762666799955605</v>
+        <v>0.009986789695760882</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02421137417267077</v>
+        <v>0.009394161263899411</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01940685113208513</v>
+        <v>0.008548565213338284</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02619990484343033</v>
+        <v>0.009754828274404848</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02622501370333972</v>
+        <v>0.009765241222071269</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02608448872570378</v>
+        <v>0.009723787438381776</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02662522803959761</v>
+        <v>0.01016433707617147</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01913388100379107</v>
+        <v>0.008471017761558898</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0335413667600679</v>
+        <v>0.0111366679085808</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0185534024896291</v>
+        <v>0.008354002697465427</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0213701973412116</v>
+        <v>0.008850105823947347</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02141213346778159</v>
+        <v>0.008893031624095219</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02455081951501883</v>
+        <v>0.009453903643828948</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02130217069626597</v>
+        <v>0.008882141454826593</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02141753647030054</v>
+        <v>0.008913131445294842</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02144264533019633</v>
+        <v>0.008923544392958862</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02130212035257401</v>
+        <v>0.00888209060927176</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02184150228519647</v>
+        <v>0.009322401347958991</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01975547581208742</v>
+        <v>0.008243610310347373</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02154428192656267</v>
+        <v>0.009025180989325188</v>
       </c>
     </row>
   </sheetData>
@@ -3290,7 +3290,7 @@
         <v>0.01074976395347068</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009800580113694527</v>
+        <v>0.009800580113694529</v>
       </c>
       <c r="D2" t="n">
         <v>0.01081400604429576</v>
@@ -3299,7 +3299,7 @@
         <v>0.01013982797427362</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01013982797427362</v>
+        <v>0.01013982797427361</v>
       </c>
       <c r="G2" t="n">
         <v>0.01079198642715061</v>
@@ -3314,7 +3314,7 @@
         <v>0.01097373117738925</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01170541766040176</v>
+        <v>0.01170541766040175</v>
       </c>
       <c r="L2" t="n">
         <v>0.01077903833731559</v>
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01152865391495837</v>
+        <v>0.01152865391495836</v>
       </c>
       <c r="C3" t="n">
         <v>0.01058075575644524</v>
@@ -3336,10 +3336,10 @@
         <v>0.01160254562711623</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01092666787268204</v>
+        <v>0.01092666787268203</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01092666787268204</v>
+        <v>0.01092666787268203</v>
       </c>
       <c r="G3" t="n">
         <v>0.01157721850604935</v>
@@ -3348,10 +3348,10 @@
         <v>0.01160452893561027</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01158945321372123</v>
+        <v>0.01158945321372122</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01176699921617865</v>
+        <v>0.01176699921617864</v>
       </c>
       <c r="K3" t="n">
         <v>0.01248493929993287</v>
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009122991796166562</v>
+        <v>0.00668841901629446</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008961966361669047</v>
+        <v>0.00666548748283935</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009161180996993768</v>
+        <v>0.006726608217121666</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009126275154577337</v>
+        <v>0.00671492203235594</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009126275154577338</v>
+        <v>0.00671492203235594</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009134437734099804</v>
+        <v>0.006711115465887187</v>
       </c>
       <c r="H4" t="n">
-        <v>0.009162079511230365</v>
+        <v>0.006727506731358264</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009062063810528828</v>
+        <v>0.006703588693901389</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009179894265460181</v>
+        <v>0.00674532148558808</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00912549171599002</v>
+        <v>0.006690918936117918</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00914056348856882</v>
+        <v>0.006705990708696718</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01476820190329688</v>
+        <v>0.007681975989765704</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01963772554763762</v>
+        <v>0.008544421089388667</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02228702198696071</v>
+        <v>0.009036756218838071</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02168673171683511</v>
+        <v>0.008925562375334716</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02168673171683511</v>
+        <v>0.008925562375334716</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0213084909131357</v>
+        <v>0.008853748813787393</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02389843952376059</v>
+        <v>0.009321106079509891</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02168669270959822</v>
+        <v>0.008925523368097802</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0247010253679087</v>
+        <v>0.009477040544816923</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0190415173847085</v>
+        <v>0.008436139444355709</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02189701521440156</v>
+        <v>0.008951126200277774</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01415455846559878</v>
+        <v>0.007573974745316056</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01035908677388066</v>
+        <v>0.006911380674056194</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01043439727670713</v>
+        <v>0.006950694281136985</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01020584431257665</v>
+        <v>0.006904926203134262</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01035078356809321</v>
+        <v>0.006930435511966953</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01416600440353203</v>
+        <v>0.007596671194908752</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01436881337553584</v>
+        <v>0.007643891886510498</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01034196691485289</v>
+        <v>0.006928851639041811</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01420473075313709</v>
+        <v>0.007629692702627157</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01040320760364812</v>
+        <v>0.006915796931127241</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01041343747491147</v>
+        <v>0.006930016529079115</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01220842379617992</v>
+        <v>0.007231455045354312</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01221641633974336</v>
+        <v>0.007238270675876745</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01224650483022364</v>
+        <v>0.007269625208827729</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01216098600453466</v>
+        <v>0.007249031139054304</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01216098600453466</v>
+        <v>0.007249031139054304</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01221986973411315</v>
+        <v>0.00725415149494701</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01224751151124371</v>
+        <v>0.007270542760418116</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01214749581054218</v>
+        <v>0.007246624722961238</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01226532626547353</v>
+        <v>0.007288357514647932</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01221092371600338</v>
+        <v>0.00723395496517777</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01222599548858216</v>
+        <v>0.00724902673775657</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01914370681094111</v>
+        <v>0.008452064849338282</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02601413048069666</v>
+        <v>0.009666668351526004</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0274499897516076</v>
+        <v>0.009945438540492143</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02407081639315783</v>
+        <v>0.009345161276093887</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01930798072533574</v>
+        <v>0.008506902203099395</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02600324909926997</v>
+        <v>0.009680026250069758</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02603089087641587</v>
+        <v>0.009696417515543562</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02593087517569901</v>
+        <v>0.009672499478083988</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02605005147755032</v>
+        <v>0.009714469138827314</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01901899982524531</v>
+        <v>0.008432176353911669</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03316278412007852</v>
+        <v>0.01093390151693305</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01801657642781145</v>
+        <v>0.008253689902982381</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02069351263412288</v>
+        <v>0.008730239615603151</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02072371029611695</v>
+        <v>0.008761613362740459</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02370453568492098</v>
+        <v>0.009280695871793511</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0206246305269133</v>
+        <v>0.008738632566921384</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02069696602849266</v>
+        <v>0.008746120434673413</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02072460780562323</v>
+        <v>0.008762511700144516</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02062459210492168</v>
+        <v>0.008738593662687644</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02074242255985305</v>
+        <v>0.008780326454374338</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01914162399302173</v>
+        <v>0.008442716094001452</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02070309178296167</v>
+        <v>0.008740995677482972</v>
       </c>
     </row>
   </sheetData>
@@ -3683,22 +3683,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01095183655602006</v>
+        <v>0.01095183655602005</v>
       </c>
       <c r="C2" t="n">
         <v>0.009827913321975242</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01116763974484075</v>
+        <v>0.01116763974484076</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01025592614073575</v>
+        <v>0.01025592614073574</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01025592614073575</v>
+        <v>0.01025592614073574</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01129044372126108</v>
+        <v>0.01129044372126107</v>
       </c>
       <c r="H2" t="n">
         <v>0.01207161613201261</v>
@@ -3707,13 +3707,13 @@
         <v>0.01104534087868338</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01120621927942075</v>
+        <v>0.01120621927942074</v>
       </c>
       <c r="K2" t="n">
         <v>0.01185991850736202</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01290517310809394</v>
+        <v>0.01290517310809393</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01172468219604269</v>
+        <v>0.01172468219604267</v>
       </c>
       <c r="C3" t="n">
         <v>0.01059476328878152</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01197290056668238</v>
+        <v>0.01197290056668237</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01104286693799908</v>
+        <v>0.01104286693799909</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01104286693799908</v>
+        <v>0.01104286693799907</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01211415057833284</v>
+        <v>0.01211415057833281</v>
       </c>
       <c r="H3" t="n">
         <v>0.01301311419062684</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01183246120793079</v>
+        <v>0.01183246120793077</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01200441472368375</v>
+        <v>0.01200441472368374</v>
       </c>
       <c r="K3" t="n">
         <v>0.0126435735259905</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01397135258788172</v>
+        <v>0.0139713525878817</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009253241662826324</v>
+        <v>0.006743669150381796</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009004713197850577</v>
+        <v>0.006681704158357704</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009381527514223432</v>
+        <v>0.006871955001778895</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009172495686861012</v>
+        <v>0.006775422876862677</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009172495686861012</v>
+        <v>0.006775422876862677</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009435470057031317</v>
+        <v>0.006941602339848118</v>
       </c>
       <c r="H4" t="n">
-        <v>0.009918814991551847</v>
+        <v>0.007409242479107319</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009180682983418717</v>
+        <v>0.006776794716846192</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009353565678834764</v>
+        <v>0.006843993166390215</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009296020702143973</v>
+        <v>0.00678644818969942</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0104142258771086</v>
+        <v>0.007904653364664086</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01790171574487865</v>
+        <v>0.008265800580575187</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02018544528382323</v>
+        <v>0.008649512994826115</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03450152633317845</v>
+        <v>0.0112930747699587</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02751058345675357</v>
+        <v>0.01000292630687528</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02751058345675357</v>
+        <v>0.01000292630687528</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04240445482851499</v>
+        <v>0.01274414362818754</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0966190230418514</v>
+        <v>0.02266847901327624</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02751049956815799</v>
+        <v>0.01000284241827968</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03288654005096916</v>
+        <v>0.01098579663344307</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0262739337615064</v>
+        <v>0.009774560871955803</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1538470502292054</v>
+        <v>0.03314883031384484</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01465508616911594</v>
+        <v>0.006975308595516864</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01046063264684213</v>
+        <v>0.006937945979991744</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01069543746381753</v>
+        <v>0.007103203151654401</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01032522942315201</v>
+        <v>0.006978304013350561</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01049807654098649</v>
+        <v>0.007008725105924587</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01483731456332091</v>
+        <v>0.007892326967803499</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01549777397470585</v>
+        <v>0.008391139254821916</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01049681620154509</v>
+        <v>0.007727519344801557</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01475853277913382</v>
+        <v>0.007795267370888283</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01058210844583094</v>
+        <v>0.007012799631361827</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01176536320927431</v>
+        <v>0.00814245353383671</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01263322485417395</v>
+        <v>0.007338546188835578</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01261165429139336</v>
+        <v>0.007316525787381385</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01276140140679375</v>
+        <v>0.007466812803647993</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01257639032134109</v>
+        <v>0.007374508329284963</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01257639032134109</v>
+        <v>0.007374508329284963</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01281545324837896</v>
+        <v>0.0075364793783019</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01329879818289948</v>
+        <v>0.00800411951756109</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01256066617476635</v>
+        <v>0.007371671755299972</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01273354887018238</v>
+        <v>0.007438870204844007</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0126760038934916</v>
+        <v>0.007381325228153203</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01379420906845625</v>
+        <v>0.008499530403117872</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02003262290433575</v>
+        <v>0.008640840238607447</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02741052719129777</v>
+        <v>0.009921127403651248</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02907476074481516</v>
+        <v>0.0103379640315821</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02533868841336667</v>
+        <v>0.009620672781310402</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0202035715829931</v>
+        <v>0.008716892224061872</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02759780064516</v>
+        <v>0.01013817250603784</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02808114557968493</v>
+        <v>0.01060581264529779</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02734301357154741</v>
+        <v>0.009973364883035905</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0275173472277969</v>
+        <v>0.01004081870168522</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01993825986914762</v>
+        <v>0.008659482272942855</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03628866440975081</v>
+        <v>0.01245855452173335</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01999606646918795</v>
+        <v>0.008634406306056275</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02317784031235484</v>
+        <v>0.0091761745169939</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02332769741913463</v>
+        <v>0.009326480891743153</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02682352623662592</v>
+        <v>0.009882004236787966</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02312693448721517</v>
+        <v>0.009231404092417021</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02338163926934041</v>
+        <v>0.009396128107914415</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02386498420386091</v>
+        <v>0.009863768247173619</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02312685219572782</v>
+        <v>0.009231320484912486</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02329973489114384</v>
+        <v>0.009298518934456521</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02131085836519</v>
+        <v>0.008914312672846971</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0243603950894177</v>
+        <v>0.01035917913273038</v>
       </c>
     </row>
   </sheetData>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01081806961916108</v>
+        <v>0.01081806961916107</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009813353247750988</v>
+        <v>0.00981335324775099</v>
       </c>
       <c r="D2" t="n">
         <v>0.01087392325301149</v>
@@ -4094,16 +4094,16 @@
         <v>0.01018989708909295</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01085517976032054</v>
+        <v>0.01085517976032053</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0108769028304426</v>
+        <v>0.01087690283044261</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01089569197716647</v>
+        <v>0.01089569197716648</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0110799421618263</v>
+        <v>0.01107994216182631</v>
       </c>
       <c r="K2" t="n">
         <v>0.01175764591854281</v>
@@ -4128,10 +4128,10 @@
         <v>0.01164703839059595</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01096634044284812</v>
+        <v>0.01096634044284811</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01096634044284812</v>
+        <v>0.01096634044284811</v>
       </c>
       <c r="G3" t="n">
         <v>0.01162547949129854</v>
@@ -4140,7 +4140,7 @@
         <v>0.01165089098073638</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01167260108207985</v>
+        <v>0.01167260108207984</v>
       </c>
       <c r="J3" t="n">
         <v>0.01185911718242997</v>
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009125176708116512</v>
+        <v>0.006695010342583776</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008939474538838177</v>
+        <v>0.006661648570461851</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009158379326721356</v>
+        <v>0.00672821296118862</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009157159721783104</v>
+        <v>0.00673885179139918</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009157159721783105</v>
+        <v>0.00673885179139918</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00912954530790925</v>
+        <v>0.006713956991061857</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00916023676170097</v>
+        <v>0.006730070396168241</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009052175185425556</v>
+        <v>0.006720339353839853</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009182361831487998</v>
+        <v>0.006752195465955242</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009135831763430375</v>
+        <v>0.006705665397897654</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009135851364962234</v>
+        <v>0.006705684999429498</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01540058145261527</v>
+        <v>0.007799481571630865</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01956537263139859</v>
+        <v>0.00853180662461884</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02243543069012202</v>
+        <v>0.009064973988485162</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02365691617056012</v>
+        <v>0.009290808912555871</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02365691617056012</v>
+        <v>0.009290808912555871</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02164200261868379</v>
+        <v>0.008916149465825376</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02416703062576658</v>
+        <v>0.009371266101932188</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02365687350155468</v>
+        <v>0.009290766243550432</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02536732329673708</v>
+        <v>0.009600748668403899</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02040328053519109</v>
+        <v>0.008688736370982048</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02186651012796135</v>
+        <v>0.008946280929576441</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01413814496665582</v>
+        <v>0.006918027035776168</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01033697163322463</v>
+        <v>0.006907608057741108</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0104243375157742</v>
+        <v>0.006951018790378133</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01019250548640859</v>
+        <v>0.006921072644985883</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01033138295475469</v>
+        <v>0.006945515079282353</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01039668561700487</v>
+        <v>0.006936973684254247</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01434645922212933</v>
+        <v>0.007642845544257671</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01031931549452118</v>
+        <v>0.007602621762562035</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0105598025275085</v>
+        <v>0.00763327908792581</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01039801022196879</v>
+        <v>0.006927808805396708</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01039693721824747</v>
+        <v>0.006927636108405042</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01221709511555281</v>
+        <v>0.007239187979343888</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01221768988195344</v>
+        <v>0.007238614467723784</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01225019437200152</v>
+        <v>0.007272372406209352</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01216453079153281</v>
+        <v>0.007268149096807078</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01216453079153281</v>
+        <v>0.007268149096807078</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01222146371534553</v>
+        <v>0.007258134627821967</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01225215516913729</v>
+        <v>0.007274248032928358</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01214409359286188</v>
+        <v>0.007264516990599962</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01227428023892428</v>
+        <v>0.007296373102715353</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0122277501708667</v>
+        <v>0.007249843034657763</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01222776977239854</v>
+        <v>0.007249862636189613</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01914296970679563</v>
+        <v>0.00845814190079759</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02601162947344108</v>
+        <v>0.009666347822670682</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02744306952312085</v>
+        <v>0.009946318418317286</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02406322012853785</v>
+        <v>0.009362318408772483</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01929928150625392</v>
+        <v>0.008523865215793751</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02599444361406682</v>
+        <v>0.00968217907686196</v>
       </c>
       <c r="H8" t="n">
-        <v>0.026025135067872</v>
+        <v>0.0096982924819707</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02591707349158309</v>
+        <v>0.009688561439639955</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02604860578980714</v>
+        <v>0.00972065438653451</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01902643626572581</v>
+        <v>0.008446411780869226</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03315312371025958</v>
+        <v>0.01093272490929716</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01843300698832429</v>
+        <v>0.008333188463023706</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02121748388324535</v>
+        <v>0.008822578203368287</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02125009275495459</v>
+        <v>0.008856354513026122</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0243564714490697</v>
+        <v>0.009413930640906424</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02114392971581776</v>
+        <v>0.008848523298917801</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02122125771663746</v>
+        <v>0.008842098363466467</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02125194917042918</v>
+        <v>0.008858211768572854</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02114388759415378</v>
+        <v>0.008848480726244459</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02127407424021622</v>
+        <v>0.008880336838359849</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01772213938691548</v>
+        <v>0.008549920213348517</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02122756377369046</v>
+        <v>0.008833826371834112</v>
       </c>
     </row>
   </sheetData>
@@ -4502,7 +4502,7 @@
         <v>0.01096403077992042</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01172253193172641</v>
+        <v>0.0117225319317264</v>
       </c>
       <c r="L2" t="n">
         <v>0.01070361578406229</v>
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009099218897455075</v>
+        <v>0.006685197218203302</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008936065874983745</v>
+        <v>0.006659323000858097</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009129117237307112</v>
+        <v>0.006715095558055337</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009110389030826265</v>
+        <v>0.006710635420250787</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009110389030826267</v>
+        <v>0.006710635420250788</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009105223651576934</v>
+        <v>0.006702407909534558</v>
       </c>
       <c r="H4" t="n">
-        <v>0.009132040239819686</v>
+        <v>0.006718018560567912</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009035658206775826</v>
+        <v>0.006697450898432193</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009152994671435724</v>
+        <v>0.006738972992183947</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009108261984639493</v>
+        <v>0.00669424030538772</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009112859370176982</v>
+        <v>0.006698837690925207</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01500308315496654</v>
+        <v>0.007724277321894957</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01957791253613217</v>
+        <v>0.008532288003071362</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02175072965563137</v>
+        <v>0.0089364993316435</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02163874907166319</v>
+        <v>0.00891562677549006</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02163874907166319</v>
+        <v>0.00891562677549006</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02102121173773953</v>
+        <v>0.008799621801335169</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02350327732417707</v>
+        <v>0.009247356273709345</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02163871036188524</v>
+        <v>0.008915588065712276</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02463663308949657</v>
+        <v>0.009464093338996298</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01987190979053072</v>
+        <v>0.008588642308959563</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02174203101932523</v>
+        <v>0.008921571889131188</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01411137882498258</v>
+        <v>0.006909973148334733</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01032958535131599</v>
+        <v>0.006904582427363615</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01039782293730864</v>
+        <v>0.006938387760045675</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01017977967162066</v>
+        <v>0.006898848172010748</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01032219946952039</v>
+        <v>0.006923914056305277</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01411738357910444</v>
+        <v>0.007584548051999433</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01431537689238329</v>
+        <v>0.007630285806475894</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01031279418035199</v>
+        <v>0.007579591040897064</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01415652857792455</v>
+        <v>0.006982946541432527</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01038443960140185</v>
+        <v>0.006918847564720837</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01038301655609935</v>
+        <v>0.006922385354436137</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01215334098521699</v>
+        <v>0.00722272270273676</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01215825984546324</v>
+        <v>0.007226429136589568</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01218313121691786</v>
+        <v>0.007252602015554292</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01210626364336378</v>
+        <v>0.0072379093492003</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01210626364336378</v>
+        <v>0.0072379093492003</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01215934573933885</v>
+        <v>0.007239933394068016</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0121861623275816</v>
+        <v>0.007255544045101371</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01208978029453775</v>
+        <v>0.007234976382965653</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01220711675919764</v>
+        <v>0.007276498476717404</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01216238407240141</v>
+        <v>0.007231765789921177</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01216698145793889</v>
+        <v>0.007236363175458667</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01905856170441158</v>
+        <v>0.008438041542729681</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02587860271564005</v>
+        <v>0.009641209468655943</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02729599205587133</v>
+        <v>0.009912465508797362</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02394914601066814</v>
+        <v>0.009322256634551612</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01922039830724799</v>
+        <v>0.008489997043259354</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02586250220804857</v>
+        <v>0.009651688919492588</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02588931879630686</v>
+        <v>0.009667299570528672</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0257929367632475</v>
+        <v>0.009646731908390212</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02591160921696278</v>
+        <v>0.009688489136214446</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01894132964497882</v>
+        <v>0.008424860204229896</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03297115025113038</v>
+        <v>0.01089789686321996</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01796360916438484</v>
+        <v>0.008245329896729194</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02062453807205675</v>
+        <v>0.008716494096395952</v>
       </c>
       <c r="D9" t="n">
-        <v>0.020649518537628</v>
+        <v>0.008742686175925092</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02362107669673916</v>
+        <v>0.009264516435612977</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02055609666796435</v>
+        <v>0.008725079953471614</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02062562396593234</v>
+        <v>0.008729998353874403</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02065244055417509</v>
+        <v>0.008745609004907751</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02055605852113124</v>
+        <v>0.008725041342772031</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02067339498579112</v>
+        <v>0.008766563436523789</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01902732481354169</v>
+        <v>0.008439995353814945</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02063325968453239</v>
+        <v>0.008726428135265047</v>
       </c>
     </row>
   </sheetData>
@@ -4871,13 +4871,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01304932556171991</v>
+        <v>0.01304932556171992</v>
       </c>
       <c r="C2" t="n">
         <v>0.01108130526518838</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01534257323846126</v>
+        <v>0.01534257323846125</v>
       </c>
       <c r="E2" t="n">
         <v>0.01120434614474347</v>
@@ -4889,13 +4889,13 @@
         <v>0.01415801885687847</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01428629671304138</v>
+        <v>0.01428629671304139</v>
       </c>
       <c r="I2" t="n">
         <v>0.01151403044469169</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01393884008495435</v>
+        <v>0.01393884008495434</v>
       </c>
       <c r="K2" t="n">
         <v>0.01343852423332604</v>
@@ -4929,10 +4929,10 @@
         <v>0.01550002435981333</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01564809870010938</v>
+        <v>0.0156480987001094</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01245719332539074</v>
+        <v>0.01245719332539075</v>
       </c>
       <c r="J3" t="n">
         <v>0.01525569115154251</v>
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01119852576203042</v>
+        <v>0.008243684122137329</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009863656296878276</v>
+        <v>0.007256661305895386</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01256176433270611</v>
+        <v>0.009606922692813031</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009925514776256639</v>
+        <v>0.007267549289652332</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009925514776256642</v>
+        <v>0.007267549289652332</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01183290722747307</v>
+        <v>0.008898409916231781</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01193392703138933</v>
+        <v>0.008979085391496252</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01012102205128597</v>
+        <v>0.007301617651559437</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01175804611580383</v>
+        <v>0.008803204475910747</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01070783295649504</v>
+        <v>0.007752991316601955</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01575578358317137</v>
+        <v>0.0128009419432783</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.146727423085721</v>
+        <v>0.03209676992185646</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0605415146804295</v>
+        <v>0.01617596433307024</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2820017645727669</v>
+        <v>0.05702836247810567</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06054151576228055</v>
+        <v>0.01617596541492137</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06054151576228054</v>
+        <v>0.01617596541492137</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2187291869638541</v>
+        <v>0.04531215495252314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2489768164370778</v>
+        <v>0.05069863370083591</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06054110202646602</v>
+        <v>0.01617555167910678</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2168375242650333</v>
+        <v>0.04489719243459604</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1027567510390516</v>
+        <v>0.02395360081134719</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2363295184409832</v>
+        <v>0.05162191906789766</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01812336708327626</v>
+        <v>0.009462456188072555</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01165585949693931</v>
+        <v>0.00757208906739695</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01461418813239303</v>
+        <v>0.009968149279600583</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01151150230952612</v>
+        <v>0.007546683093995248</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01189552093547152</v>
+        <v>0.007614270371795411</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01363314325955535</v>
+        <v>0.01011718198216701</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01378725603812717</v>
+        <v>0.01022291856219195</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01704586337253183</v>
+        <v>0.008520389717494662</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01872992104374529</v>
+        <v>0.01003025445657955</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01238801950986195</v>
+        <v>0.008048704148392179</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0178109276349418</v>
+        <v>0.01316264729442995</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01527439641619035</v>
+        <v>0.008961037353382429</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01419730535940936</v>
+        <v>0.008019383536767968</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01663749681154914</v>
+        <v>0.01032425160520249</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01419252256112291</v>
+        <v>0.00801854265571946</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01419252256112291</v>
+        <v>0.00801854265571946</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01590877788163302</v>
+        <v>0.009615763147476879</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01600979768554928</v>
+        <v>0.009696438622741346</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01419689270544591</v>
+        <v>0.008018970882804528</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01583391676996378</v>
+        <v>0.00952055770715584</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01478370361065499</v>
+        <v>0.008470344547847054</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01983165423733133</v>
+        <v>0.01351829517452339</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02327547445382002</v>
+        <v>0.01036922708037482</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03053001951616943</v>
+        <v>0.01089394121278166</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03470131121131779</v>
+        <v>0.01350348292233478</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02825089990101113</v>
+        <v>0.01049281705413267</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02245980086045936</v>
+        <v>0.009473583628518387</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03224426093292877</v>
+        <v>0.0124908081489262</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03234528073684439</v>
+        <v>0.01257148362419055</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03053237575674173</v>
+        <v>0.01089401588425387</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03217103777026434</v>
+        <v>0.01239589098762845</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02262996579630563</v>
+        <v>0.009851286685038794</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04487312023664326</v>
+        <v>0.01792559316652088</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0264115183343908</v>
+        <v>0.01092117080036451</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02982929172766072</v>
+        <v>0.01077061312267237</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03226962519098851</v>
+        <v>0.01307550618507584</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03501626985328934</v>
+        <v>0.01168352215928167</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02982928905542693</v>
+        <v>0.01077061354380458</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03154076424988436</v>
+        <v>0.01236699273338128</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03164178405380062</v>
+        <v>0.01244766820864576</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02982887907369729</v>
+        <v>0.01077020046870895</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03146590313821513</v>
+        <v>0.01227178729306026</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02781134947720443</v>
+        <v>0.01076321020793563</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03546364060558266</v>
+        <v>0.01626952476042781</v>
       </c>
     </row>
   </sheetData>
@@ -5267,22 +5267,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01253021595865393</v>
+        <v>0.01253021595865395</v>
       </c>
       <c r="C2" t="n">
         <v>0.01143778305035927</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01505295823272893</v>
+        <v>0.01505295823272891</v>
       </c>
       <c r="E2" t="n">
         <v>0.01155876186387157</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01111986433076437</v>
+        <v>0.01111986433076436</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01397440498756907</v>
+        <v>0.01397440498756906</v>
       </c>
       <c r="H2" t="n">
         <v>0.0139150891155275</v>
@@ -5291,13 +5291,13 @@
         <v>0.01186508127884262</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01297087146792541</v>
+        <v>0.0129708714679254</v>
       </c>
       <c r="K2" t="n">
         <v>0.01341722255797045</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02007161123010976</v>
+        <v>0.02007161123010975</v>
       </c>
     </row>
     <row r="3">
@@ -5307,13 +5307,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01365965467099436</v>
+        <v>0.01365965467099438</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01246680606868932</v>
+        <v>0.01246680606868931</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01656133087066833</v>
+        <v>0.0165613308706683</v>
       </c>
       <c r="E3" t="n">
         <v>0.01258829265011114</v>
@@ -5322,22 +5322,22 @@
         <v>0.01214939511700393</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01532077121710286</v>
+        <v>0.01532077121710285</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0152530470816295</v>
+        <v>0.01525304708162949</v>
       </c>
       <c r="I3" t="n">
         <v>0.01289321988178325</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01417609996513263</v>
+        <v>0.01417609996513262</v>
       </c>
       <c r="K3" t="n">
         <v>0.0144974947627242</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02233356833625252</v>
+        <v>0.02233356833625254</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01084556705371994</v>
+        <v>0.007928842574451988</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01008944297738357</v>
+        <v>0.00746995913182611</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01234523043799949</v>
+        <v>0.00942850595873152</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01014502107520497</v>
+        <v>0.007479741700414103</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01014502107520497</v>
+        <v>0.007479741700414103</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01168135590127049</v>
+        <v>0.008783352977783432</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0116689321981592</v>
+        <v>0.008752207718891241</v>
       </c>
       <c r="I4" t="n">
-        <v>0.010298257328336</v>
+        <v>0.007506431634965854</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01114551160233091</v>
+        <v>0.008228787123062938</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01065098639946977</v>
+        <v>0.007734261920201808</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01532750003452182</v>
+        <v>0.01241077555525388</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1122489214581658</v>
+        <v>0.02577583285292865</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07457239971308084</v>
+        <v>0.01881895945581311</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2446683827354547</v>
+        <v>0.0503173805415228</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07457240071238233</v>
+        <v>0.01881896045511459</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07457240071238233</v>
+        <v>0.01881896045511459</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1926070655488382</v>
+        <v>0.04062627770321108</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2109936708248639</v>
+        <v>0.04383336152710037</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07457206133634736</v>
+        <v>0.01881862107907959</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1485598281545391</v>
+        <v>0.03241370670520304</v>
       </c>
       <c r="K5" t="n">
-        <v>0.09124394661050846</v>
+        <v>0.02191862284048519</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6096490527176303</v>
+        <v>0.05387310004853713</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01257414669686279</v>
+        <v>0.009074796799491448</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01182299026336522</v>
+        <v>0.007775063452505638</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0142777591682251</v>
+        <v>0.009768631013408226</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01168545737455587</v>
+        <v>0.007750858487630789</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01200771431247442</v>
+        <v>0.007807575708397124</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01340993554441334</v>
+        <v>0.009929307202822894</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01829779229331088</v>
+        <v>0.009918887089316158</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01202683697147885</v>
+        <v>0.008652385860005312</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01303874784297063</v>
+        <v>0.009380853257483938</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01227660295110579</v>
+        <v>0.00802037043173944</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01743714539936266</v>
+        <v>0.01278207313745395</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01456970113108582</v>
+        <v>0.008584290168516775</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01402272978243539</v>
+        <v>0.008162217605764155</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01606923630796645</v>
+        <v>0.01008393098829422</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01401620692148945</v>
+        <v>0.008161070405668325</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01401620692148945</v>
+        <v>0.008161070405668325</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01540548997863637</v>
+        <v>0.009438800571848226</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01539306627552508</v>
+        <v>0.00940765531295602</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01402239140570188</v>
+        <v>0.008161879229030642</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01486964567969678</v>
+        <v>0.008884234717127721</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01437512047683565</v>
+        <v>0.008389709514266592</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0190516341118877</v>
+        <v>0.01306622314931866</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02193905201501471</v>
+        <v>0.009881295917060291</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02903511535476736</v>
+        <v>0.0108043974521817</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03267211389709757</v>
+        <v>0.01300603742814754</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02694402175432124</v>
+        <v>0.01043636580391778</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02163068395387647</v>
+        <v>0.009501218356106702</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0304224564489666</v>
+        <v>0.01208178665630506</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03041003274585531</v>
+        <v>0.01205064139741283</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02903935787603224</v>
+        <v>0.01080486531348749</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02988811512531219</v>
+        <v>0.0115274853252333</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02160241297498777</v>
+        <v>0.009661712987048878</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04205717454514025</v>
+        <v>0.01711519824363131</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02400311860603574</v>
+        <v>0.01024457163511155</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02735562379992139</v>
+        <v>0.01050880694012645</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02940226197337467</v>
+        <v>0.0124305434926907</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03185553736270576</v>
+        <v>0.01130079254630948</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02735562176361842</v>
+        <v>0.01050880740516156</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02873838399612237</v>
+        <v>0.01178538990621053</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02872596029301113</v>
+        <v>0.01175424464731831</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0273552854231879</v>
+        <v>0.01050846856339293</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02820253969718277</v>
+        <v>0.01123082405149002</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02279787658145826</v>
+        <v>0.009872114580647604</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03238452812937368</v>
+        <v>0.01541281248368097</v>
       </c>
     </row>
   </sheetData>
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01223431946884176</v>
+        <v>0.01223431946884175</v>
       </c>
       <c r="C2" t="n">
         <v>0.01201473319210535</v>
@@ -5672,16 +5672,16 @@
         <v>0.01432722610632336</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01211038271108612</v>
+        <v>0.01211038271108613</v>
       </c>
       <c r="F2" t="n">
         <v>0.01174899598331298</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01352500499289342</v>
+        <v>0.01352500499289341</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01375085736760866</v>
+        <v>0.01375085736760865</v>
       </c>
       <c r="I2" t="n">
         <v>0.01247189338317091</v>
@@ -5693,7 +5693,7 @@
         <v>0.01321635294826604</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01896964901551008</v>
+        <v>0.01896964901551012</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01327813832116871</v>
+        <v>0.0132781383211687</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01309381626597536</v>
+        <v>0.01309381626597537</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01568541449857641</v>
+        <v>0.01568541449857642</v>
       </c>
       <c r="E3" t="n">
         <v>0.01318991464652828</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01282852791875514</v>
+        <v>0.01282852791875515</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01476269403852894</v>
+        <v>0.01476269403852896</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01502291580505651</v>
+        <v>0.0150229158050565</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01355064202172683</v>
+        <v>0.01355064202172685</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01312272465282531</v>
+        <v>0.0131227246528253</v>
       </c>
       <c r="K3" t="n">
         <v>0.01422509021226992</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02102492806098282</v>
+        <v>0.02102492806098279</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01073425067095906</v>
+        <v>0.007768348131354499</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01058322271671744</v>
+        <v>0.007858228628864948</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01197839498296481</v>
+        <v>0.009012492443360238</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01063579647011301</v>
+        <v>0.007867482356117924</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01063579647011301</v>
+        <v>0.00786748235611792</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01148193667699685</v>
+        <v>0.00853216133936035</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01163581722611649</v>
+        <v>0.008669914686511921</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01074420255678982</v>
+        <v>0.007886402629941626</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01074472253427861</v>
+        <v>0.007778819994674036</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01059541228802111</v>
+        <v>0.007629509748416538</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01473714398073865</v>
+        <v>0.01177124144113405</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09489854250489969</v>
+        <v>0.02258126341386269</v>
       </c>
       <c r="C5" t="n">
-        <v>0.104836825571121</v>
+        <v>0.02444686264135274</v>
       </c>
       <c r="D5" t="n">
-        <v>0.20079301891733</v>
+        <v>0.04224386607574079</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1048368264773169</v>
+        <v>0.02444686354754873</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1048368264773169</v>
+        <v>0.02444686354754873</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1653829523392796</v>
+        <v>0.03561873994915047</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1942920047825973</v>
+        <v>0.04081740352225806</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1048366332766763</v>
+        <v>0.02444667034690802</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1046806448416455</v>
+        <v>0.02431154223118628</v>
       </c>
       <c r="K5" t="n">
-        <v>0.07854640305119059</v>
+        <v>0.01958888405793128</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5328641497523443</v>
+        <v>0.1029615939628124</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01247467476594479</v>
+        <v>0.008074662770412178</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01238451540882825</v>
+        <v>0.008175256140958608</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01835462819326414</v>
+        <v>0.01013470948229207</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01224514760977049</v>
+        <v>0.008150728155162854</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01249206422199031</v>
+        <v>0.00819418547867806</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01322236077198256</v>
+        <v>0.008838475978418036</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01808853160143052</v>
+        <v>0.0098055924104134</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01707709712221786</v>
+        <v>0.009000992067417442</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01710650810292202</v>
+        <v>0.008112469374371184</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01224218933676941</v>
+        <v>0.007919342507425743</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01661882472307278</v>
+        <v>0.01210241724999038</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0143923616197864</v>
+        <v>0.008412175654859457</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01440250580006177</v>
+        <v>0.008530422447891211</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01563637555351656</v>
+        <v>0.009656297020288829</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01439549566106313</v>
+        <v>0.00852918941013962</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01439549566106313</v>
+        <v>0.00852918941013962</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01514004762582417</v>
+        <v>0.009175988862865301</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01529392817494383</v>
+        <v>0.00931374221001688</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01440231350561714</v>
+        <v>0.00853023015344659</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01440283348310594</v>
+        <v>0.008422647518178996</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01425352323684843</v>
+        <v>0.0082733372719215</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01839525492956599</v>
+        <v>0.01241506896463906</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0216620367779148</v>
+        <v>0.009691638475757148</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02919103548951805</v>
+        <v>0.01113320365913205</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03199023763236817</v>
+        <v>0.01253457673057043</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02713382129264383</v>
+        <v>0.01077113470914961</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02190657393035863</v>
+        <v>0.009851139178372516</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02993364503406229</v>
+        <v>0.01177966199260693</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03008752558318243</v>
+        <v>0.01191741533975859</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02919591091385521</v>
+        <v>0.01113390328318821</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02919790955740546</v>
+        <v>0.01102658089314602</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02138343767641957</v>
+        <v>0.009528202206486397</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04104821826796129</v>
+        <v>0.01640199049059305</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02289761731001331</v>
+        <v>0.009909100648228145</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02652427898209883</v>
+        <v>0.0106638545163695</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02775828161486503</v>
+        <v>0.01178975247552579</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03069766320977617</v>
+        <v>0.01139837088316616</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02652427713437986</v>
+        <v>0.01066385493787646</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02726182080786127</v>
+        <v>0.01130942093134361</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02741570135698089</v>
+        <v>0.01144717427849519</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02652408668765424</v>
+        <v>0.01066366222192488</v>
       </c>
       <c r="J9" t="n">
-        <v>0.026524606665143</v>
+        <v>0.0105560795866573</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0242798730328965</v>
+        <v>0.01003797482646409</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03051702811160308</v>
+        <v>0.01454850103311735</v>
       </c>
     </row>
   </sheetData>
@@ -6071,25 +6071,25 @@
         <v>0.0105707978550061</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01015593143385692</v>
+        <v>0.01015593143385691</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01165048725449469</v>
+        <v>0.01165048725449468</v>
       </c>
       <c r="H2" t="n">
         <v>0.0118017009204923</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01089012113826708</v>
+        <v>0.01089012113826707</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01185825687781418</v>
+        <v>0.01185825687781417</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01249637197738333</v>
+        <v>0.01249637197738332</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02015775435914465</v>
+        <v>0.02015775435914466</v>
       </c>
     </row>
     <row r="3">
@@ -6105,7 +6105,7 @@
         <v>0.01130409087450329</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01289794653166496</v>
+        <v>0.01289794653166495</v>
       </c>
       <c r="E3" t="n">
         <v>0.01141675012397378</v>
@@ -6123,13 +6123,13 @@
         <v>0.01173547254505786</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01286445679657014</v>
+        <v>0.01286445679657013</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01340322237916932</v>
+        <v>0.01340322237916931</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02239532260736857</v>
+        <v>0.02239532260736858</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009578773343405053</v>
+        <v>0.00695952348765451</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009193460899877642</v>
+        <v>0.006846224153244898</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0101239421195732</v>
+        <v>0.007504692263822657</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009247182283417426</v>
+        <v>0.006855679968392449</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009247182283417425</v>
+        <v>0.006855679968392449</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009954658063702536</v>
+        <v>0.007352534715877324</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01006539075954982</v>
+        <v>0.007446140903799275</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009383912305109526</v>
+        <v>0.006879616468928208</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01015776869419351</v>
+        <v>0.007538518838442971</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009764584492989486</v>
+        <v>0.007145334637238942</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01503089644773212</v>
+        <v>0.01241164659198158</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03916140365894782</v>
+        <v>0.01216606639497785</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0342503328102006</v>
+        <v>0.01125623358556565</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08629731188128682</v>
+        <v>0.02091120526923967</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03425033384381198</v>
+        <v>0.01125623461917702</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03425033384381198</v>
+        <v>0.01125623461917702</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07650610752446917</v>
+        <v>0.01906558975750386</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0899679210781303</v>
+        <v>0.02150898616366845</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03425017852445338</v>
+        <v>0.0112560792998184</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1011087650164929</v>
+        <v>0.02354589410442999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05560674509067708</v>
+        <v>0.01521355485871345</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1118085464135337</v>
+        <v>0.1222331581089945</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01103772543379632</v>
+        <v>0.007216299054172008</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01072752467785618</v>
+        <v>0.007116219376706119</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01163983613732828</v>
+        <v>0.008545409975368306</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01059994175229237</v>
+        <v>0.007093765633624346</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01082638155184333</v>
+        <v>0.007133619038129362</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01582626985266449</v>
+        <v>0.00760931028239482</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01605532589206825</v>
+        <v>0.008500369481410076</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01525552409407148</v>
+        <v>0.007136392035445702</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01605900219094871</v>
+        <v>0.008577135928244033</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01119994783204385</v>
+        <v>0.007397958583543637</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01673979917558051</v>
+        <v>0.01271241347045315</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01306017575247724</v>
+        <v>0.007572250308331092</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01286546899992896</v>
+        <v>0.007492497575352032</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01360521450417094</v>
+        <v>0.008117396200191862</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01285947467080996</v>
+        <v>0.007491443425128587</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01285947467080996</v>
+        <v>0.007491443425128587</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01343606047277473</v>
+        <v>0.007965261536553907</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01354679316862202</v>
+        <v>0.008058867724475859</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01286531471418172</v>
+        <v>0.007492343289604788</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01363917110326571</v>
+        <v>0.008151245659119552</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01324598690206168</v>
+        <v>0.007758061457915522</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01851229885680431</v>
+        <v>0.01302437341265816</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02054532304828253</v>
+        <v>0.008889636225254427</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02785311669153066</v>
+        <v>0.01013032355477694</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03015363421317433</v>
+        <v>0.01102991805319466</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02580053680418254</v>
+        <v>0.009769070348260606</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02058506599886219</v>
+        <v>0.00885114749149808</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02842780775017553</v>
+        <v>0.0106038090430792</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02853854044602264</v>
+        <v>0.01069741523100113</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02785706199158252</v>
+        <v>0.01013089079613009</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02863239364260412</v>
+        <v>0.01079005281174447</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0205916952493194</v>
+        <v>0.00905090612002747</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04134531750662157</v>
+        <v>0.01704298467325074</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0213885855712512</v>
+        <v>0.009038050428492716</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02469436051790477</v>
+        <v>0.009574382471234854</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02543423722418312</v>
+        <v>0.01019930418763296</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02873384155447431</v>
+        <v>0.01028533198151454</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0246943593753479</v>
+        <v>0.009574383121840632</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0252649519907505</v>
+        <v>0.01004714643243673</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02537568468659779</v>
+        <v>0.01014075262035868</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0246942062321575</v>
+        <v>0.009574228185487614</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02546806262124145</v>
+        <v>0.01023313055500237</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02066714682177054</v>
+        <v>0.009482984502362783</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03034119037478011</v>
+        <v>0.01510625830854096</v>
       </c>
     </row>
   </sheetData>
@@ -6455,19 +6455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01076560097037802</v>
+        <v>0.01076560097037803</v>
       </c>
       <c r="C2" t="n">
         <v>0.01047899637512499</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01083550387510363</v>
+        <v>0.01083550387510364</v>
       </c>
       <c r="E2" t="n">
         <v>0.01058858455687268</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01018239510713029</v>
+        <v>0.01018239510713028</v>
       </c>
       <c r="G2" t="n">
         <v>0.01098019796047418</v>
@@ -6476,13 +6476,13 @@
         <v>0.01075596791210609</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01090821056394084</v>
+        <v>0.01090821056394085</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0111314354710738</v>
+        <v>0.01113143547107381</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01223075488704295</v>
+        <v>0.01223075488704294</v>
       </c>
       <c r="L2" t="n">
         <v>0.01061928362880106</v>
@@ -6495,22 +6495,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01161052620440991</v>
+        <v>0.01161052620440992</v>
       </c>
       <c r="C3" t="n">
         <v>0.01134503601241642</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01169092902518746</v>
+        <v>0.01169092902518747</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01145498417262639</v>
+        <v>0.0114549841726264</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01104879472288399</v>
+        <v>0.011048794722884</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01185735719665307</v>
+        <v>0.01185735719665309</v>
       </c>
       <c r="H3" t="n">
         <v>0.01159984326988105</v>
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009298525911162526</v>
+        <v>0.006807473655318206</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009129924892174464</v>
+        <v>0.006847828191011251</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009340080225984558</v>
+        <v>0.006849027970140248</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009174421971022906</v>
+        <v>0.006855660403099943</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009174421971022906</v>
+        <v>0.006855660403099943</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009407648454911838</v>
+        <v>0.006931795928545537</v>
       </c>
       <c r="H4" t="n">
-        <v>0.009292941061927313</v>
+        <v>0.006801888806083003</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009259067844936434</v>
+        <v>0.006870508968657384</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009582952642459197</v>
+        <v>0.007091900386614881</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009459117466737124</v>
+        <v>0.006968065210892812</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009211805542125558</v>
+        <v>0.006720753286281245</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02803515598704033</v>
+        <v>0.01010512053080407</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0351788579747086</v>
+        <v>0.01143244038869505</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03140674518557384</v>
+        <v>0.01073276098198354</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03517885885608458</v>
+        <v>0.01143244127007103</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03517885885608458</v>
+        <v>0.01143244127007103</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03905084700527885</v>
+        <v>0.01214899884514015</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02965110471252771</v>
+        <v>0.01038492558917361</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03517879925879022</v>
+        <v>0.01143238167277667</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05460699776951673</v>
+        <v>0.01501613228603873</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04112647166596041</v>
+        <v>0.01254151951975576</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0406960494671522</v>
+        <v>0.01226198018706021</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01062557384133549</v>
+        <v>0.007711424471134551</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01053819450734486</v>
+        <v>0.007095683641938211</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01065419449896841</v>
+        <v>0.007080309865095656</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01041942351040383</v>
+        <v>0.007074780672843659</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01058012537982584</v>
+        <v>0.007103064201708676</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0107346963850848</v>
+        <v>0.007165356362990409</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01450282760575184</v>
+        <v>0.007033523882949256</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01058611577510941</v>
+        <v>0.007104069403102253</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01102568444185641</v>
+        <v>0.007997132695195319</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0107940137167277</v>
+        <v>0.007203006949618096</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01075837739505556</v>
+        <v>0.006992949930921998</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0123697192541477</v>
+        <v>0.007348003680754681</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01233031990384</v>
+        <v>0.007411097710012254</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01241115130924768</v>
+        <v>0.007389536477865757</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01232531296871751</v>
+        <v>0.00741021721568927</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01232531296871751</v>
+        <v>0.00741021721568927</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01247884179789702</v>
+        <v>0.007472325953982012</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01236413440491249</v>
+        <v>0.007342418831519475</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01233026118792161</v>
+        <v>0.007411038994093857</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01265414598544437</v>
+        <v>0.00763243041205135</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0125303108097223</v>
+        <v>0.007508595236329283</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01228299888511074</v>
+        <v>0.007261283311717718</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01914626586817872</v>
+        <v>0.00854067587836152</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02582181794258313</v>
+        <v>0.009785601351964553</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02729916948578354</v>
+        <v>0.01000982766273774</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02398475821204142</v>
+        <v>0.009462279567394965</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01931691177183911</v>
+        <v>0.008640738598370962</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02597366027783447</v>
+        <v>0.009847413993581335</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02585895288484917</v>
+        <v>0.009717506871118664</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02582507966785901</v>
+        <v>0.009786127033693177</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02615028479847277</v>
+        <v>0.01000775083027342</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01918206207466411</v>
+        <v>0.008679303452615443</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03279561410190003</v>
+        <v>0.01087150357031028</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01899624600423996</v>
+        <v>0.008514272382451371</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02183950834044035</v>
+        <v>0.009084714865785241</v>
       </c>
       <c r="D9" t="n">
-        <v>0.021920463292476</v>
+        <v>0.009063175377845152</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02516604005775561</v>
+        <v>0.0096701851711141</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0218395085887559</v>
+        <v>0.009084715635742579</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02198803023449737</v>
+        <v>0.009145943109755006</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02187332284151286</v>
+        <v>0.009016035987292469</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02183944962452198</v>
+        <v>0.00908465614986685</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02216333442204473</v>
+        <v>0.009306047567824346</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02030151109665298</v>
+        <v>0.008876326479417886</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0217921873217111</v>
+        <v>0.00893490046749071</v>
       </c>
     </row>
   </sheetData>
@@ -6906,7 +6906,7 @@
         <v>0.01111290196196076</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01179396189193213</v>
+        <v>0.01179396189193214</v>
       </c>
       <c r="H3" t="n">
         <v>0.0115623547093407</v>
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009381684770377659</v>
+        <v>0.006890431718400894</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00920174299763908</v>
+        <v>0.006899174292659013</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00930103838847938</v>
+        <v>0.006809785336502626</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009244807076152458</v>
+        <v>0.006906754233663091</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009244807076152458</v>
+        <v>0.006906754233663092</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009389385020966269</v>
+        <v>0.0069123269934609</v>
       </c>
       <c r="H4" t="n">
-        <v>0.009286849495161757</v>
+        <v>0.006795596443184978</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009314369039501566</v>
+        <v>0.0069189622550655</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009515141029254721</v>
+        <v>0.007023887977277951</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009419051938966892</v>
+        <v>0.006927798886990098</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009266411365997668</v>
+        <v>0.006775158314020892</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03523533577182908</v>
+        <v>0.01144067427000038</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03939091102769362</v>
+        <v>0.01221246783715787</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02834379488979211</v>
+        <v>0.01016131046257308</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03939091183258055</v>
+        <v>0.0122124686420448</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03939091183258055</v>
+        <v>0.0122124686420448</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03777110376601878</v>
+        <v>0.01190750946552332</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02916635038062408</v>
+        <v>0.01029438858006778</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03939086949753125</v>
+        <v>0.01221242630699555</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04892645103269305</v>
+        <v>0.01396027850029754</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03742339588005533</v>
+        <v>0.01185656339391464</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03883173612918652</v>
+        <v>0.00999133347813305</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0107262647274703</v>
+        <v>0.007127077789566904</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01062031933459013</v>
+        <v>0.007148843726609544</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01437931854749647</v>
+        <v>0.007041350515571318</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01050077327175672</v>
+        <v>0.007127804282891652</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01065366496928355</v>
+        <v>0.00715471322151057</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01073396497805884</v>
+        <v>0.00780731469333816</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01442861672702681</v>
+        <v>0.007700547471089659</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0106589489965942</v>
+        <v>0.007155608326231513</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01097064801075413</v>
+        <v>0.007917479076250853</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01076557833114711</v>
+        <v>0.00716478753072967</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01060423123553177</v>
+        <v>0.007010614609783049</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01243915777793906</v>
+        <v>0.007428546964815864</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01237188357722541</v>
+        <v>0.007457119031642928</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01235838813225683</v>
+        <v>0.007347878888491747</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01236683131371546</v>
+        <v>0.007456230496496783</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01236683131371546</v>
+        <v>0.007456230496496783</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01244685802852768</v>
+        <v>0.007450442239875871</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01234432250272317</v>
+        <v>0.007333711689599949</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01237184204706295</v>
+        <v>0.007457077501480471</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01257261403681612</v>
+        <v>0.00756200322369292</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01247652494652821</v>
+        <v>0.007465914133405071</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01232388437355907</v>
+        <v>0.00731327356043586</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01919754867458134</v>
+        <v>0.008618023756179597</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02581990506705645</v>
+        <v>0.009823970801030958</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02719773621397525</v>
+        <v>0.009959604136722268</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02398976164192419</v>
+        <v>0.009501866223177025</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01933949209140216</v>
+        <v>0.008683418786719996</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02589824625026522</v>
+        <v>0.009817886554073459</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0257957107244596</v>
+        <v>0.009701156003797323</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02582323026880056</v>
+        <v>0.009824521815678057</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02602531762454789</v>
+        <v>0.009929679042304223</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01911058998164573</v>
+        <v>0.008633509573259012</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03276666796091984</v>
+        <v>0.01091120345231562</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01866207429118262</v>
+        <v>0.008523780265212104</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02135986164257182</v>
+        <v>0.009039003162572291</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02134649064470792</v>
+        <v>0.008929784922111416</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02455068516914683</v>
+        <v>0.009600588763433279</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0213598618471708</v>
+        <v>0.009039003861808505</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02143483609387403</v>
+        <v>0.009032326370805241</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02133230056806949</v>
+        <v>0.008915595820529316</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02135982011240935</v>
+        <v>0.00903896163240984</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02156059210216244</v>
+        <v>0.009143887354622288</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01986241598705171</v>
+        <v>0.008754391170902764</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0213118624389054</v>
+        <v>0.008895157691365226</v>
       </c>
     </row>
   </sheetData>
@@ -7256,7 +7256,7 @@
         <v>0.01509424905501346</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01099315518897446</v>
+        <v>0.01099315518897447</v>
       </c>
       <c r="F2" t="n">
         <v>0.01056118415941661</v>
@@ -7277,7 +7277,7 @@
         <v>0.01311875338261397</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01933001786015712</v>
+        <v>0.01933001786015713</v>
       </c>
     </row>
     <row r="3">
@@ -7293,7 +7293,7 @@
         <v>0.01178680266184726</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01657429210496469</v>
+        <v>0.01657429210496468</v>
       </c>
       <c r="E3" t="n">
         <v>0.01190545600746164</v>
@@ -7302,13 +7302,13 @@
         <v>0.01147348497790379</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01484003664906465</v>
+        <v>0.01484003664906464</v>
       </c>
       <c r="H3" t="n">
         <v>0.01549004391536211</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01222539352602802</v>
+        <v>0.01222539352602803</v>
       </c>
       <c r="J3" t="n">
         <v>0.0137163043254632</v>
@@ -7317,7 +7317,7 @@
         <v>0.01412108481031427</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02144605370085092</v>
+        <v>0.02144605370085091</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01050642615754079</v>
+        <v>0.007647500148637596</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009648102844373885</v>
+        <v>0.007124070808957962</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01230141703731755</v>
+        <v>0.009442491028414357</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009708278801312847</v>
+        <v>0.007134662669695889</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009708278801312847</v>
+        <v>0.007134662669695887</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0113811807644404</v>
+        <v>0.008541970569044242</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01174077477092112</v>
+        <v>0.008881848762017926</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009894645697540182</v>
+        <v>0.007167164444399387</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01086703231250602</v>
+        <v>0.008008106303602824</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01041083247959529</v>
+        <v>0.007551906470692089</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01481836194709307</v>
+        <v>0.01195943593818989</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09377037290476259</v>
+        <v>0.02230195469674199</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05151922901084285</v>
+        <v>0.01449338897432507</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2586390124267088</v>
+        <v>0.0527979075820213</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05151923009382104</v>
+        <v>0.01449339005730329</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05151923009382103</v>
+        <v>0.01449339005730329</v>
       </c>
       <c r="G5" t="n">
-        <v>0.182380652882657</v>
+        <v>0.03863787749877261</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2250649969567826</v>
+        <v>0.04642691166328769</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05151886747385202</v>
+        <v>0.01449302743733433</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1386741062872557</v>
+        <v>0.03050215120127246</v>
       </c>
       <c r="K5" t="n">
-        <v>0.08543884036725864</v>
+        <v>0.0207568357873686</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6001457841515827</v>
+        <v>0.1149770616879683</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01220099281225967</v>
+        <v>0.007945743878252051</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01135557157377675</v>
+        <v>0.007424585303704496</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01427002560252194</v>
+        <v>0.009788966134012906</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0112180515667231</v>
+        <v>0.007400382674968262</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01156659021268541</v>
+        <v>0.007461725476325236</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01800633462623565</v>
+        <v>0.009707997642401968</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01853002755358311</v>
+        <v>0.0100767572452917</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01158921235225905</v>
+        <v>0.008333191517757112</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01755521009630593</v>
+        <v>0.00918522558717327</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01200100815354742</v>
+        <v>0.007831777387791157</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01674421316166753</v>
+        <v>0.01229838575011836</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01441490495590648</v>
+        <v>0.00833539241342254</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01380348603289661</v>
+        <v>0.007855418246175081</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01620976060234166</v>
+        <v>0.0101303594921313</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01379786865858103</v>
+        <v>0.007854430480674954</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01379786865858103</v>
+        <v>0.007854430480674954</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01528965956280609</v>
+        <v>0.009229862833829188</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0156492535692868</v>
+        <v>0.009569741026802869</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01380312449590586</v>
+        <v>0.007855056709184332</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0147755111108717</v>
+        <v>0.008695998568387771</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01431931127796098</v>
+        <v>0.008239798735477036</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01872684074545876</v>
+        <v>0.01264732820297483</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02227368102867153</v>
+        <v>0.009718536994734482</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02976330192187518</v>
+        <v>0.0106643458274194</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03385388045316121</v>
+        <v>0.01323572456904881</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02754710717061224</v>
+        <v>0.01027429644568015</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02191589724267929</v>
+        <v>0.009283203503734294</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03125309107750197</v>
+        <v>0.01203942676519176</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03161268508398223</v>
+        <v>0.01237930495816535</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02976655601060178</v>
+        <v>0.01066462064054691</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03074053542227804</v>
+        <v>0.01150584283196985</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02202753921498761</v>
+        <v>0.00959644684504259</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04315626256922268</v>
+        <v>0.01694690642065958</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02491731020578964</v>
+        <v>0.01018381572738611</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02856457746393347</v>
+        <v>0.0104533703239603</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03097099026702476</v>
+        <v>0.01272833589903814</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03347901026478618</v>
+        <v>0.01131831138459767</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02856457490798716</v>
+        <v>0.01045337076648781</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03005075099384294</v>
+        <v>0.0118278149116144</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03041034500032363</v>
+        <v>0.01216769310458808</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02856421592694271</v>
+        <v>0.01045300878696955</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02953660254190854</v>
+        <v>0.01129395064617298</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02651279483030094</v>
+        <v>0.01040347112597468</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03348793217649563</v>
+        <v>0.01524528028076005</v>
       </c>
     </row>
   </sheetData>
@@ -7649,7 +7649,7 @@
         <v>0.01047864801154898</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01410092503972192</v>
+        <v>0.01410092503972193</v>
       </c>
       <c r="E2" t="n">
         <v>0.01059312116403733</v>
@@ -7673,7 +7673,7 @@
         <v>0.01220508478675639</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06238118673877102</v>
+        <v>0.06238118673877097</v>
       </c>
     </row>
     <row r="3">
@@ -7683,13 +7683,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01161524645261318</v>
+        <v>0.01161524645261317</v>
       </c>
       <c r="C3" t="n">
         <v>0.01135913364282607</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01545944078333331</v>
+        <v>0.01545944078333332</v>
       </c>
       <c r="E3" t="n">
         <v>0.01147405970131919</v>
@@ -7713,7 +7713,7 @@
         <v>0.01310169151502155</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07098922958746022</v>
+        <v>0.07098922958746015</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009494331199508762</v>
+        <v>0.006831389147698159</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009273187515081603</v>
+        <v>0.006872171943562042</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01148111300530907</v>
+        <v>0.008818170953498471</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009323208419677192</v>
+        <v>0.00688097640821345</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009323208419677192</v>
+        <v>0.00688097640821345</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01031756129683193</v>
+        <v>0.007671989093756079</v>
       </c>
       <c r="H4" t="n">
-        <v>0.009732451111895354</v>
+        <v>0.007069509060084766</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009449625985417683</v>
+        <v>0.006903042755593195</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009945766720204535</v>
+        <v>0.007282824668393939</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009653068614487082</v>
+        <v>0.006990126562676491</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04017033997003271</v>
+        <v>0.03750739791822223</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0236447378597815</v>
+        <v>0.009321860706411276</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03233173832606766</v>
+        <v>0.01093047686430523</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1874838693760091</v>
+        <v>0.03979465590689231</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03233173927933253</v>
+        <v>0.01093047781757015</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03233173927933253</v>
+        <v>0.01093047781757015</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0974067042515285</v>
+        <v>0.022999678170728</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04779390989631024</v>
+        <v>0.01376832576984353</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03233151701711189</v>
+        <v>0.01093025555534951</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06766076028869776</v>
+        <v>0.01744066348140746</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03705924250440909</v>
+        <v>0.01181361314116619</v>
       </c>
       <c r="L5" t="n">
-        <v>3.192326948223122</v>
+        <v>0.04401103584543409</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01092560825577503</v>
+        <v>0.007993004371862825</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01074045524051461</v>
+        <v>0.007130411061838954</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01316890643238066</v>
+        <v>0.009115222595053386</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01061783181452698</v>
+        <v>0.007108830124472368</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01086529301070057</v>
+        <v>0.00715238329476292</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0169176478335308</v>
+        <v>0.00792389385429397</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01638719822050503</v>
+        <v>0.008240744544853606</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01604971252211655</v>
+        <v>0.008064657979757856</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01653378048941641</v>
+        <v>0.007557619267181834</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01101041893088927</v>
+        <v>0.007229020217068809</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0427870586533498</v>
+        <v>0.03796794040399044</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01281936048256064</v>
+        <v>0.007416594298344296</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01277487657742528</v>
+        <v>0.007488469215195056</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01480602000669159</v>
+        <v>0.009403354582570921</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01276877391188322</v>
+        <v>0.007487395931555767</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01276877391188323</v>
+        <v>0.007487395931555767</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01364259057988381</v>
+        <v>0.008257194244402209</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01305748039494724</v>
+        <v>0.007654714210730901</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01277465526846955</v>
+        <v>0.007488247906239327</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01327079600325641</v>
+        <v>0.007868029819040077</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01297809789753897</v>
+        <v>0.007575331713322631</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0434953692530847</v>
+        <v>0.03809260306886823</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0199260512516979</v>
+        <v>0.008667371866934991</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02702356830740824</v>
+        <v>0.009996238946086927</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03054094698949057</v>
+        <v>0.01217270171653754</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02506955326791754</v>
+        <v>0.009652333086486871</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02010452634665331</v>
+        <v>0.008778488353079379</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0278955665010292</v>
+        <v>0.01076571799293111</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02731045631609228</v>
+        <v>0.01016323795925973</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02702763118961497</v>
+        <v>0.009996771654768222</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02752517637414381</v>
+        <v>0.01037680075072221</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01995204275107714</v>
+        <v>0.008802746000894479</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06521323757815248</v>
+        <v>0.04191494787336849</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02054140797911089</v>
+        <v>0.008775674650372821</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02377755069285136</v>
+        <v>0.009424939849017076</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02580881584558037</v>
+        <v>0.01133984663972226</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02756331901300574</v>
+        <v>0.01009123585524415</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02377754709718369</v>
+        <v>0.009424940001669869</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0246452646953099</v>
+        <v>0.01019366487822423</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02406015451037331</v>
+        <v>0.009591184844552916</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02377732938389564</v>
+        <v>0.009424718540061345</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0242734701186825</v>
+        <v>0.009804500452862099</v>
       </c>
       <c r="K9" t="n">
-        <v>0.022079963831194</v>
+        <v>0.008784764944028732</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05449804336851073</v>
+        <v>0.04002907370269033</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ammonia/ammonia acidification results.xlsx
+++ b/Results/Ammonia/ammonia acidification results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01370519145606197</v>
+        <v>0.004235768894747247</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01180398953512965</v>
+        <v>0.00382364584719475</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01567779719861086</v>
+        <v>0.004339583217067023</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01193242419364211</v>
+        <v>0.003933783179384065</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01146739430805001</v>
+        <v>0.003546701698999105</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0145440429689295</v>
+        <v>0.004279915983776171</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0170962487292138</v>
+        <v>0.004413956654248839</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0122000057983928</v>
+        <v>0.004156552622777856</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01418480620657234</v>
+        <v>0.004256634592528541</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0138999583975525</v>
+        <v>0.005211147926762093</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02446037087927613</v>
+        <v>0.004807904440165377</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01496453947382713</v>
+        <v>0.00486047399501748</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01283673357618647</v>
+        <v>0.003751060903693246</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01723344470180689</v>
+        <v>0.00560107221133615</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01296567873896725</v>
+        <v>0.003930004832794484</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01250064885337515</v>
+        <v>0.003291059109657877</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01592939248119217</v>
+        <v>0.005177951605307814</v>
       </c>
       <c r="H3" t="n">
-        <v>0.018865482511363</v>
+        <v>0.00614697103931491</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01323182468165857</v>
+        <v>0.004297685013722431</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01551703866751266</v>
+        <v>0.005039659496385177</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01500264216263344</v>
+        <v>0.006171875364348662</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02733476743916072</v>
+        <v>0.008938458990379891</v>
       </c>
     </row>
     <row r="4">
@@ -595,34 +595,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008692190420483159</v>
+        <v>0.008692190420483198</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007738244084064292</v>
+        <v>0.007738244084064288</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009864820948032772</v>
+        <v>0.009864820948032779</v>
       </c>
       <c r="E4" t="n">
         <v>0.007750085765902653</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007750085765902657</v>
+        <v>0.007750085765902654</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009187203934614634</v>
+        <v>0.009187203934614648</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0107075469136177</v>
+        <v>0.01070754691361769</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00777275510957858</v>
+        <v>0.007772755109578579</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008980636831135777</v>
+        <v>0.00898063683113578</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00807217825608119</v>
+        <v>0.008072178256081192</v>
       </c>
       <c r="L4" t="n">
         <v>0.01508372799749877</v>
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04069247268031605</v>
+        <v>0.04069247268031644</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02418347271651899</v>
+        <v>0.02418347271651898</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06411072611997443</v>
+        <v>0.06411072611997459</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02418347351285698</v>
+        <v>0.024183473512857</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02418347351285698</v>
+        <v>0.024183473512857</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05215583184832509</v>
+        <v>0.05215583184832505</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08919754554157927</v>
+        <v>0.08919754554157916</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02418310606139156</v>
+        <v>0.02418310606139151</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04925911951034245</v>
+        <v>0.0492591195103426</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02969769143883297</v>
+        <v>0.0296976914388331</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05654565058485384</v>
+        <v>0.1891360860179326</v>
       </c>
     </row>
     <row r="6">
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.009059756121580144</v>
+        <v>0.009059756121580165</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008097806649529998</v>
+        <v>0.008097806649529988</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01027655073264834</v>
+        <v>0.01027655295556058</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008068853032051269</v>
+        <v>0.008068853032051272</v>
       </c>
       <c r="F6" t="n">
         <v>0.008137766997870579</v>
@@ -696,13 +696,13 @@
         <v>0.01211858749309576</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00814032081067555</v>
+        <v>0.009149786929280271</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009385596691922743</v>
+        <v>0.01036325374830739</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008418664900131717</v>
+        <v>0.008418664900131706</v>
       </c>
       <c r="L6" t="n">
         <v>0.01549869542043363</v>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.009496021632035237</v>
+        <v>0.009496021632035235</v>
       </c>
       <c r="C7" t="n">
         <v>0.008576952976258063</v>
@@ -724,22 +724,22 @@
         <v>0.01066862481231049</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008576147444639342</v>
+        <v>0.008576147444639338</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008576147444639342</v>
+        <v>0.00857614744463934</v>
       </c>
       <c r="G7" t="n">
         <v>0.009991035146166683</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01151137812516974</v>
+        <v>0.01151137812516973</v>
       </c>
       <c r="I7" t="n">
         <v>0.008576586321130619</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009784468042687821</v>
+        <v>0.009784468042687818</v>
       </c>
       <c r="K7" t="n">
         <v>0.008876009467633228</v>
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01104565752780205</v>
+        <v>0.01104565752780206</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01175251753432711</v>
+        <v>0.01175251753433258</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01418186842746349</v>
+        <v>0.01418186842746348</v>
       </c>
       <c r="E8" t="n">
         <v>0.01130776549315569</v>
@@ -770,13 +770,13 @@
         <v>0.01017767765011141</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0131670178158219</v>
+        <v>0.01316701781582189</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01468736079482488</v>
+        <v>0.01468736079482487</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01175256899078582</v>
+        <v>0.01175256899078583</v>
       </c>
       <c r="J8" t="n">
         <v>0.01296077033600104</v>
@@ -785,7 +785,7 @@
         <v>0.01039543513711599</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0207623970768574</v>
+        <v>0.02076239707685737</v>
       </c>
     </row>
     <row r="9">
@@ -795,16 +795,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01198921646367786</v>
+        <v>0.01198921646367784</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01203896674657279</v>
+        <v>0.01203896674657278</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01413066622381869</v>
+        <v>0.01413066622381868</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01315696284994241</v>
+        <v>0.01315696284994239</v>
       </c>
       <c r="F9" t="n">
         <v>0.01203896636562039</v>
@@ -813,19 +813,19 @@
         <v>0.0134530489164814</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01497339189548446</v>
+        <v>0.01497339189548445</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01203860009144535</v>
+        <v>0.01203860009144534</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01324648181300255</v>
+        <v>0.01324648181300254</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01177668586365703</v>
+        <v>0.01111810718441336</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01934957297936555</v>
+        <v>0.01934957297936554</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0106508615455486</v>
+        <v>0.003731512726685843</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01046279808303825</v>
+        <v>0.003348149684531079</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01092882065149373</v>
+        <v>0.003746141162360489</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01055151844765867</v>
+        <v>0.003423145296892166</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01021069761814161</v>
+        <v>0.00313945065633407</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01102029031688416</v>
+        <v>0.003750955029176599</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01085388835128796</v>
+        <v>0.003741333138600976</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01093984434842619</v>
+        <v>0.003746739672235228</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01085452924592964</v>
+        <v>0.003573709626722601</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01213091315563781</v>
+        <v>0.004739115102355512</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01073393690416562</v>
+        <v>0.003735112849133309</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01145474278409981</v>
+        <v>0.003524631207284798</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01130977852709899</v>
+        <v>0.002975756860390547</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01177445333499204</v>
+        <v>0.003628483344180142</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01139885935564806</v>
+        <v>0.003098702533401221</v>
       </c>
       <c r="F3" t="n">
-        <v>0.011058038526131</v>
+        <v>0.002630416358406574</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01187966239807515</v>
+        <v>0.003662927174273212</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01168864990111406</v>
+        <v>0.003600690430159077</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01178702702915767</v>
+        <v>0.003632806496192809</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01172146636933504</v>
+        <v>0.003385502142375546</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01297801203170427</v>
+        <v>0.005270109530697994</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01155032139255075</v>
+        <v>0.003555938943315706</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006741070799962355</v>
+        <v>0.006741070799962359</v>
       </c>
       <c r="C4" t="n">
-        <v>0.006871366359934354</v>
+        <v>0.006871366359934357</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006906305710320308</v>
+        <v>0.006906305710320309</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006879132051031797</v>
+        <v>0.006879132051031802</v>
       </c>
       <c r="F4" t="n">
         <v>0.006879132051031799</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006957607683761957</v>
+        <v>0.006957607683761963</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006861889904463123</v>
+        <v>0.006861889904463128</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006892275642373213</v>
+        <v>0.006892275642373216</v>
       </c>
       <c r="J4" t="n">
-        <v>0.006990619851369395</v>
+        <v>0.006990619851369397</v>
       </c>
       <c r="K4" t="n">
-        <v>0.006912108292670977</v>
+        <v>0.00691210829267098</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006790699328711645</v>
+        <v>0.006790699328711648</v>
       </c>
     </row>
     <row r="5">
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008966460674515288</v>
+        <v>0.008966460674515286</v>
       </c>
       <c r="C5" t="n">
         <v>0.01172854389294711</v>
@@ -1046,22 +1046,22 @@
         <v>0.01172854471355799</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01260672178482188</v>
+        <v>0.01260672178482183</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01141188113496298</v>
+        <v>0.01141188113496299</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01172848591186774</v>
+        <v>0.01172848591186775</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01345492239764985</v>
+        <v>0.01345492239764987</v>
       </c>
       <c r="K5" t="n">
         <v>0.01156181851670445</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01022949158302068</v>
+        <v>0.01022949158302069</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007635397552656019</v>
+        <v>0.006976672179273448</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007120694341484984</v>
+        <v>0.007120694341484981</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007805098880796091</v>
+        <v>0.007805098880796093</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007099570112786856</v>
+        <v>0.007099570112786855</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007127917637280395</v>
+        <v>0.007127917637280398</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007193209063073053</v>
+        <v>0.007851934436455621</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007773812405427525</v>
+        <v>0.007773812405427528</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007127877021684305</v>
+        <v>0.007127877021684307</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007889018082329389</v>
+        <v>0.00724691900252868</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007148396269826587</v>
+        <v>0.007148396269826663</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007026419963437899</v>
+        <v>0.0070264199634379</v>
       </c>
     </row>
     <row r="7">
@@ -1111,34 +1111,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0072850923713975</v>
+        <v>0.007285092371397504</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007436355194887713</v>
+        <v>0.007436355194887715</v>
       </c>
       <c r="D7" t="n">
         <v>0.00745030561316141</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007435401588511741</v>
+        <v>0.007435401588511742</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007435401588511741</v>
+        <v>0.007435401588511742</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007501629255197105</v>
+        <v>0.007501629255197107</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007405911475898271</v>
+        <v>0.007405911475898273</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007436297213808358</v>
+        <v>0.007436297213808361</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007534641422804539</v>
+        <v>0.007534641422804542</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007456129864106122</v>
+        <v>0.007456129864106123</v>
       </c>
       <c r="L7" t="n">
         <v>0.007334720900146792</v>
@@ -1151,34 +1151,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008480538099904816</v>
+        <v>0.00848053809990482</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00981834271113746</v>
+        <v>0.009818342711140371</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01007914036202935</v>
+        <v>0.01007914036202936</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009493720991302591</v>
+        <v>0.009493720991302598</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008668877549716092</v>
+        <v>0.008668877549716097</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009884269763934101</v>
+        <v>0.00988426976393411</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009788551984635324</v>
+        <v>0.009788551984635333</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00981893772254536</v>
+        <v>0.009818937722545365</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009917515249360374</v>
+        <v>0.00991751524936038</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008629522840061795</v>
+        <v>0.0086295228400618</v>
       </c>
       <c r="L8" t="n">
         <v>0.01095748562847193</v>
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008387809385224676</v>
+        <v>0.00838780938522468</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009030158138385178</v>
+        <v>0.009030158138385182</v>
       </c>
       <c r="D9" t="n">
         <v>0.009044130450056361</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009596861759884579</v>
+        <v>0.009596861759884584</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009030158837024209</v>
+        <v>0.00903015883702421</v>
       </c>
       <c r="G9" t="n">
         <v>0.009095432198694575</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008999714419395739</v>
+        <v>0.008999714419395743</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009030100157305826</v>
+        <v>0.009030100157305829</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009128444366302012</v>
+        <v>0.009128444366302009</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008765395785860795</v>
+        <v>0.008765395785860799</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008928523843644259</v>
+        <v>0.008928523843644258</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01145277658615315</v>
+        <v>0.004080067763402207</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01280611923764017</v>
+        <v>0.003325536295128344</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01382507383697777</v>
+        <v>0.004204917055951256</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01095137637056897</v>
+        <v>0.003422853713165743</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01095137637056897</v>
+        <v>0.003422848050184695</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01283681242306756</v>
+        <v>0.004152906820582435</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01286252483702306</v>
+        <v>0.00415307268750528</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01176011762852135</v>
+        <v>0.004096252722721213</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01419411271509437</v>
+        <v>0.004297741929978309</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01265922516188327</v>
+        <v>0.004786455297928078</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01374435192202865</v>
+        <v>0.004200500502878225</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01229965552428158</v>
+        <v>0.004239112342896161</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01401458868994183</v>
+        <v>0.003691448117312879</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01502828878262494</v>
+        <v>0.005129433167568509</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01184444927317918</v>
+        <v>0.003244160915033575</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01184444927317918</v>
+        <v>0.003244155252052536</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01389158343889306</v>
+        <v>0.004760072162258999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01392167574962207</v>
+        <v>0.004772360168441729</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01265253329670801</v>
+        <v>0.004355686325860917</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01543861977856717</v>
+        <v>0.005364954856330992</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01356347594796537</v>
+        <v>0.005516329008894818</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01493542475617767</v>
+        <v>0.00510724454344592</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007100389967753604</v>
+        <v>0.007100389967753606</v>
       </c>
       <c r="C4" t="n">
         <v>0.008505230148742507</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008510620160607218</v>
+        <v>0.00851062016060722</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007242075954449767</v>
+        <v>0.007242075954449772</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007242075954449767</v>
+        <v>0.007242075954449772</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007919479933210169</v>
+        <v>0.007919479933210171</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007938518947853744</v>
+        <v>0.007938518947853747</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007258497688006423</v>
+        <v>0.007258497688006424</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008674037244639901</v>
+        <v>0.008674037244639905</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007327443957518644</v>
+        <v>0.007327443957518645</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008462667660738343</v>
+        <v>0.008462667660738346</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01242990205404643</v>
+        <v>0.01242990205404644</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03952254337585854</v>
+        <v>0.03952254337585858</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03828248394837132</v>
+        <v>0.03828248394837134</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01638949998596068</v>
+        <v>0.01638949998596064</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01638949998596068</v>
+        <v>0.01638949998596064</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02834753475998355</v>
+        <v>0.02834753475998359</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03069840435650493</v>
+        <v>0.03069840435650492</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01638930185345798</v>
+        <v>0.01638930185345791</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04292423033887463</v>
+        <v>0.04292423033887457</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01715564385412098</v>
+        <v>0.01715564385412096</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04192075222085441</v>
+        <v>0.04192075222085435</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007410413680311988</v>
+        <v>0.008209658390963456</v>
       </c>
       <c r="C6" t="n">
         <v>0.008861564205952084</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008849484971708775</v>
+        <v>0.008849487510748348</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007520493781330785</v>
+        <v>0.007520493781330784</v>
       </c>
       <c r="F6" t="n">
         <v>0.007567794547406051</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00902874835642002</v>
+        <v>0.008229503645768547</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009084559683685671</v>
+        <v>0.009084559683685673</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008367766111216276</v>
+        <v>0.007568521400564805</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009788056514966295</v>
+        <v>0.009788056514966297</v>
       </c>
       <c r="K6" t="n">
         <v>0.007624722575039909</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008780095337864552</v>
+        <v>0.00878009533786455</v>
       </c>
     </row>
     <row r="7">
@@ -1507,34 +1507,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007763031030300347</v>
+        <v>0.007763031030300352</v>
       </c>
       <c r="C7" t="n">
         <v>0.009195709462359423</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009173240290200325</v>
+        <v>0.009173240290200332</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007921226117563549</v>
+        <v>0.007921226117563547</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007921226117563549</v>
+        <v>0.007921226117563547</v>
       </c>
       <c r="G7" t="n">
         <v>0.008582120995756913</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008601160010400484</v>
+        <v>0.008601160010400486</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007921138750553162</v>
+        <v>0.007921138750553164</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009336678307186647</v>
+        <v>0.009336678307186645</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007990085020065384</v>
+        <v>0.007990085020065386</v>
       </c>
       <c r="L7" t="n">
         <v>0.009125308723285092</v>
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009116843845827787</v>
+        <v>0.009116843845827796</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01193865088283289</v>
+        <v>0.0119386508828329</v>
       </c>
       <c r="D8" t="n">
         <v>0.01220401514552991</v>
@@ -1559,10 +1559,10 @@
         <v>0.01028439186833648</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009319123240392744</v>
+        <v>0.009319123240392748</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01132486995968506</v>
+        <v>0.01132486995968507</v>
       </c>
       <c r="H8" t="n">
         <v>0.01134390897432988</v>
@@ -1574,10 +1574,10 @@
         <v>0.01207970023680116</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009318097633560224</v>
+        <v>0.009318097633560231</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01331891763511567</v>
+        <v>0.01331891763511569</v>
       </c>
     </row>
     <row r="9">
@@ -1587,16 +1587,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009378063864891732</v>
+        <v>0.009378063864891737</v>
       </c>
       <c r="C9" t="n">
         <v>0.01148752309909711</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01146507517957266</v>
+        <v>0.01146507517957267</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01099414090003986</v>
+        <v>0.01099414090003987</v>
       </c>
       <c r="F9" t="n">
         <v>0.01021315003631805</v>
@@ -1614,10 +1614,10 @@
         <v>0.01162849194392433</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009889769336572792</v>
+        <v>0.00988976933657279</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01141712236002278</v>
+        <v>0.01141712236002279</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01120278275538452</v>
+        <v>0.003956187071382694</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01160306136235348</v>
+        <v>0.003172957550628892</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01284474011719616</v>
+        <v>0.004042600026144846</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01062825837242629</v>
+        <v>0.003334971206519454</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01062825837242629</v>
+        <v>0.003334965591576239</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01201615268683089</v>
+        <v>0.003998993115391912</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01195655339903909</v>
+        <v>0.003994832228774507</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01138581819014848</v>
+        <v>0.003965834220688398</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01292556028458009</v>
+        <v>0.004160500902728752</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01209893221118648</v>
+        <v>0.004675926594509158</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01173564256456765</v>
+        <v>0.003983322075716175</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01202168823472867</v>
+        <v>0.004055649729367648</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01263632501081214</v>
+        <v>0.003177706383208643</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01391027933125488</v>
+        <v>0.004672303001874325</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0114746980619958</v>
+        <v>0.003084375030113715</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0114746980619958</v>
+        <v>0.003084369415170504</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01295723214496571</v>
+        <v>0.004362390578930947</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0128891596400554</v>
+        <v>0.004341295088015009</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01223202509144274</v>
+        <v>0.004125686811215153</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01398134654387916</v>
+        <v>0.004850170201301507</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01292288245727118</v>
+        <v>0.005254634299761486</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01263462200624508</v>
+        <v>0.004258562184380821</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006947111712937386</v>
+        <v>0.006947111712937395</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007768165776161692</v>
+        <v>0.007768165776161694</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00792318578889906</v>
+        <v>0.007923185788899062</v>
       </c>
       <c r="E4" t="n">
         <v>0.007039726238189532</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007039726238189534</v>
+        <v>0.007039726238189533</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00742725751687146</v>
+        <v>0.007427257516871465</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007395306815699379</v>
+        <v>0.007395306815699385</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007033333502774016</v>
+        <v>0.00703333350277402</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007884587637206895</v>
+        <v>0.007884587637206897</v>
       </c>
       <c r="K4" t="n">
-        <v>0.006967076808306134</v>
+        <v>0.006967076808306139</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0072641514280135</v>
+        <v>0.007264151428013504</v>
       </c>
     </row>
     <row r="5">
@@ -1826,31 +1826,31 @@
         <v>0.01053611768616335</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02610853582436982</v>
+        <v>0.02610853582436986</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02775798830349048</v>
+        <v>0.02775798830349049</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01305484409436023</v>
+        <v>0.01305484409436024</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01305484409436023</v>
+        <v>0.01305484409436024</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01972293393635733</v>
+        <v>0.01972293393635748</v>
       </c>
       <c r="H5" t="n">
         <v>0.0202701426337783</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01305470939450747</v>
+        <v>0.01305470939450748</v>
       </c>
       <c r="J5" t="n">
         <v>0.02811067419468925</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01152426164424631</v>
+        <v>0.0115242616442463</v>
       </c>
       <c r="L5" t="n">
         <v>0.01796941051907823</v>
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007936201657730384</v>
+        <v>0.007936201657730379</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008074358586261232</v>
+        <v>0.008074358586261229</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008919788373776863</v>
+        <v>0.008919788373776877</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007268407124475949</v>
+        <v>0.00726840712447595</v>
       </c>
       <c r="F6" t="n">
         <v>0.007305097336629118</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007697889504451526</v>
+        <v>0.008416347461664444</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008424650684104716</v>
+        <v>0.00842465068410472</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007303965490354081</v>
+        <v>0.007303965490354082</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008183168388373796</v>
+        <v>0.008183168388373808</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007228058964141873</v>
+        <v>0.007228058964141876</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00753536500488559</v>
+        <v>0.007535365004885597</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007545197924851242</v>
+        <v>0.007545197924851249</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008395288242124462</v>
+        <v>0.008395288242124464</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008521253007928527</v>
+        <v>0.008521253007928531</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007632787435721588</v>
+        <v>0.007632787435721589</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007632787435721588</v>
+        <v>0.007632787435721589</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008025343728785316</v>
+        <v>0.008025343728785323</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007993393027613239</v>
+        <v>0.007993393027613238</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007631419714687874</v>
+        <v>0.007631419714687876</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008482673849120742</v>
+        <v>0.008482673849120756</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007565163020219986</v>
+        <v>0.007565163020219992</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007862237639927362</v>
+        <v>0.00786223763992736</v>
       </c>
     </row>
     <row r="8">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008808139236342822</v>
+        <v>0.008808139236342823</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01093958652643463</v>
+        <v>0.01093958652642842</v>
       </c>
       <c r="D8" t="n">
         <v>0.01132951387450942</v>
@@ -1955,13 +1955,13 @@
         <v>0.009825652933042668</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00893581359714994</v>
+        <v>0.008935813597149943</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01056818914795779</v>
+        <v>0.0105681891479578</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01053623844678896</v>
+        <v>0.01053623844678898</v>
       </c>
       <c r="I8" t="n">
         <v>0.01017426513386036</v>
@@ -1970,7 +1970,7 @@
         <v>0.01102577080603782</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008804329455813267</v>
+        <v>0.008804329455813279</v>
       </c>
       <c r="L8" t="n">
         <v>0.01174204992334332</v>
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008827693216727512</v>
+        <v>0.008827693216727519</v>
       </c>
       <c r="C9" t="n">
         <v>0.01024027382138704</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0103662578610668</v>
+        <v>0.01036625786106681</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01012564175728825</v>
+        <v>0.01012564175728826</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009476539709444566</v>
+        <v>0.009476539709444568</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009870329308047881</v>
+        <v>0.009870329308047893</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009838378606875822</v>
+        <v>0.00983837860687582</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009476405293950448</v>
+        <v>0.009476405293950455</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01032765942838332</v>
+        <v>0.01032765942838333</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009084239636084965</v>
+        <v>0.009084239636084976</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009707223219189941</v>
+        <v>0.009707223219189954</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01086849568035437</v>
+        <v>0.003817952508977043</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01086607854009687</v>
+        <v>0.003061288795418729</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01203026443545486</v>
+        <v>0.003879094091099378</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0101960354993341</v>
+        <v>0.003242188606768123</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0101960354993341</v>
+        <v>0.003242183453035409</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01138694321018697</v>
+        <v>0.003845237372752393</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01144783574514345</v>
+        <v>0.003847640851547409</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01088866814818704</v>
+        <v>0.003819029649198135</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01161224427552077</v>
+        <v>0.003948375471767198</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01181984398876876</v>
+        <v>0.004588655783779867</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01102209387981605</v>
+        <v>0.003825165116710765</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01166455666474105</v>
+        <v>0.003825932238166096</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01180686627316696</v>
+        <v>0.002857960303324849</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01300083139277921</v>
+        <v>0.00426272804429524</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01099517078104427</v>
+        <v>0.002882850688702533</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01099517078104427</v>
+        <v>0.002882845534969813</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0122608787201308</v>
+        <v>0.004021970525890218</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01233136633375007</v>
+        <v>0.004045560476111962</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01168767888831289</v>
+        <v>0.00383498716455088</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01250243751658786</v>
+        <v>0.004223814475071589</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01261998310380356</v>
+        <v>0.005107297285573206</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01184125750618846</v>
+        <v>0.003885127274694055</v>
       </c>
     </row>
     <row r="4">
@@ -2182,31 +2182,31 @@
         <v>0.006768531995398325</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007313419915145464</v>
+        <v>0.007313419915145462</v>
       </c>
       <c r="D4" t="n">
         <v>0.00745915429198749</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006768255716945831</v>
+        <v>0.00676825571694583</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006768255716945831</v>
+        <v>0.006768255716945832</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007074135484696068</v>
+        <v>0.007074135484696071</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00711300498991688</v>
+        <v>0.007113004989916878</v>
       </c>
       <c r="I4" t="n">
         <v>0.006763140230141268</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007141068443276557</v>
+        <v>0.007141068443276554</v>
       </c>
       <c r="K4" t="n">
-        <v>0.006784671545847896</v>
+        <v>0.006784671545847895</v>
       </c>
       <c r="L4" t="n">
         <v>0.006860114005944808</v>
@@ -2219,34 +2219,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008200728399879342</v>
+        <v>0.008200728399879344</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01897189253240771</v>
+        <v>0.01897189253240772</v>
       </c>
       <c r="D5" t="n">
         <v>0.02063591728868888</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009107049045178008</v>
+        <v>0.009107049045178006</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009107049045178008</v>
+        <v>0.009107049045178006</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01432528343002449</v>
+        <v>0.01432528343002451</v>
       </c>
       <c r="H5" t="n">
         <v>0.01573438732657526</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009106940162136687</v>
+        <v>0.00910694016213669</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01564418695501133</v>
+        <v>0.01564418695501132</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009180080010287819</v>
+        <v>0.009180080010287806</v>
       </c>
       <c r="L5" t="n">
         <v>0.01097308397666587</v>
@@ -2259,19 +2259,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00701843176707209</v>
+        <v>0.007018431767072088</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007594965285116832</v>
+        <v>0.00759496528511683</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007723550543260121</v>
+        <v>0.007723547633694204</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006979451165124815</v>
+        <v>0.006979451165124811</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007013672468179546</v>
+        <v>0.007013672468179545</v>
       </c>
       <c r="G6" t="n">
         <v>0.008019224310181282</v>
@@ -2283,13 +2283,13 @@
         <v>0.007708229055626486</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008088519756998447</v>
+        <v>0.008088519756998444</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007029416809835723</v>
+        <v>0.007029416809835714</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007109042095072482</v>
+        <v>0.007109042095072461</v>
       </c>
     </row>
     <row r="7">
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007343009704337382</v>
+        <v>0.00734300970433738</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007917571183822938</v>
+        <v>0.007917571183822936</v>
       </c>
       <c r="D7" t="n">
         <v>0.008033612795415509</v>
@@ -2314,22 +2314,22 @@
         <v>0.00733919145348807</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007648613193635126</v>
+        <v>0.007648613193635122</v>
       </c>
       <c r="H7" t="n">
         <v>0.007687482698855936</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007337617939080326</v>
+        <v>0.007337617939080322</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00771554615221561</v>
+        <v>0.007715546152215612</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007359149254786952</v>
+        <v>0.007359149254786949</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007434591714883864</v>
+        <v>0.007434591714883861</v>
       </c>
     </row>
     <row r="8">
@@ -2339,22 +2339,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008589915803616543</v>
+        <v>0.008589915803616545</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0104171698871308</v>
+        <v>0.01041716988713767</v>
       </c>
       <c r="D8" t="n">
         <v>0.01079096901805893</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009495000909094973</v>
+        <v>0.009495000909094962</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008625173603485643</v>
+        <v>0.008625173603485645</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01014654241644961</v>
+        <v>0.0101465424164496</v>
       </c>
       <c r="H8" t="n">
         <v>0.01018541192167382</v>
@@ -2363,10 +2363,10 @@
         <v>0.009835547161894807</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01021372123681618</v>
+        <v>0.01021372123681617</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008582816957276742</v>
+        <v>0.008582816957276737</v>
       </c>
       <c r="L8" t="n">
         <v>0.01123931919899723</v>
@@ -2379,34 +2379,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008444666800782647</v>
+        <v>0.008444666800782643</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009523570982001369</v>
+        <v>0.009523570982001364</v>
       </c>
       <c r="D9" t="n">
-        <v>0.009639632012993277</v>
+        <v>0.009639632012993275</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009525727305368496</v>
+        <v>0.009525727305368494</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008943726386468504</v>
+        <v>0.008943726386468502</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00925461299181355</v>
+        <v>0.009254612991813554</v>
       </c>
       <c r="H9" t="n">
         <v>0.009293482497034369</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00894361773725876</v>
+        <v>0.008943617737258755</v>
       </c>
       <c r="J9" t="n">
         <v>0.009321545950394044</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008330091511194265</v>
+        <v>0.008661075336655829</v>
       </c>
       <c r="L9" t="n">
         <v>0.009040591513062293</v>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01103700703803391</v>
+        <v>0.003956375099927706</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009858786617870589</v>
+        <v>0.00302336130467126</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0123752159769314</v>
+        <v>0.004026802378484844</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0103092680153662</v>
+        <v>0.003285992832889491</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0103092680153662</v>
+        <v>0.003285986717249747</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01202058165695582</v>
+        <v>0.004008138678585024</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0123751848667125</v>
+        <v>0.004026023850752633</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01111958625338044</v>
+        <v>0.003960733207294655</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01393863467602902</v>
+        <v>0.004186388452354118</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01227092556843208</v>
+        <v>0.004668563813693619</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01347254438482196</v>
+        <v>0.004084933937655134</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01182210290454895</v>
+        <v>0.004019976423241018</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01063393016315619</v>
+        <v>0.002464542119989882</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01336132039342763</v>
+        <v>0.004522892977425467</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0111068024832363</v>
+        <v>0.002938663485535814</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0111068024832363</v>
+        <v>0.002938657369896067</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01295341746317764</v>
+        <v>0.004390617026148741</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01336177288558554</v>
+        <v>0.00452595109095339</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01191687404148443</v>
+        <v>0.004052404091512583</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01514468366609814</v>
+        <v>0.005210913684166652</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01311668043741594</v>
+        <v>0.005313237085622952</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01462342120917595</v>
+        <v>0.004942165666733858</v>
       </c>
     </row>
     <row r="4">
@@ -2575,28 +2575,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006799421538481405</v>
+        <v>0.006799421538481407</v>
       </c>
       <c r="C4" t="n">
-        <v>0.006716751526611653</v>
+        <v>0.006716751526611654</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007594930047933093</v>
+        <v>0.007594930047933095</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006817384578790458</v>
+        <v>0.006817384578790457</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006817384578790458</v>
+        <v>0.006817384578790457</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007380524265617499</v>
+        <v>0.0073805242656175</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007594925123984311</v>
+        <v>0.007594925123984313</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006824399282777707</v>
+        <v>0.006824399282777705</v>
       </c>
       <c r="J4" t="n">
         <v>0.008465379488523161</v>
@@ -2605,7 +2605,7 @@
         <v>0.007039484723073888</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008247120445755346</v>
+        <v>0.008247120445755349</v>
       </c>
     </row>
     <row r="5">
@@ -2618,31 +2618,31 @@
         <v>0.00864372946692982</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008747264092601641</v>
+        <v>0.008747264092601643</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02360358094069257</v>
+        <v>0.02360358094069256</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01026031899275285</v>
+        <v>0.01026031899275281</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01026031899275285</v>
+        <v>0.01026031899275281</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02018281907589999</v>
+        <v>0.02018281907590002</v>
       </c>
       <c r="H5" t="n">
         <v>0.02570407785194039</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01026014532011697</v>
+        <v>0.01026014532011695</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04079646992028754</v>
+        <v>0.04079646992028756</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01369337210620958</v>
+        <v>0.0136933721062096</v>
       </c>
       <c r="L5" t="n">
         <v>0.03946220552897665</v>
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007054822760295432</v>
+        <v>0.007054822760295436</v>
       </c>
       <c r="C6" t="n">
-        <v>0.006991598208490175</v>
+        <v>0.006991598208490173</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00786400340786733</v>
+        <v>0.007864000751623097</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007038170480289002</v>
+        <v>0.007038170480288998</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007079054233684433</v>
+        <v>0.007079054233684432</v>
       </c>
       <c r="G6" t="n">
         <v>0.00763592548743153</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008628807616040729</v>
+        <v>0.008628807616040733</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007079800504591735</v>
+        <v>0.007825194896369526</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009469102071913309</v>
+        <v>0.008751765061105329</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007287967947488452</v>
+        <v>0.007287967947488455</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008510369398947098</v>
+        <v>0.008510369398947103</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007425453554556751</v>
+        <v>0.007425453554556752</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007387614894981518</v>
+        <v>0.007387614894981521</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00822094270254174</v>
+        <v>0.008220942702541744</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007452842748378171</v>
+        <v>0.007452842748378172</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007452842748378171</v>
+        <v>0.007452842748378172</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008006556281692846</v>
+        <v>0.008006556281692849</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008220957140059654</v>
+        <v>0.008220957140059659</v>
       </c>
       <c r="I7" t="n">
         <v>0.00745043129885305</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009091411504598503</v>
+        <v>0.009091411504598506</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00766551673914923</v>
+        <v>0.007665516739149235</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008873152461830687</v>
+        <v>0.008873152461830692</v>
       </c>
     </row>
     <row r="8">
@@ -2735,34 +2735,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008750475252113666</v>
+        <v>0.008750475252113671</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01005464625098011</v>
+        <v>0.01005464625098533</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01116334080644274</v>
+        <v>0.01116334080644275</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009751012457825793</v>
+        <v>0.009751012457825798</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008819435947381132</v>
+        <v>0.008819435947381134</v>
       </c>
       <c r="G8" t="n">
         <v>0.01067116328449767</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0108855641428653</v>
+        <v>0.01088556414286531</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01011503830165787</v>
+        <v>0.01011503830165788</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01175628177424881</v>
+        <v>0.01175628177424882</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008965654951920983</v>
+        <v>0.008965654951920992</v>
       </c>
       <c r="L8" t="n">
         <v>0.01293706833022613</v>
@@ -2778,31 +2778,31 @@
         <v>0.008853231338806975</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009426869338492001</v>
+        <v>0.009426869338492003</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01026021683507602</v>
+        <v>0.01026021683507603</v>
       </c>
       <c r="E9" t="n">
         <v>0.0101954904371543</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009489859116330136</v>
+        <v>0.009489859116330128</v>
       </c>
       <c r="G9" t="n">
         <v>0.01004581072520332</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01026021158357012</v>
+        <v>0.01026021158357013</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009489685742363523</v>
+        <v>0.009489685742363524</v>
       </c>
       <c r="J9" t="n">
         <v>0.01113066594810899</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008934812835557705</v>
+        <v>0.009350479342599419</v>
       </c>
       <c r="L9" t="n">
         <v>0.01091240690534116</v>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01084682749310565</v>
+        <v>0.003816930897811843</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009804060382856132</v>
+        <v>0.002947319883782824</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01092010199889244</v>
+        <v>0.003820787189516518</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01019710308786291</v>
+        <v>0.003205446723180878</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01019710308786291</v>
+        <v>0.003205440422833044</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01095919468854238</v>
+        <v>0.003822844560128456</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01097128152062066</v>
+        <v>0.003822784108374739</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01093699869952531</v>
+        <v>0.003821696490148409</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01178889453861608</v>
+        <v>0.003980745275553596</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0117579206521113</v>
+        <v>0.004551656690170038</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01114219011984476</v>
+        <v>0.003832102252584894</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01161256015766827</v>
+        <v>0.003844032734700637</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01056950975876712</v>
+        <v>0.002411078103686942</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01169684101809123</v>
+        <v>0.003872855973412887</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01097643736851805</v>
+        <v>0.002862187392625538</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01097643736851805</v>
+        <v>0.002862181092277697</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01174180570921494</v>
+        <v>0.00388763126870824</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01175614759915207</v>
+        <v>0.003892066856613109</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01171668347596538</v>
+        <v>0.003879377528733864</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01267412645700022</v>
+        <v>0.004345802121655386</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01252820732361274</v>
+        <v>0.005066934795834681</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01195228843292337</v>
+        <v>0.003957085871858708</v>
       </c>
     </row>
     <row r="4">
@@ -2971,13 +2971,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006698711940845475</v>
+        <v>0.006698711940845476</v>
       </c>
       <c r="C4" t="n">
         <v>0.006665943111873125</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006742270529631532</v>
+        <v>0.006742270529631531</v>
       </c>
       <c r="E4" t="n">
         <v>0.006747330350597596</v>
@@ -2989,16 +2989,16 @@
         <v>0.006762370544441593</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006772783492105615</v>
+        <v>0.006772783492105617</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006731329708418513</v>
+        <v>0.006731329708418512</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007171640447105746</v>
+        <v>0.007171640447105748</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0067167348123714</v>
+        <v>0.006716734812371399</v>
       </c>
       <c r="L4" t="n">
         <v>0.006874420088471949</v>
@@ -3011,13 +3011,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007739515550846757</v>
+        <v>0.007739515550846759</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008494304268488215</v>
+        <v>0.008494304268488212</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00918397206025447</v>
+        <v>0.009183972060254472</v>
       </c>
       <c r="E5" t="n">
         <v>0.009360966066758646</v>
@@ -3026,22 +3026,22 @@
         <v>0.009360966066758646</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009639393506159107</v>
+        <v>0.009639393506159074</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01005305894732823</v>
+        <v>0.01005305894732822</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009360915114009782</v>
+        <v>0.009360915114009792</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01696201716204372</v>
+        <v>0.01696201716204373</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008757192630227039</v>
+        <v>0.008757192630227036</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01209924715866744</v>
+        <v>0.01209924715866745</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.006925318871905299</v>
+        <v>0.0069253188719053</v>
       </c>
       <c r="C6" t="n">
-        <v>0.006915105269556855</v>
+        <v>0.006915105269556856</v>
       </c>
       <c r="D6" t="n">
-        <v>0.006968140015444764</v>
+        <v>0.007632642755655535</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006934118870719198</v>
+        <v>0.006934118870719197</v>
       </c>
       <c r="F6" t="n">
         <v>0.006959924665957859</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007651522223979208</v>
+        <v>0.006988977475501417</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007693279040604496</v>
+        <v>0.007693279040604497</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007620481387956124</v>
+        <v>0.007620481387956123</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007420291361837554</v>
+        <v>0.008059979042536389</v>
       </c>
       <c r="K6" t="n">
-        <v>0.006941878946252606</v>
+        <v>0.006941878946252607</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007100865233811398</v>
+        <v>0.007100865233811399</v>
       </c>
     </row>
     <row r="7">
@@ -3094,10 +3094,10 @@
         <v>0.007250764133814526</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007251397116063147</v>
+        <v>0.007251397116063146</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007294304496233985</v>
+        <v>0.007294304496233984</v>
       </c>
       <c r="E7" t="n">
         <v>0.007286413282236641</v>
@@ -3106,22 +3106,22 @@
         <v>0.007286413282236641</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00731442273741064</v>
+        <v>0.007314422737410643</v>
       </c>
       <c r="H7" t="n">
         <v>0.007324835685074665</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007283381901387562</v>
+        <v>0.007283381901387561</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007723692640074796</v>
+        <v>0.007723692640074797</v>
       </c>
       <c r="K7" t="n">
         <v>0.007268787005340448</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007426472281440995</v>
+        <v>0.007426472281440996</v>
       </c>
     </row>
     <row r="8">
@@ -3131,16 +3131,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008475575181751953</v>
+        <v>0.008475575181751955</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009694911616940314</v>
+        <v>0.009694911616934787</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009986789695760882</v>
+        <v>0.009986789695760879</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009394161263899411</v>
+        <v>0.009394161263899407</v>
       </c>
       <c r="F8" t="n">
         <v>0.008548565213338284</v>
@@ -3149,7 +3149,7 @@
         <v>0.009754828274404848</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009765241222071269</v>
+        <v>0.009765241222071263</v>
       </c>
       <c r="I8" t="n">
         <v>0.009723787438381776</v>
@@ -3158,10 +3158,10 @@
         <v>0.01016433707617147</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008471017761558898</v>
+        <v>0.008471017761558893</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0111366679085808</v>
+        <v>0.01113666790858079</v>
       </c>
     </row>
     <row r="9">
@@ -3174,7 +3174,7 @@
         <v>0.008354002697465427</v>
       </c>
       <c r="C9" t="n">
-        <v>0.008850105823947347</v>
+        <v>0.008850105823947341</v>
       </c>
       <c r="D9" t="n">
         <v>0.008893031624095219</v>
@@ -3192,16 +3192,16 @@
         <v>0.008923544392958862</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00888209060927176</v>
+        <v>0.008882090609271765</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009322401347958991</v>
+        <v>0.009322401347958989</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008243610310347373</v>
+        <v>0.008580418447226257</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009025180989325188</v>
+        <v>0.009025180989325187</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01074976395347068</v>
+        <v>0.003726155158101856</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009800580113694529</v>
+        <v>0.002926435745892544</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01081400604429576</v>
+        <v>0.003729536091746911</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01013982797427362</v>
+        <v>0.0031771243736685</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01013982797427361</v>
+        <v>0.003177118740043063</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01079198642715061</v>
+        <v>0.003728377243031046</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01081537347436719</v>
+        <v>0.003728944098891649</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01080230574652055</v>
+        <v>0.003728940574055952</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01097373117738925</v>
+        <v>0.003837940493275847</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01170541766040175</v>
+        <v>0.004518333021130028</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01077903833731559</v>
+        <v>0.003727192202286597</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01152865391495836</v>
+        <v>0.003717061248478548</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01058075575644524</v>
+        <v>0.002402395977536614</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01160254562711623</v>
+        <v>0.00374250204134676</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01092666787268203</v>
+        <v>0.002827469880092272</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01092666787268203</v>
+        <v>0.002827464246466839</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01157721850604935</v>
+        <v>0.003734329517758377</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01160452893561027</v>
+        <v>0.00374291626357854</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01158945321372122</v>
+        <v>0.003738298175341962</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01176699921617864</v>
+        <v>0.003930743584608936</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01248493929993287</v>
+        <v>0.005027280044546564</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01156233375315851</v>
+        <v>0.003729494670342284</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00668841901629446</v>
+        <v>0.006688419016294469</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00666548748283935</v>
+        <v>0.006665487482839351</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006726608217121666</v>
+        <v>0.006726608217121672</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00671492203235594</v>
+        <v>0.006714922032355942</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00671492203235594</v>
+        <v>0.006714922032355942</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006711115465887187</v>
+        <v>0.006711115465887264</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006727506731358264</v>
+        <v>0.00672750673135826</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006703588693901389</v>
+        <v>0.006703588693901366</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00674532148558808</v>
+        <v>0.006745321485588087</v>
       </c>
       <c r="K4" t="n">
-        <v>0.006690918936117918</v>
+        <v>0.00669091893611792</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006705990708696718</v>
+        <v>0.006705990708696714</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007681975989765704</v>
+        <v>0.007681975989765722</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008544421089388667</v>
+        <v>0.008544421089388668</v>
       </c>
       <c r="D5" t="n">
         <v>0.009036756218838071</v>
       </c>
       <c r="E5" t="n">
-        <v>0.008925562375334716</v>
+        <v>0.008925562375334737</v>
       </c>
       <c r="F5" t="n">
-        <v>0.008925562375334716</v>
+        <v>0.008925562375334737</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008853748813787393</v>
+        <v>0.00885374881378739</v>
       </c>
       <c r="H5" t="n">
-        <v>0.009321106079509891</v>
+        <v>0.009321106079509896</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008925523368097802</v>
+        <v>0.008925523368097824</v>
       </c>
       <c r="J5" t="n">
-        <v>0.009477040544816923</v>
+        <v>0.009477040544816916</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008436139444355709</v>
+        <v>0.008436139444355712</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008951126200277774</v>
+        <v>0.008951126200277781</v>
       </c>
     </row>
     <row r="6">
@@ -3447,34 +3447,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007573974745316056</v>
+        <v>0.007573974745316055</v>
       </c>
       <c r="C6" t="n">
-        <v>0.006911380674056194</v>
+        <v>0.006911380674056197</v>
       </c>
       <c r="D6" t="n">
-        <v>0.006950694281136985</v>
+        <v>0.00695069428113698</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006904926203134262</v>
+        <v>0.006904926203134265</v>
       </c>
       <c r="F6" t="n">
-        <v>0.006930435511966953</v>
+        <v>0.006930435511966955</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007596671194908752</v>
+        <v>0.007596671194908746</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007643891886510498</v>
+        <v>0.006951847994695337</v>
       </c>
       <c r="I6" t="n">
-        <v>0.006928851639041811</v>
+        <v>0.007589144422922984</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007629692702627157</v>
+        <v>0.006990102491955845</v>
       </c>
       <c r="K6" t="n">
-        <v>0.006915796931127241</v>
+        <v>0.006915796931127221</v>
       </c>
       <c r="L6" t="n">
         <v>0.006930016529079115</v>
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007231455045354312</v>
+        <v>0.007231455045354314</v>
       </c>
       <c r="C7" t="n">
         <v>0.007238270675876745</v>
@@ -3496,13 +3496,13 @@
         <v>0.007269625208827729</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007249031139054304</v>
+        <v>0.007249031139054306</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007249031139054304</v>
+        <v>0.007249031139054306</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00725415149494701</v>
+        <v>0.007254151494947013</v>
       </c>
       <c r="H7" t="n">
         <v>0.007270542760418116</v>
@@ -3514,10 +3514,10 @@
         <v>0.007288357514647932</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00723395496517777</v>
+        <v>0.007233954965177766</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00724902673775657</v>
+        <v>0.007249026737756566</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008452064849338282</v>
+        <v>0.008452064849338279</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009666668351526004</v>
+        <v>0.009666668351532293</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009945438540492143</v>
+        <v>0.009945438540492133</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009345161276093887</v>
+        <v>0.009345161276093885</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008506902203099395</v>
+        <v>0.008506902203099392</v>
       </c>
       <c r="G8" t="n">
         <v>0.009680026250069758</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009696417515543562</v>
+        <v>0.009696417515543565</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009672499478083988</v>
+        <v>0.009672499478083985</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009714469138827314</v>
+        <v>0.009714469138827311</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008432176353911669</v>
+        <v>0.008432176353911667</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01093390151693305</v>
+        <v>0.01093390151693304</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008253689902982381</v>
+        <v>0.008253689902982383</v>
       </c>
       <c r="C9" t="n">
-        <v>0.008730239615603151</v>
+        <v>0.008730239615603154</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008761613362740459</v>
+        <v>0.008761613362740454</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009280695871793511</v>
+        <v>0.009280695871793514</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008738632566921384</v>
+        <v>0.008738632566921388</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008746120434673413</v>
+        <v>0.008746120434673418</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008762511700144516</v>
+        <v>0.008762511700144528</v>
       </c>
       <c r="I9" t="n">
-        <v>0.008738593662687644</v>
+        <v>0.008738593662687649</v>
       </c>
       <c r="J9" t="n">
-        <v>0.008780326454374338</v>
+        <v>0.00878032645437434</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008442716094001452</v>
+        <v>0.008453758207323376</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008740995677482972</v>
+        <v>0.008740995677482977</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01095183655602005</v>
+        <v>0.003883129747760744</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009827913321975242</v>
+        <v>0.002975370379296849</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01116763974484076</v>
+        <v>0.003894487040968758</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01025592614073574</v>
+        <v>0.003230641202455751</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01025592614073574</v>
+        <v>0.003230634632967916</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01129044372126107</v>
+        <v>0.00390094997033942</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01207161613201261</v>
+        <v>0.003941732393931791</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01104534087868338</v>
+        <v>0.003888068261895571</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01120621927942074</v>
+        <v>0.003963276602282183</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01185991850736202</v>
+        <v>0.004582876796063852</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01290517310809393</v>
+        <v>0.003986564384655869</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01172468219604267</v>
+        <v>0.003943762139274014</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01059476328878152</v>
+        <v>0.002437080340896509</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01197290056668237</v>
+        <v>0.004025987527020761</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01104286693799909</v>
+        <v>0.002895164921885453</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01104286693799907</v>
+        <v>0.00289515835239761</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01211415057833281</v>
+        <v>0.004072288016102173</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01301311419062684</v>
+        <v>0.004367660662310556</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01183246120793077</v>
+        <v>0.003980326680087698</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01200441472368374</v>
+        <v>0.00412634567249809</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0126435735259905</v>
+        <v>0.005120903091061629</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0139713525878817</v>
+        <v>0.004683957075797851</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006743669150381796</v>
+        <v>0.006743669150381812</v>
       </c>
       <c r="C4" t="n">
         <v>0.006681704158357704</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006871955001778895</v>
+        <v>0.006871955001778911</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006775422876862677</v>
+        <v>0.006775422876862678</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006775422876862677</v>
+        <v>0.006775422876862678</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006941602339848118</v>
+        <v>0.006941602339848129</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007409242479107319</v>
+        <v>0.007409242479107331</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006776794716846192</v>
+        <v>0.006776794716846194</v>
       </c>
       <c r="J4" t="n">
-        <v>0.006843993166390215</v>
+        <v>0.006843993166390228</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00678644818969942</v>
+        <v>0.006786448189699431</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007904653364664086</v>
+        <v>0.007904653364664093</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008265800580575187</v>
+        <v>0.008265800580575191</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008649512994826115</v>
+        <v>0.008649512994826112</v>
       </c>
       <c r="D5" t="n">
         <v>0.0112930747699587</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01000292630687528</v>
+        <v>0.01000292630687521</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01000292630687528</v>
+        <v>0.01000292630687521</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01274414362818754</v>
+        <v>0.01274414362818752</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02266847901327624</v>
+        <v>0.02266847901327628</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01000284241827968</v>
+        <v>0.01000284241827964</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01098579663344307</v>
+        <v>0.01098579663344308</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009774560871955803</v>
+        <v>0.009774560871955818</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03314883031384484</v>
+        <v>0.0331488303138449</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.006975308595516864</v>
+        <v>0.006975308595516887</v>
       </c>
       <c r="C6" t="n">
-        <v>0.006937945979991744</v>
+        <v>0.006937945979991742</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007103203151654401</v>
+        <v>0.00710320315165441</v>
       </c>
       <c r="E6" t="n">
         <v>0.006978304013350561</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007008725105924587</v>
+        <v>0.007008725105924588</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007892326967803499</v>
+        <v>0.007173241784983203</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008391139254821916</v>
+        <v>0.008391139254821912</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007727519344801557</v>
+        <v>0.00700843416198127</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007795267370888283</v>
+        <v>0.007095877178415928</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007012799631361827</v>
+        <v>0.007012799631361828</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00814245353383671</v>
+        <v>0.008142453533836712</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007338546188835578</v>
+        <v>0.007338546188835588</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007316525787381385</v>
+        <v>0.007316525787381386</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007466812803647993</v>
+        <v>0.007466812803647983</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007374508329284963</v>
+        <v>0.007374508329284962</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007374508329284963</v>
+        <v>0.007374508329284962</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0075364793783019</v>
+        <v>0.007536479378301913</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00800411951756109</v>
+        <v>0.008004119517561109</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007371671755299972</v>
+        <v>0.007371671755299971</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007438870204844007</v>
+        <v>0.007438870204844018</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007381325228153203</v>
+        <v>0.007381325228153207</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008499530403117872</v>
+        <v>0.008499530403117881</v>
       </c>
     </row>
     <row r="8">
@@ -3923,19 +3923,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008640840238607447</v>
+        <v>0.008640840238607441</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009921127403651248</v>
+        <v>0.009921127403646167</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0103379640315821</v>
+        <v>0.01033796403158211</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009620672781310402</v>
+        <v>0.009620672781310399</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008716892224061872</v>
+        <v>0.008716892224061868</v>
       </c>
       <c r="G8" t="n">
         <v>0.01013817250603784</v>
@@ -3947,10 +3947,10 @@
         <v>0.009973364883035905</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01004081870168522</v>
+        <v>0.01004081870168525</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008659482272942855</v>
+        <v>0.008659482272942847</v>
       </c>
       <c r="L8" t="n">
         <v>0.01245855452173335</v>
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008634406306056275</v>
+        <v>0.008634406306056296</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0091761745169939</v>
+        <v>0.009176174516993896</v>
       </c>
       <c r="D9" t="n">
-        <v>0.009326480891743153</v>
+        <v>0.009326480891743172</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009882004236787966</v>
+        <v>0.009882004236787964</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009231404092417021</v>
+        <v>0.009231404092417015</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009396128107914415</v>
+        <v>0.009396128107914428</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009863768247173619</v>
+        <v>0.009863768247173627</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009231320484912486</v>
+        <v>0.009231320484912485</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009298518934456521</v>
+        <v>0.00929851893445653</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008914312672846971</v>
+        <v>0.008914312672846991</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01035917913273038</v>
+        <v>0.01035917913273039</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01081806961916107</v>
+        <v>0.003783088986929623</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00981335324775099</v>
+        <v>0.00294684284799187</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01087392325301149</v>
+        <v>0.003786028452744919</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01018989708909295</v>
+        <v>0.003199323313751635</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01018989708909295</v>
+        <v>0.003199316944566683</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01085517976032053</v>
+        <v>0.003785042019952169</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01087690283044261</v>
+        <v>0.003785519679265241</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01089569197716648</v>
+        <v>0.003787194558402486</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01107994216182631</v>
+        <v>0.003926054799002718</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01175764591854281</v>
+        <v>0.004551187533618565</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01083573871971664</v>
+        <v>0.003783509086558918</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01158279514162257</v>
+        <v>0.003799304493199651</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01057748859591886</v>
+        <v>0.002420758729357627</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01164703839059595</v>
+        <v>0.003821592401201853</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01096634044284811</v>
+        <v>0.002859595246192708</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01096634044284811</v>
+        <v>0.002859588877007753</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01162547949129854</v>
+        <v>0.003814651284229669</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01165089098073638</v>
+        <v>0.003822620457564754</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01167260108207984</v>
+        <v>0.00382994172818797</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01185911718242997</v>
+        <v>0.004064595525836902</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01252506375314574</v>
+        <v>0.005073719387504243</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01160312731917919</v>
+        <v>0.00380737296774127</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006695010342583776</v>
+        <v>0.006695010342583777</v>
       </c>
       <c r="C4" t="n">
-        <v>0.006661648570461851</v>
+        <v>0.00666164857046185</v>
       </c>
       <c r="D4" t="n">
         <v>0.00672821296118862</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00673885179139918</v>
+        <v>0.006738851791399179</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00673885179139918</v>
+        <v>0.006738851791399179</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006713956991061857</v>
+        <v>0.006713956991061852</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006730070396168241</v>
+        <v>0.006730070396168246</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006720339353839853</v>
+        <v>0.006720339353839852</v>
       </c>
       <c r="J4" t="n">
-        <v>0.006752195465955242</v>
+        <v>0.006752195465955241</v>
       </c>
       <c r="K4" t="n">
-        <v>0.006705665397897654</v>
+        <v>0.006705665397897653</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006705684999429498</v>
+        <v>0.006705684999429502</v>
       </c>
     </row>
     <row r="5">
@@ -4199,13 +4199,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007799481571630865</v>
+        <v>0.007799481571630862</v>
       </c>
       <c r="C5" t="n">
         <v>0.00853180662461884</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009064973988485162</v>
+        <v>0.009064973988485154</v>
       </c>
       <c r="E5" t="n">
         <v>0.009290808912555871</v>
@@ -4214,19 +4214,19 @@
         <v>0.009290808912555871</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008916149465825376</v>
+        <v>0.008916149465825276</v>
       </c>
       <c r="H5" t="n">
-        <v>0.009371266101932188</v>
+        <v>0.009371266101932181</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009290766243550432</v>
+        <v>0.009290766243550434</v>
       </c>
       <c r="J5" t="n">
-        <v>0.009600748668403899</v>
+        <v>0.009600748668403903</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008688736370982048</v>
+        <v>0.008688736370982044</v>
       </c>
       <c r="L5" t="n">
         <v>0.008946280929576441</v>
@@ -4239,34 +4239,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.006918027035776168</v>
+        <v>0.007577292751305959</v>
       </c>
       <c r="C6" t="n">
-        <v>0.006907608057741108</v>
+        <v>0.006907608057741107</v>
       </c>
       <c r="D6" t="n">
-        <v>0.006951018790378133</v>
+        <v>0.006951021601254586</v>
       </c>
       <c r="E6" t="n">
         <v>0.006921072644985883</v>
       </c>
       <c r="F6" t="n">
-        <v>0.006945515079282353</v>
+        <v>0.00694551507928235</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006936973684254247</v>
+        <v>0.006936973684254243</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007642845544257671</v>
+        <v>0.007642845544257667</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007602621762562035</v>
+        <v>0.007602621762562032</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00763327908792581</v>
+        <v>0.006994625027141222</v>
       </c>
       <c r="K6" t="n">
-        <v>0.006927808805396708</v>
+        <v>0.006927808805396694</v>
       </c>
       <c r="L6" t="n">
         <v>0.006927636108405042</v>
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007239187979343888</v>
+        <v>0.007239187979343887</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007238614467723784</v>
+        <v>0.007238614467723785</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007272372406209352</v>
+        <v>0.007272372406209349</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007268149096807078</v>
+        <v>0.007268149096807075</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007268149096807078</v>
+        <v>0.007268149096807075</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007258134627821967</v>
+        <v>0.007258134627821961</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007274248032928358</v>
+        <v>0.007274248032928355</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007264516990599962</v>
+        <v>0.007264516990599961</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007296373102715353</v>
+        <v>0.007296373102715351</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007249843034657763</v>
+        <v>0.007249843034657761</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007249862636189613</v>
+        <v>0.00724986263618961</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00845814190079759</v>
+        <v>0.008458141900797588</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009666347822670682</v>
+        <v>0.009666347822670673</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009946318418317286</v>
+        <v>0.009946318418317271</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009362318408772483</v>
+        <v>0.009362318408772476</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008523865215793751</v>
+        <v>0.008523865215793753</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00968217907686196</v>
+        <v>0.009682179076861948</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0096982924819707</v>
+        <v>0.009698292481970692</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009688561439639955</v>
+        <v>0.009688561439639949</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00972065438653451</v>
+        <v>0.009720654386534503</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008446411780869226</v>
+        <v>0.008446411780869223</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01093272490929716</v>
+        <v>0.01093272490929715</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008333188463023706</v>
+        <v>0.008333188463023705</v>
       </c>
       <c r="C9" t="n">
-        <v>0.008822578203368287</v>
+        <v>0.008822578203368282</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008856354513026122</v>
+        <v>0.008856354513026117</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009413930640906424</v>
+        <v>0.009413930640906419</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008848523298917801</v>
+        <v>0.008848523298917792</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008842098363466467</v>
+        <v>0.008842098363466456</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008858211768572854</v>
+        <v>0.008858211768572849</v>
       </c>
       <c r="I9" t="n">
-        <v>0.008848480726244459</v>
+        <v>0.008848480726244454</v>
       </c>
       <c r="J9" t="n">
-        <v>0.008880336838359849</v>
+        <v>0.008880336838359844</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008549920213348517</v>
+        <v>0.008216855531442484</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008833826371834112</v>
+        <v>0.008833826371834108</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01068095249734581</v>
+        <v>0.003657626204325555</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009810794124405053</v>
+        <v>0.00292780443312991</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01073124765468582</v>
+        <v>0.003660273138562132</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0101366347903193</v>
+        <v>0.003167118841056874</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0101366347903193</v>
+        <v>0.003167113141832204</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01071393078140884</v>
+        <v>0.003659361785915642</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01073602061025056</v>
+        <v>0.00365986889192071</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01072848568249319</v>
+        <v>0.003660148080426166</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01096403077992042</v>
+        <v>0.003822715021149343</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0117225319317264</v>
+        <v>0.004512743441904507</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01070361578406229</v>
+        <v>0.003658318258557143</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01145752191267687</v>
+        <v>0.003618594591365513</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01058786692687268</v>
+        <v>0.002417773200699951</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01151537176222833</v>
+        <v>0.003638804665619747</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01092040196578821</v>
+        <v>0.002824161553180458</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01092040196578821</v>
+        <v>0.002824155853955788</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01149545377078032</v>
+        <v>0.003632392119367234</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01152126016333311</v>
+        <v>0.003640488634527538</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01151263202688467</v>
+        <v>0.003637951300876745</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01175418822130467</v>
+        <v>0.003918745502295612</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01250138634818655</v>
+        <v>0.005035873795838512</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0114835975500855</v>
+        <v>0.003628542625315323</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006685197218203302</v>
+        <v>0.0066851972182033</v>
       </c>
       <c r="C4" t="n">
         <v>0.006659323000858097</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006715095558055337</v>
+        <v>0.006715095558055334</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006710635420250787</v>
+        <v>0.006710635420250783</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006710635420250788</v>
+        <v>0.006710635420250783</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006702407909534558</v>
+        <v>0.006702407909534557</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006718018560567912</v>
+        <v>0.00671801856056791</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006697450898432193</v>
+        <v>0.006697450898432191</v>
       </c>
       <c r="J4" t="n">
-        <v>0.006738972992183947</v>
+        <v>0.006738972992183945</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00669424030538772</v>
+        <v>0.006694240305387717</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006698837690925207</v>
+        <v>0.006698837690925204</v>
       </c>
     </row>
     <row r="5">
@@ -4595,28 +4595,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007724277321894957</v>
+        <v>0.007724277321894954</v>
       </c>
       <c r="C5" t="n">
         <v>0.008532288003071362</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0089364993316435</v>
+        <v>0.008936499331643488</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00891562677549006</v>
+        <v>0.008915626775490095</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00891562677549006</v>
+        <v>0.008915626775490095</v>
       </c>
       <c r="G5" t="n">
         <v>0.008799621801335169</v>
       </c>
       <c r="H5" t="n">
-        <v>0.009247356273709345</v>
+        <v>0.009247356273709338</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008915588065712276</v>
+        <v>0.00891558806571225</v>
       </c>
       <c r="J5" t="n">
         <v>0.009464093338996298</v>
@@ -4625,7 +4625,7 @@
         <v>0.008588642308959563</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008921571889131188</v>
+        <v>0.008921571889131183</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.006909973148334733</v>
+        <v>0.007567337360668175</v>
       </c>
       <c r="C6" t="n">
-        <v>0.006904582427363615</v>
+        <v>0.006904582427363614</v>
       </c>
       <c r="D6" t="n">
-        <v>0.006938387760045675</v>
+        <v>0.006938384915604574</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006898848172010748</v>
+        <v>0.006898848172010746</v>
       </c>
       <c r="F6" t="n">
         <v>0.006923914056305277</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007584548051999433</v>
+        <v>0.00692718383966599</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007630285806475894</v>
+        <v>0.007630285806475892</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007579591040897064</v>
+        <v>0.006922226828563623</v>
       </c>
       <c r="J6" t="n">
-        <v>0.006982946541432527</v>
+        <v>0.007619594954954237</v>
       </c>
       <c r="K6" t="n">
-        <v>0.006918847564720837</v>
+        <v>0.006918847564720836</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006922385354436137</v>
+        <v>0.006922385354436224</v>
       </c>
     </row>
     <row r="7">
@@ -4678,34 +4678,34 @@
         <v>0.00722272270273676</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007226429136589568</v>
+        <v>0.007226429136589566</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007252602015554292</v>
+        <v>0.007252602015554293</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0072379093492003</v>
+        <v>0.007237909349200298</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0072379093492003</v>
+        <v>0.007237909349200298</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007239933394068016</v>
+        <v>0.007239933394068017</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007255544045101371</v>
+        <v>0.00725554404510137</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007234976382965653</v>
+        <v>0.007234976382965651</v>
       </c>
       <c r="J7" t="n">
         <v>0.007276498476717404</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007231765789921177</v>
+        <v>0.007231765789921176</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007236363175458667</v>
+        <v>0.007236363175458665</v>
       </c>
     </row>
     <row r="8">
@@ -4715,34 +4715,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008438041542729681</v>
+        <v>0.008438041542729676</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009641209468655943</v>
+        <v>0.009641209468649842</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009912465508797362</v>
+        <v>0.009912465508797352</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009322256634551612</v>
+        <v>0.009322256634551603</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008489997043259354</v>
+        <v>0.008489997043259352</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009651688919492588</v>
+        <v>0.00965168891949258</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009667299570528672</v>
+        <v>0.009667299570528668</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009646731908390212</v>
+        <v>0.009646731908390209</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009688489136214446</v>
+        <v>0.009688489136214447</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008424860204229896</v>
+        <v>0.0084248602042299</v>
       </c>
       <c r="L8" t="n">
         <v>0.01089789686321996</v>
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008245329896729194</v>
+        <v>0.008245329896729195</v>
       </c>
       <c r="C9" t="n">
-        <v>0.008716494096395952</v>
+        <v>0.008716494096395948</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008742686175925092</v>
+        <v>0.008742686175925088</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009264516435612977</v>
+        <v>0.009264516435612971</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008725079953471614</v>
+        <v>0.008725079953471606</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008729998353874403</v>
+        <v>0.008729998353874399</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008745609004907751</v>
+        <v>0.008745609004907746</v>
       </c>
       <c r="I9" t="n">
-        <v>0.008725041342772031</v>
+        <v>0.008725041342772027</v>
       </c>
       <c r="J9" t="n">
-        <v>0.008766563436523789</v>
+        <v>0.008766563436523784</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008439995353814945</v>
+        <v>0.008439995353814941</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008726428135265047</v>
+        <v>0.008726428135265042</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01304932556171992</v>
+        <v>0.004136414776232878</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01108130526518838</v>
+        <v>0.003692487761913996</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01534257323846125</v>
+        <v>0.004257103846703021</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01120434614474347</v>
+        <v>0.003797849570680465</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01075883235402426</v>
+        <v>0.00342701323540648</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01415801885687847</v>
+        <v>0.004194763102314828</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01428629671304139</v>
+        <v>0.004199936200026776</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01151403044469169</v>
+        <v>0.00405561024144127</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01393884008495434</v>
+        <v>0.004142904766567265</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01343852423332604</v>
+        <v>0.005104006514874671</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02071759782415515</v>
+        <v>0.004543686217217129</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01422479740525679</v>
+        <v>0.0045776589791491</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01202558359952404</v>
+        <v>0.003406815200936064</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01686250727833447</v>
+        <v>0.005437504616504725</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01214919140859238</v>
+        <v>0.003577971930448521</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01170367761787317</v>
+        <v>0.002965841439655827</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01550002435981333</v>
+        <v>0.004995456962880187</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0156480987001094</v>
+        <v>0.005049184123335025</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01245719332539075</v>
+        <v>0.004003408841423297</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01525569115154251</v>
+        <v>0.004864132577128692</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01449000815196334</v>
+        <v>0.005938550209102435</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02304461646489033</v>
+        <v>0.007485998255408906</v>
       </c>
     </row>
     <row r="4">
@@ -4951,34 +4951,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008243684122137329</v>
+        <v>0.008243684122137336</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007256661305895386</v>
+        <v>0.007256661305895384</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009606922692813031</v>
+        <v>0.00960692269281303</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007267549289652332</v>
+        <v>0.00726754928965233</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007267549289652332</v>
+        <v>0.00726754928965233</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008898409916231781</v>
+        <v>0.00889840991623179</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008979085391496252</v>
+        <v>0.008979085391496253</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007301617651559437</v>
+        <v>0.007301617651559436</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008803204475910747</v>
+        <v>0.008803204475910752</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007752991316601955</v>
+        <v>0.007752991316601957</v>
       </c>
       <c r="L4" t="n">
         <v>0.0128009419432783</v>
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03209676992185646</v>
+        <v>0.03209676992185659</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01617596433307024</v>
+        <v>0.01617596433307021</v>
       </c>
       <c r="D5" t="n">
         <v>0.05702836247810567</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01617596541492137</v>
+        <v>0.01617596541492134</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01617596541492137</v>
+        <v>0.01617596541492134</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04531215495252314</v>
+        <v>0.04531215495252316</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05069863370083591</v>
+        <v>0.05069863370083588</v>
       </c>
       <c r="I5" t="n">
         <v>0.01617555167910678</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04489719243459604</v>
+        <v>0.04489719243459605</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02395360081134719</v>
+        <v>0.02395360081134728</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05162191906789766</v>
+        <v>0.05162191906789763</v>
       </c>
     </row>
     <row r="6">
@@ -5031,34 +5031,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.009462456188072555</v>
+        <v>0.008560525662066975</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00757208906739695</v>
+        <v>0.007572089067396947</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009968149279600583</v>
+        <v>0.009968150915579605</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007546683093995248</v>
+        <v>0.007546683093995246</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007614270371795411</v>
+        <v>0.007614270371795408</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01011718198216701</v>
+        <v>0.009215251456161418</v>
       </c>
       <c r="H6" t="n">
         <v>0.01022291856219195</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008520389717494662</v>
+        <v>0.008520389717494661</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01003025445657955</v>
+        <v>0.009154881653608338</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008048704148392179</v>
+        <v>0.008048704148392155</v>
       </c>
       <c r="L6" t="n">
         <v>0.01316264729442995</v>
@@ -5074,34 +5074,34 @@
         <v>0.008961037353382429</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008019383536767968</v>
+        <v>0.008019383536767967</v>
       </c>
       <c r="D7" t="n">
         <v>0.01032425160520249</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00801854265571946</v>
+        <v>0.008018542655719456</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00801854265571946</v>
+        <v>0.008018542655719456</v>
       </c>
       <c r="G7" t="n">
-        <v>0.009615763147476879</v>
+        <v>0.009615763147476886</v>
       </c>
       <c r="H7" t="n">
         <v>0.009696438622741346</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008018970882804528</v>
+        <v>0.008018970882804531</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00952055770715584</v>
+        <v>0.009520557707155843</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008470344547847054</v>
+        <v>0.008470344547847057</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01351829517452339</v>
+        <v>0.01351829517452338</v>
       </c>
     </row>
     <row r="8">
@@ -5111,10 +5111,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01036922708037482</v>
+        <v>0.01036922708037483</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01089394121278166</v>
+        <v>0.0108939412127866</v>
       </c>
       <c r="D8" t="n">
         <v>0.01350348292233478</v>
@@ -5123,10 +5123,10 @@
         <v>0.01049281705413267</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009473583628518387</v>
+        <v>0.009473583628518386</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0124908081489262</v>
+        <v>0.01249080814892621</v>
       </c>
       <c r="H8" t="n">
         <v>0.01257148362419055</v>
@@ -5135,10 +5135,10 @@
         <v>0.01089401588425387</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01239589098762845</v>
+        <v>0.01239589098762846</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009851286685038794</v>
+        <v>0.009851286685038796</v>
       </c>
       <c r="L8" t="n">
         <v>0.01792559316652088</v>
@@ -5151,25 +5151,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01092117080036451</v>
+        <v>0.01092117080036452</v>
       </c>
       <c r="C9" t="n">
         <v>0.01077061312267237</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01307550618507584</v>
+        <v>0.01307550618507585</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01168352215928167</v>
+        <v>0.01168352215928168</v>
       </c>
       <c r="F9" t="n">
         <v>0.01077061354380458</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01236699273338128</v>
+        <v>0.01236699273338129</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01244766820864576</v>
+        <v>0.01244766820864577</v>
       </c>
       <c r="I9" t="n">
         <v>0.01077020046870895</v>
@@ -5181,7 +5181,7 @@
         <v>0.01076321020793563</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01626952476042781</v>
+        <v>0.0162695247604278</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01253021595865395</v>
+        <v>0.004095951640499756</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01143778305035927</v>
+        <v>0.003702369383265763</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01505295823272891</v>
+        <v>0.004228718555814593</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01155876186387157</v>
+        <v>0.003805906125996135</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01111986433076436</v>
+        <v>0.003440577032305455</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01397440498756906</v>
+        <v>0.00417195644070112</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0139150891155275</v>
+        <v>0.004167207492768601</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01186508127884262</v>
+        <v>0.004060946943723274</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0129708714679254</v>
+        <v>0.004069306914193725</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01341722255797045</v>
+        <v>0.005089497481270247</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02007161123010975</v>
+        <v>0.004496239952640421</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01365965467099438</v>
+        <v>0.004377782078179853</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01246680606868931</v>
+        <v>0.003538758017687572</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0165613308706683</v>
+        <v>0.005321520661056974</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01258829265011114</v>
+        <v>0.003707127092451615</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01214939511700393</v>
+        <v>0.003104087266082194</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01532077121710285</v>
+        <v>0.004919595900404533</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01525304708162949</v>
+        <v>0.004903132814959179</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01289321988178325</v>
+        <v>0.004128073387021959</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01417609996513262</v>
+        <v>0.004482059417016088</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0144974947627242</v>
+        <v>0.005922498545241191</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02233356833625254</v>
+        <v>0.007236283160802742</v>
       </c>
     </row>
     <row r="4">
@@ -5347,34 +5347,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007928842574451988</v>
+        <v>0.007928842574451991</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00746995913182611</v>
+        <v>0.007469959131826111</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00942850595873152</v>
+        <v>0.00942850595873153</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007479741700414103</v>
+        <v>0.007479741700414105</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007479741700414103</v>
+        <v>0.007479741700414104</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008783352977783432</v>
+        <v>0.008783352977783447</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008752207718891241</v>
+        <v>0.008752207718891238</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007506431634965854</v>
+        <v>0.007506431634965857</v>
       </c>
       <c r="J4" t="n">
         <v>0.008228787123062938</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007734261920201808</v>
+        <v>0.00773426192020181</v>
       </c>
       <c r="L4" t="n">
         <v>0.01241077555525388</v>
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02577583285292865</v>
+        <v>0.02577583285292867</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01881895945581311</v>
+        <v>0.0188189594558131</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0503173805415228</v>
+        <v>0.05031738054152301</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01881896045511459</v>
+        <v>0.01881896045511457</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01881896045511459</v>
+        <v>0.01881896045511458</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04062627770321108</v>
+        <v>0.04062627770321123</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04383336152710037</v>
+        <v>0.04383336152710027</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01881862107907959</v>
+        <v>0.01881862107907958</v>
       </c>
       <c r="J5" t="n">
         <v>0.03241370670520304</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02191862284048519</v>
+        <v>0.02191862284048524</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05387310004853713</v>
+        <v>0.05387310004853719</v>
       </c>
     </row>
     <row r="6">
@@ -5427,34 +5427,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.009074796799491448</v>
+        <v>0.008233072589996629</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007775063452505638</v>
+        <v>0.007775063452505639</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009768631013408226</v>
+        <v>0.009768631013408241</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007750858487630789</v>
+        <v>0.007750858487630791</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007807575708397124</v>
+        <v>0.007807575708397125</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009929307202822894</v>
+        <v>0.009087582993328087</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009918887089316158</v>
+        <v>0.009918887089316156</v>
       </c>
       <c r="I6" t="n">
         <v>0.008652385860005312</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009380853257483938</v>
+        <v>0.008561996699609969</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00802037043173944</v>
+        <v>0.008020370431739442</v>
       </c>
       <c r="L6" t="n">
         <v>0.01278207313745395</v>
@@ -5470,34 +5470,34 @@
         <v>0.008584290168516775</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008162217605764155</v>
+        <v>0.008162217605764159</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01008393098829422</v>
+        <v>0.01008393098829423</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008161070405668325</v>
+        <v>0.008161070405668326</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008161070405668325</v>
+        <v>0.008161070405668326</v>
       </c>
       <c r="G7" t="n">
-        <v>0.009438800571848226</v>
+        <v>0.009438800571848229</v>
       </c>
       <c r="H7" t="n">
         <v>0.00940765531295602</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008161879229030642</v>
+        <v>0.008161879229030644</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008884234717127721</v>
+        <v>0.008884234717127725</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008389709514266592</v>
+        <v>0.008389709514266595</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01306622314931866</v>
+        <v>0.01306622314931867</v>
       </c>
     </row>
     <row r="8">
@@ -5507,34 +5507,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009881295917060291</v>
+        <v>0.009881295917060294</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0108043974521817</v>
+        <v>0.01080439745218171</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01300603742814754</v>
+        <v>0.01300603742814756</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01043636580391778</v>
+        <v>0.01043636580391779</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009501218356106702</v>
+        <v>0.009501218356106705</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01208178665630506</v>
+        <v>0.01208178665630508</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01205064139741283</v>
+        <v>0.01205064139741284</v>
       </c>
       <c r="I8" t="n">
         <v>0.01080486531348749</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0115274853252333</v>
+        <v>0.01152748532523331</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009661712987048878</v>
+        <v>0.009661712987048883</v>
       </c>
       <c r="L8" t="n">
         <v>0.01711519824363131</v>
@@ -5547,16 +5547,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01024457163511155</v>
+        <v>0.01024457163511156</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01050880694012645</v>
+        <v>0.01050880694012646</v>
       </c>
       <c r="D9" t="n">
         <v>0.0124305434926907</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01130079254630948</v>
+        <v>0.01130079254630949</v>
       </c>
       <c r="F9" t="n">
         <v>0.01050880740516156</v>
@@ -5568,16 +5568,16 @@
         <v>0.01175424464731831</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01050846856339293</v>
+        <v>0.01050846856339294</v>
       </c>
       <c r="J9" t="n">
         <v>0.01123082405149002</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009872114580647604</v>
+        <v>0.01033864962938985</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01541281248368097</v>
+        <v>0.01541281248368096</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01223431946884175</v>
+        <v>0.004051201717818829</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01201473319210535</v>
+        <v>0.003680347556236706</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01432722610632336</v>
+        <v>0.004161347237302088</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01211038271108613</v>
+        <v>0.003762579734028465</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01174899598331298</v>
+        <v>0.00346176804217681</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01352500499289341</v>
+        <v>0.004119127933441735</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01375085736760865</v>
+        <v>0.004129684961824139</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01247189338317091</v>
+        <v>0.004063714495274927</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01207625977718565</v>
+        <v>0.003905901864257104</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01321635294826604</v>
+        <v>0.00505072870272704</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01896964901551012</v>
+        <v>0.004408670350461534</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0132781383211687</v>
+        <v>0.004251542813383948</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01309381626597537</v>
+        <v>0.003708985197072724</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01568541449857642</v>
+        <v>0.005033137326609444</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01318991464652828</v>
+        <v>0.003842635642788141</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01282852791875515</v>
+        <v>0.003346093746596634</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01476269403852896</v>
+        <v>0.00473531422882689</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0150229158050565</v>
+        <v>0.004824285036038304</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01355064202172685</v>
+        <v>0.004339667914947306</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0131227246528253</v>
+        <v>0.004019766600035593</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01422509021226992</v>
+        <v>0.005832973461913431</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02102492806098279</v>
+        <v>0.006802354745242691</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007768348131354499</v>
+        <v>0.007768348131354503</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007858228628864948</v>
+        <v>0.007858228628864953</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009012492443360238</v>
+        <v>0.009012492443360243</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007867482356117924</v>
+        <v>0.007867482356117932</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00786748235611792</v>
+        <v>0.007867482356117932</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00853216133936035</v>
+        <v>0.008532161339360342</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008669914686511921</v>
+        <v>0.008669914686511926</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007886402629941626</v>
+        <v>0.007886402629941624</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007778819994674036</v>
+        <v>0.007778819994674042</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007629509748416538</v>
+        <v>0.007629509748416544</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01177124144113405</v>
+        <v>0.01177124144113409</v>
       </c>
     </row>
     <row r="5">
@@ -5786,34 +5786,34 @@
         <v>0.02258126341386269</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02444686264135274</v>
+        <v>0.02444686264135276</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04224386607574079</v>
+        <v>0.04224386607574084</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02444686354754873</v>
+        <v>0.02444686354754874</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02444686354754873</v>
+        <v>0.02444686354754874</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03561873994915047</v>
+        <v>0.03561873994915044</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04081740352225806</v>
+        <v>0.04081740352225807</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02444667034690802</v>
+        <v>0.02444667034690814</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02431154223118628</v>
+        <v>0.02431154223118627</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01958888405793128</v>
+        <v>0.01958888405793123</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1029615939628124</v>
+        <v>0.03976513271960812</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008074662770412178</v>
+        <v>0.008074662770412185</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008175256140958608</v>
+        <v>0.008175256140958612</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01013470948229207</v>
+        <v>0.009344481407279179</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008150728155162854</v>
+        <v>0.008150728155162849</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00819418547867806</v>
+        <v>0.008194185478678057</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008838475978418036</v>
+        <v>0.00964675077683615</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0098055924104134</v>
+        <v>0.009805592410413401</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009000992067417442</v>
+        <v>0.008192717268999313</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008112469374371184</v>
+        <v>0.00889849424868821</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007919342507425743</v>
+        <v>0.007919342507425748</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01210241724999038</v>
+        <v>0.01210241724999039</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008412175654859457</v>
+        <v>0.008412175654859463</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008530422447891211</v>
+        <v>0.008530422447891204</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009656297020288829</v>
+        <v>0.009656297020288822</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00852918941013962</v>
+        <v>0.008529189410139623</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00852918941013962</v>
+        <v>0.008529189410139623</v>
       </c>
       <c r="G7" t="n">
-        <v>0.009175988862865301</v>
+        <v>0.009175988862865294</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00931374221001688</v>
+        <v>0.009313742210016889</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00853023015344659</v>
+        <v>0.008530230153446589</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008422647518178996</v>
+        <v>0.008422647518179</v>
       </c>
       <c r="K7" t="n">
         <v>0.0082733372719215</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01241506896463906</v>
+        <v>0.01241506896463905</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009691638475757148</v>
+        <v>0.009691638475757165</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01113320365913205</v>
+        <v>0.01113320365913206</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01253457673057043</v>
+        <v>0.01253457673057045</v>
       </c>
       <c r="E8" t="n">
         <v>0.01077113470914961</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009851139178372516</v>
+        <v>0.009851139178372515</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01177966199260693</v>
+        <v>0.01177966199260694</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01191741533975859</v>
+        <v>0.0119174153397586</v>
       </c>
       <c r="I8" t="n">
         <v>0.01113390328318821</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01102658089314602</v>
+        <v>0.01102658089314603</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009528202206486397</v>
+        <v>0.009528202206486402</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01640199049059305</v>
+        <v>0.01640199049059307</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009909100648228145</v>
+        <v>0.009909100648228144</v>
       </c>
       <c r="C9" t="n">
         <v>0.0106638545163695</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01178975247552579</v>
+        <v>0.01178975247552581</v>
       </c>
       <c r="E9" t="n">
         <v>0.01139837088316616</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01066385493787646</v>
+        <v>0.01066385493787647</v>
       </c>
       <c r="G9" t="n">
         <v>0.01130942093134361</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01144717427849519</v>
+        <v>0.0114471742784952</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01066366222192488</v>
+        <v>0.01066366222192489</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0105560795866573</v>
+        <v>0.01055607958665731</v>
       </c>
       <c r="K9" t="n">
         <v>0.01003797482646409</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01454850103311735</v>
+        <v>0.01454850103311737</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01098320787300421</v>
+        <v>0.003810302007135876</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01045856754944295</v>
+        <v>0.003444433337606493</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01190029388881423</v>
+        <v>0.003858566422668415</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0105707978550061</v>
+        <v>0.003539356336815676</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01015593143385691</v>
+        <v>0.003194028384268786</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01165048725449468</v>
+        <v>0.003845419595660118</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0118017009204923</v>
+        <v>0.003852518385483937</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01089012113826707</v>
+        <v>0.003805415228404881</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01185825687781417</v>
+        <v>0.003779206270027398</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01249637197738332</v>
+        <v>0.004826087820460349</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02015775435914466</v>
+        <v>0.004298746806130244</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01184310763968757</v>
+        <v>0.003684935257111855</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01130409087450329</v>
+        <v>0.003055806153674161</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01289794653166495</v>
+        <v>0.004026590666558584</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01141675012397378</v>
+        <v>0.003211210271274389</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0110018837028246</v>
+        <v>0.002641187045922013</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01261061715490906</v>
+        <v>0.00393449778262087</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0127849630327529</v>
+        <v>0.003991795965272399</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01173547254505786</v>
+        <v>0.003650342901890639</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01286445679657013</v>
+        <v>0.003915609583711478</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01340322237916931</v>
+        <v>0.005451089279469392</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02239532260736858</v>
+        <v>0.007148176314394711</v>
       </c>
     </row>
     <row r="4">
@@ -6139,19 +6139,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00695952348765451</v>
+        <v>0.006959523487654514</v>
       </c>
       <c r="C4" t="n">
-        <v>0.006846224153244898</v>
+        <v>0.006846224153244899</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007504692263822657</v>
+        <v>0.007504692263822656</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006855679968392449</v>
+        <v>0.006855679968392448</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006855679968392449</v>
+        <v>0.006855679968392448</v>
       </c>
       <c r="G4" t="n">
         <v>0.007352534715877324</v>
@@ -6163,10 +6163,10 @@
         <v>0.006879616468928208</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007538518838442971</v>
+        <v>0.007538518838442972</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007145334637238942</v>
+        <v>0.007145334637238943</v>
       </c>
       <c r="L4" t="n">
         <v>0.01241164659198158</v>
@@ -6179,13 +6179,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01216606639497785</v>
+        <v>0.01216606639497793</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01125623358556565</v>
+        <v>0.01125623358556564</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02091120526923967</v>
+        <v>0.0209112052692397</v>
       </c>
       <c r="E5" t="n">
         <v>0.01125623461917702</v>
@@ -6194,19 +6194,19 @@
         <v>0.01125623461917702</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01906558975750386</v>
+        <v>0.01906558975750385</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02150898616366845</v>
+        <v>0.02150898616366844</v>
       </c>
       <c r="I5" t="n">
         <v>0.0112560792998184</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02354589410442999</v>
+        <v>0.02354589410443003</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01521355485871345</v>
+        <v>0.01521355485871349</v>
       </c>
       <c r="L5" t="n">
         <v>0.1222331581089945</v>
@@ -6219,34 +6219,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007216299054172008</v>
+        <v>0.007992927156912211</v>
       </c>
       <c r="C6" t="n">
         <v>0.007116219376706119</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008545409975368306</v>
+        <v>0.008545409975368302</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007093765633624346</v>
+        <v>0.007093765633624348</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007133619038129362</v>
+        <v>0.007133619038129364</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00760931028239482</v>
+        <v>0.008385938385135024</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008500369481410076</v>
+        <v>0.007704531736763733</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007136392035445702</v>
+        <v>0.007913020138185902</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008577135928244033</v>
+        <v>0.00857713592824403</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007397958583543637</v>
+        <v>0.007397958583543638</v>
       </c>
       <c r="L6" t="n">
         <v>0.01271241347045315</v>
@@ -6262,31 +6262,31 @@
         <v>0.007572250308331092</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007492497575352032</v>
+        <v>0.00749249757535203</v>
       </c>
       <c r="D7" t="n">
         <v>0.008117396200191862</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007491443425128587</v>
+        <v>0.007491443425128585</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007491443425128587</v>
+        <v>0.007491443425128586</v>
       </c>
       <c r="G7" t="n">
         <v>0.007965261536553907</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008058867724475859</v>
+        <v>0.008058867724475857</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007492343289604788</v>
+        <v>0.007492343289604787</v>
       </c>
       <c r="J7" t="n">
         <v>0.008151245659119552</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007758061457915522</v>
+        <v>0.007758061457915521</v>
       </c>
       <c r="L7" t="n">
         <v>0.01302437341265816</v>
@@ -6299,7 +6299,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008889636225254427</v>
+        <v>0.008889636225254433</v>
       </c>
       <c r="C8" t="n">
         <v>0.01013032355477694</v>
@@ -6311,10 +6311,10 @@
         <v>0.009769070348260606</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00885114749149808</v>
+        <v>0.008851147491498077</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0106038090430792</v>
+        <v>0.01060380904307921</v>
       </c>
       <c r="H8" t="n">
         <v>0.01069741523100113</v>
@@ -6323,10 +6323,10 @@
         <v>0.01013089079613009</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01079005281174447</v>
+        <v>0.01079005281174446</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00905090612002747</v>
+        <v>0.009050906120027475</v>
       </c>
       <c r="L8" t="n">
         <v>0.01704298467325074</v>
@@ -6351,22 +6351,22 @@
         <v>0.01028533198151454</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009574383121840632</v>
+        <v>0.009574383121840634</v>
       </c>
       <c r="G9" t="n">
         <v>0.01004714643243673</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01014075262035868</v>
+        <v>0.01014075262035869</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009574228185487614</v>
+        <v>0.009574228185487612</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01023313055500237</v>
+        <v>0.01023313055500238</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009482984502362783</v>
+        <v>0.00948298450236278</v>
       </c>
       <c r="L9" t="n">
         <v>0.01510625830854096</v>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01076560097037803</v>
+        <v>0.003735753536495974</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01047899637512499</v>
+        <v>0.003384528166911628</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01083550387510364</v>
+        <v>0.003739432387533327</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01058858455687268</v>
+        <v>0.003476861830325041</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01018239510713028</v>
+        <v>0.00313875611680517</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01098019796047418</v>
+        <v>0.003747047349860783</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01075596791210609</v>
+        <v>0.003734360170274652</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01090821056394085</v>
+        <v>0.003743277506314697</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01113143547107381</v>
+        <v>0.003667184582981156</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01223075488704294</v>
+        <v>0.004744657311391564</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01061928362880106</v>
+        <v>0.003727234430228849</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01161052620440992</v>
+        <v>0.003566498846899688</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01134503601241642</v>
+        <v>0.003028595209732529</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01169092902518747</v>
+        <v>0.0035925479058863</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0114549841726264</v>
+        <v>0.003180180324548614</v>
       </c>
       <c r="F3" t="n">
-        <v>0.011048794722884</v>
+        <v>0.002622078861631235</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01185735719665309</v>
+        <v>0.003646699785423314</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01159984326988105</v>
+        <v>0.003562801657198942</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01177443528677108</v>
+        <v>0.00361990078536141</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01204822945843083</v>
+        <v>0.003591232694549591</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01311625828628834</v>
+        <v>0.005309101401927201</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01144226837579673</v>
+        <v>0.003511650252813211</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006807473655318206</v>
+        <v>0.006807473655318209</v>
       </c>
       <c r="C4" t="n">
-        <v>0.006847828191011251</v>
+        <v>0.00684782819101125</v>
       </c>
       <c r="D4" t="n">
         <v>0.006849027970140248</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006855660403099943</v>
+        <v>0.006855660403099944</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006855660403099943</v>
+        <v>0.006855660403099944</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006931795928545537</v>
+        <v>0.006931795928545541</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006801888806083003</v>
+        <v>0.006801888806083005</v>
       </c>
       <c r="I4" t="n">
         <v>0.006870508968657384</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007091900386614881</v>
+        <v>0.00709190038661488</v>
       </c>
       <c r="K4" t="n">
         <v>0.006968065210892812</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006720753286281245</v>
+        <v>0.006720753286281246</v>
       </c>
     </row>
     <row r="5">
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01010512053080407</v>
+        <v>0.01010512053080406</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01143244038869505</v>
+        <v>0.01143244038869506</v>
       </c>
       <c r="D5" t="n">
         <v>0.01073276098198354</v>
@@ -6590,16 +6590,16 @@
         <v>0.01143244127007103</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01214899884514015</v>
+        <v>0.01214899884514021</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01038492558917361</v>
+        <v>0.01038492558917362</v>
       </c>
       <c r="I5" t="n">
         <v>0.01143238167277667</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01501613228603873</v>
+        <v>0.01501613228603872</v>
       </c>
       <c r="K5" t="n">
         <v>0.01254151951975576</v>
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007711424471134551</v>
+        <v>0.007711424471134552</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007095683641938211</v>
+        <v>0.007095683641938212</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007080309865095656</v>
+        <v>0.007080312080932169</v>
       </c>
       <c r="E6" t="n">
         <v>0.007074780672843659</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007103064201708676</v>
+        <v>0.007103064201708674</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007165356362990409</v>
+        <v>0.007835746744361879</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007033523882949256</v>
+        <v>0.007718828832827583</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007104069403102253</v>
+        <v>0.007774459784473726</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007997132695195319</v>
+        <v>0.007345821181932893</v>
       </c>
       <c r="K6" t="n">
         <v>0.007203006949618096</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006992949930921998</v>
+        <v>0.006992949930922</v>
       </c>
     </row>
     <row r="7">
@@ -6655,13 +6655,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007348003680754681</v>
+        <v>0.007348003680754683</v>
       </c>
       <c r="C7" t="n">
         <v>0.007411097710012254</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007389536477865757</v>
+        <v>0.007389536477865758</v>
       </c>
       <c r="E7" t="n">
         <v>0.00741021721568927</v>
@@ -6670,22 +6670,22 @@
         <v>0.00741021721568927</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007472325953982012</v>
+        <v>0.007472325953982015</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007342418831519475</v>
+        <v>0.007342418831519477</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007411038994093857</v>
+        <v>0.007411038994093858</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00763243041205135</v>
+        <v>0.007632430412051352</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007508595236329283</v>
+        <v>0.007508595236329282</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007261283311717718</v>
+        <v>0.00726128331171772</v>
       </c>
     </row>
     <row r="8">
@@ -6695,10 +6695,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00854067587836152</v>
+        <v>0.008540675878361522</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009785601351964553</v>
+        <v>0.009785601351964549</v>
       </c>
       <c r="D8" t="n">
         <v>0.01000982766273774</v>
@@ -6707,22 +6707,22 @@
         <v>0.009462279567394965</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008640738598370962</v>
+        <v>0.008640738598370957</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009847413993581335</v>
+        <v>0.009847413993581336</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009717506871118664</v>
+        <v>0.009717506871118662</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009786127033693177</v>
+        <v>0.009786127033693175</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01000775083027342</v>
+        <v>0.01000775083027343</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008679303452615443</v>
+        <v>0.008679303452615438</v>
       </c>
       <c r="L8" t="n">
         <v>0.01087150357031028</v>
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008514272382451371</v>
+        <v>0.008514272382451372</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009084714865785241</v>
+        <v>0.009084714865785245</v>
       </c>
       <c r="D9" t="n">
-        <v>0.009063175377845152</v>
+        <v>0.009063175377845158</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0096701851711141</v>
+        <v>0.009670185171114102</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009084715635742579</v>
+        <v>0.009084715635742582</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009145943109755006</v>
+        <v>0.009145943109755011</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009016035987292469</v>
+        <v>0.009016035987292474</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00908465614986685</v>
+        <v>0.009084656149866852</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009306047567824346</v>
+        <v>0.009306047567824353</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008876326479417886</v>
+        <v>0.008888252800562428</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00893490046749071</v>
+        <v>0.008934900467490717</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01090371668997541</v>
+        <v>0.003737615444589607</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01050805364373025</v>
+        <v>0.003342788710848094</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01076805288768575</v>
+        <v>0.003730475728125117</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01059550745310778</v>
+        <v>0.003416666446528952</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01025849543870406</v>
+        <v>0.003136142066858155</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01094564940461695</v>
+        <v>0.003739822280076112</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0107439549999941</v>
+        <v>0.003728348532284278</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01098584977488233</v>
+        <v>0.003741957444808305</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01090581636652469</v>
+        <v>0.003564310509476584</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01215838643072381</v>
+        <v>0.004732950260682894</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01070941765124553</v>
+        <v>0.003726667696897294</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0117457305837587</v>
+        <v>0.003614657699818411</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01136211229073688</v>
+        <v>0.002987421033690785</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01158968910845361</v>
+        <v>0.003563984849260444</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01144991397636447</v>
+        <v>0.003108597237144886</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01111290196196076</v>
+        <v>0.002645544210529333</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01179396189193214</v>
+        <v>0.003630463931998158</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0115623547093407</v>
+        <v>0.003554889596561755</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0118401511555239</v>
+        <v>0.003645501712322987</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01178155189717806</v>
+        <v>0.003393715016761663</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01300984223529219</v>
+        <v>0.005275317009966239</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0115222677558822</v>
+        <v>0.003542217060324726</v>
       </c>
     </row>
     <row r="4">
@@ -6931,7 +6931,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006890431718400894</v>
+        <v>0.006890431718400892</v>
       </c>
       <c r="C4" t="n">
         <v>0.006899174292659013</v>
@@ -6940,28 +6940,28 @@
         <v>0.006809785336502626</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006906754233663091</v>
+        <v>0.006906754233663093</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006906754233663092</v>
+        <v>0.006906754233663093</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0069123269934609</v>
+        <v>0.006912326993460898</v>
       </c>
       <c r="H4" t="n">
         <v>0.006795596443184978</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0069189622550655</v>
+        <v>0.006918962255065499</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007023887977277951</v>
+        <v>0.007023887977277949</v>
       </c>
       <c r="K4" t="n">
-        <v>0.006927798886990098</v>
+        <v>0.006927798886990097</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006775158314020892</v>
+        <v>0.00677515831402089</v>
       </c>
     </row>
     <row r="5">
@@ -6974,34 +6974,34 @@
         <v>0.01144067427000038</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01221246783715787</v>
+        <v>0.01221246783715798</v>
       </c>
       <c r="D5" t="n">
         <v>0.01016131046257308</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0122124686420448</v>
+        <v>0.01221246864204486</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0122124686420448</v>
+        <v>0.01221246864204486</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01190750946552332</v>
+        <v>0.01190750946552327</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01029438858006778</v>
+        <v>0.01029438858006777</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01221242630699555</v>
+        <v>0.01221242630699553</v>
       </c>
       <c r="J5" t="n">
         <v>0.01396027850029754</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01185656339391464</v>
+        <v>0.01185656339391463</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00999133347813305</v>
+        <v>0.01197865544414644</v>
       </c>
     </row>
     <row r="6">
@@ -7011,34 +7011,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007127077789566904</v>
+        <v>0.007127077789566903</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007148843726609544</v>
+        <v>0.007148843726609538</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007041350515571318</v>
+        <v>0.007041350515571317</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007127804282891652</v>
+        <v>0.007127804282891653</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00715471322151057</v>
+        <v>0.007154713221510571</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00780731469333816</v>
+        <v>0.007148973064626911</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007700547471089659</v>
+        <v>0.007700547471089657</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007155608326231513</v>
+        <v>0.00715560832623151</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007917479076250853</v>
+        <v>0.007280057204633766</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00716478753072967</v>
+        <v>0.007164787530729669</v>
       </c>
       <c r="L6" t="n">
         <v>0.007010614609783049</v>
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007428546964815864</v>
+        <v>0.007428546964815861</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007457119031642928</v>
+        <v>0.007457119031642925</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007347878888491747</v>
+        <v>0.007347878888491744</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007456230496496783</v>
+        <v>0.007456230496496782</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007456230496496783</v>
+        <v>0.007456230496496782</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007450442239875871</v>
+        <v>0.007450442239875869</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007333711689599949</v>
+        <v>0.007333711689599945</v>
       </c>
       <c r="I7" t="n">
         <v>0.007457077501480471</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00756200322369292</v>
+        <v>0.007562003223692919</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007465914133405071</v>
+        <v>0.007465914133405067</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00731327356043586</v>
+        <v>0.007313273560435858</v>
       </c>
     </row>
     <row r="8">
@@ -7094,34 +7094,34 @@
         <v>0.008618023756179597</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009823970801030958</v>
+        <v>0.009823970801030956</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009959604136722268</v>
+        <v>0.009959604136722273</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009501866223177025</v>
+        <v>0.009501866223177032</v>
       </c>
       <c r="F8" t="n">
         <v>0.008683418786719996</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009817886554073459</v>
+        <v>0.00981788655407345</v>
       </c>
       <c r="H8" t="n">
         <v>0.009701156003797323</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009824521815678057</v>
+        <v>0.009824521815678054</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009929679042304223</v>
+        <v>0.009929679042304218</v>
       </c>
       <c r="K8" t="n">
         <v>0.008633509573259012</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01091120345231562</v>
+        <v>0.01091120345231561</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008523780265212104</v>
+        <v>0.0085237802652121</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009039003162572291</v>
+        <v>0.009039003162572286</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008929784922111416</v>
+        <v>0.008929784922111409</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009600588763433279</v>
+        <v>0.009600588763433273</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009039003861808505</v>
+        <v>0.0090390038618085</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009032326370805241</v>
+        <v>0.009032326370805236</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008915595820529316</v>
+        <v>0.008915595820529313</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00903896163240984</v>
+        <v>0.009038961632409834</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009143887354622288</v>
+        <v>0.009143887354622281</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008754391170902764</v>
+        <v>0.008754391170902761</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008895157691365226</v>
+        <v>0.008895157691365221</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01207470518839615</v>
+        <v>0.004028374631516374</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0108750356692556</v>
+        <v>0.003619892575535576</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01509424905501346</v>
+        <v>0.004187287227919269</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01099315518897447</v>
+        <v>0.003720803901266856</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01056118415941661</v>
+        <v>0.003361239772458639</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01358647242813282</v>
+        <v>0.004107935938732133</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01415118242967336</v>
+        <v>0.004136499608300662</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01131456189816136</v>
+        <v>0.003988367628291727</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0125987006337638</v>
+        <v>0.003991530573406901</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01311875338261397</v>
+        <v>0.005022797318668746</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01933001786015713</v>
+        <v>0.004413415793489512</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0131011911617272</v>
+        <v>0.004182437938525395</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01178680266184726</v>
+        <v>0.003292511871213023</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01657429210496468</v>
+        <v>0.005310413297572274</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01190545600746164</v>
+        <v>0.003456661533454264</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01147348497790379</v>
+        <v>0.002863138126713388</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01484003664906464</v>
+        <v>0.004749098521386684</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01549004391536211</v>
+        <v>0.004962622562226691</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01222539352602803</v>
+        <v>0.00389827958920196</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0137163043254632</v>
+        <v>0.004299256384882637</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01412108481031427</v>
+        <v>0.005777955149866461</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02144605370085091</v>
+        <v>0.006930280511294353</v>
       </c>
     </row>
     <row r="4">
@@ -7327,34 +7327,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007647500148637596</v>
+        <v>0.007647500148637592</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007124070808957962</v>
+        <v>0.007124070808957959</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009442491028414357</v>
+        <v>0.009442491028414353</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007134662669695889</v>
+        <v>0.007134662669695885</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007134662669695887</v>
+        <v>0.007134662669695885</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008541970569044242</v>
+        <v>0.008541970569044231</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008881848762017926</v>
+        <v>0.008881848762017908</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007167164444399387</v>
+        <v>0.007167164444399385</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008008106303602824</v>
+        <v>0.008008106303602823</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007551906470692089</v>
+        <v>0.007551906470692087</v>
       </c>
       <c r="L4" t="n">
         <v>0.01195943593818989</v>
@@ -7367,13 +7367,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02230195469674199</v>
+        <v>0.02230195469674195</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01449338897432507</v>
+        <v>0.01449338897432505</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0527979075820213</v>
+        <v>0.05279790758202128</v>
       </c>
       <c r="E5" t="n">
         <v>0.01449339005730329</v>
@@ -7382,22 +7382,22 @@
         <v>0.01449339005730329</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03863787749877261</v>
+        <v>0.03863787749877247</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04642691166328769</v>
+        <v>0.0464269116632876</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01449302743733433</v>
+        <v>0.01449302743733431</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03050215120127246</v>
+        <v>0.03050215120127245</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0207568357873686</v>
+        <v>0.02075683578736856</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1149770616879683</v>
+        <v>0.0385878015544612</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007945743878252051</v>
+        <v>0.007945743878252047</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007424585303704496</v>
+        <v>0.007424585303704493</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009788966134012906</v>
+        <v>0.00978896613401292</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007400382674968262</v>
+        <v>0.007400382674968257</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007461725476325236</v>
+        <v>0.007461725476325233</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009707997642401968</v>
+        <v>0.009707997642401961</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0100767572452917</v>
+        <v>0.01007675724529168</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008333191517757112</v>
+        <v>0.008333191517757101</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00918522558717327</v>
+        <v>0.009185225587173267</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007831777387791157</v>
+        <v>0.007831777387791139</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01229838575011836</v>
+        <v>0.01229838575011835</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00833539241342254</v>
+        <v>0.008335392413422531</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007855418246175081</v>
+        <v>0.00785541824617508</v>
       </c>
       <c r="D7" t="n">
         <v>0.0101303594921313</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007854430480674954</v>
+        <v>0.007854430480674947</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007854430480674954</v>
+        <v>0.007854430480674947</v>
       </c>
       <c r="G7" t="n">
-        <v>0.009229862833829188</v>
+        <v>0.009229862833829183</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009569741026802869</v>
+        <v>0.009569741026802858</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007855056709184332</v>
+        <v>0.007855056709184328</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008695998568387771</v>
+        <v>0.008695998568387762</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008239798735477036</v>
+        <v>0.008239798735477031</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01264732820297483</v>
+        <v>0.01264732820297482</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009718536994734482</v>
+        <v>0.009718536994734467</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0106643458274194</v>
+        <v>0.01066434582741483</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01323572456904881</v>
+        <v>0.01323572456904879</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01027429644568015</v>
+        <v>0.01027429644568014</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009283203503734294</v>
+        <v>0.009283203503734287</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01203942676519176</v>
+        <v>0.01203942676519175</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01237930495816535</v>
+        <v>0.01237930495816533</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01066462064054691</v>
+        <v>0.01066462064054689</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01150584283196985</v>
+        <v>0.01150584283196983</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00959644684504259</v>
+        <v>0.009596446845042574</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01694690642065958</v>
+        <v>0.01694690642065955</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01018381572738611</v>
+        <v>0.01018381572738609</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0104533703239603</v>
+        <v>0.01045337032396028</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01272833589903814</v>
+        <v>0.01272833589903811</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01131831138459767</v>
+        <v>0.01131831138459765</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01045337076648781</v>
+        <v>0.0104533707664878</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0118278149116144</v>
+        <v>0.01182781491161438</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01216769310458808</v>
+        <v>0.01216769310458807</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01045300878696955</v>
+        <v>0.01045300878696954</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01129395064617298</v>
+        <v>0.01129395064617297</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01040347112597468</v>
+        <v>0.01040347112597467</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01524528028076005</v>
+        <v>0.01524528028076004</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0107587493865747</v>
+        <v>0.003862447508079034</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01047864801154898</v>
+        <v>0.003500574923843658</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01410092503972193</v>
+        <v>0.004038339574608663</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01059312116403733</v>
+        <v>0.003597633712174273</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01017301559142067</v>
+        <v>0.003247945410882733</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0121790524886091</v>
+        <v>0.003937195239389929</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01115875822739406</v>
+        <v>0.00388181693770135</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01092132598573814</v>
+        <v>0.003871011055767752</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01141355258932307</v>
+        <v>0.003815344270494815</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01220508478675639</v>
+        <v>0.004858119373706295</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06238118673877097</v>
+        <v>0.006615537072929692</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01161524645261317</v>
+        <v>0.003647825818789808</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01135913364282607</v>
+        <v>0.00309896816770809</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01545944078333332</v>
+        <v>0.004894171061129252</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01147405970131919</v>
+        <v>0.00325758228117252</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01105395412870254</v>
+        <v>0.00268036113693667</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01324888923485398</v>
+        <v>0.00417888915048921</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01207579307342604</v>
+        <v>0.003797023889766907</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01180135697631138</v>
+        <v>0.003708795035121632</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01238411807618537</v>
+        <v>0.00378960138968354</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01310169151502155</v>
+        <v>0.005367856196690966</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07098922958746015</v>
+        <v>0.023145782198597</v>
       </c>
     </row>
     <row r="4">
@@ -7726,31 +7726,31 @@
         <v>0.006831389147698159</v>
       </c>
       <c r="C4" t="n">
-        <v>0.006872171943562042</v>
+        <v>0.006872171943562039</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008818170953498471</v>
+        <v>0.00881817095349847</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00688097640821345</v>
+        <v>0.006880976408213453</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00688097640821345</v>
+        <v>0.006880976408213452</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007671989093756079</v>
+        <v>0.007671989093756076</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007069509060084766</v>
+        <v>0.007069509060084763</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006903042755593195</v>
+        <v>0.006903042755593194</v>
       </c>
       <c r="J4" t="n">
         <v>0.007282824668393939</v>
       </c>
       <c r="K4" t="n">
-        <v>0.006990126562676491</v>
+        <v>0.006990126562676492</v>
       </c>
       <c r="L4" t="n">
         <v>0.03750739791822223</v>
@@ -7763,13 +7763,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009321860706411276</v>
+        <v>0.009321860706411278</v>
       </c>
       <c r="C5" t="n">
         <v>0.01093047686430523</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03979465590689231</v>
+        <v>0.03979465590689234</v>
       </c>
       <c r="E5" t="n">
         <v>0.01093047781757015</v>
@@ -7778,22 +7778,22 @@
         <v>0.01093047781757015</v>
       </c>
       <c r="G5" t="n">
-        <v>0.022999678170728</v>
+        <v>0.02299967817072803</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01376832576984353</v>
+        <v>0.01376832576984355</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01093025555534951</v>
+        <v>0.0109302555553495</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01744066348140746</v>
+        <v>0.01744066348140745</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01181361314116619</v>
+        <v>0.0118136131411662</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04401103584543409</v>
+        <v>0.5922869579646353</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007993004371862825</v>
+        <v>0.007993004371862827</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007130411061838954</v>
+        <v>0.007130411061838955</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009115222595053386</v>
+        <v>0.009115224914576867</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007108830124472368</v>
+        <v>0.007108830124472366</v>
       </c>
       <c r="F6" t="n">
         <v>0.00715238329476292</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00792389385429397</v>
+        <v>0.008833604317920749</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008240744544853606</v>
+        <v>0.008240744544853604</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008064657979757856</v>
+        <v>0.008064657979757859</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007557619267181834</v>
+        <v>0.007557619267181833</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007229020217068809</v>
+        <v>0.007229020217068807</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03796794040399044</v>
+        <v>0.03796794040399046</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007416594298344296</v>
+        <v>0.007416594298344295</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007488469215195056</v>
+        <v>0.007488469215195057</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009403354582570921</v>
+        <v>0.00940335458257092</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007487395931555767</v>
+        <v>0.007487395931555766</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007487395931555767</v>
+        <v>0.007487395931555766</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008257194244402209</v>
+        <v>0.008257194244402213</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007654714210730901</v>
+        <v>0.007654714210730898</v>
       </c>
       <c r="I7" t="n">
         <v>0.007488247906239327</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007868029819040077</v>
+        <v>0.007868029819040074</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007575331713322631</v>
+        <v>0.00757533171332263</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03809260306886823</v>
+        <v>0.03809260306886824</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008667371866934991</v>
+        <v>0.008667371866934989</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009996238946086927</v>
+        <v>0.009996238946086923</v>
       </c>
       <c r="D8" t="n">
         <v>0.01217270171653754</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009652333086486871</v>
+        <v>0.009652333086486864</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008778488353079379</v>
+        <v>0.008778488353079383</v>
       </c>
       <c r="G8" t="n">
         <v>0.01076571799293111</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01016323795925973</v>
+        <v>0.01016323795925972</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009996771654768222</v>
+        <v>0.009996771654768217</v>
       </c>
       <c r="J8" t="n">
         <v>0.01037680075072221</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008802746000894479</v>
+        <v>0.008802746000894477</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04191494787336849</v>
+        <v>0.04191494787336852</v>
       </c>
     </row>
     <row r="9">
@@ -7923,10 +7923,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008775674650372821</v>
+        <v>0.008775674650372817</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009424939849017076</v>
+        <v>0.009424939849017077</v>
       </c>
       <c r="D9" t="n">
         <v>0.01133984663972226</v>
@@ -7941,16 +7941,16 @@
         <v>0.01019366487822423</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009591184844552916</v>
+        <v>0.009591184844552915</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009424718540061345</v>
+        <v>0.009424718540061347</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009804500452862099</v>
+        <v>0.009804500452862094</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008784764944028732</v>
+        <v>0.009177260108965699</v>
       </c>
       <c r="L9" t="n">
         <v>0.04002907370269033</v>

--- a/Results/Ammonia/ammonia acidification results.xlsx
+++ b/Results/Ammonia/ammonia acidification results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004235768894747247</v>
+        <v>0.004235768894747252</v>
       </c>
       <c r="C2" t="n">
         <v>0.00382364584719475</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004339583217067023</v>
+        <v>0.004339583217067025</v>
       </c>
       <c r="E2" t="n">
         <v>0.003933783179384065</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003546701698999105</v>
+        <v>0.003546701698999106</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004279915983776171</v>
+        <v>0.004279915983776173</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004413956654248839</v>
+        <v>0.004413956654248843</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004156552622777856</v>
+        <v>0.004156552622777857</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004256634592528541</v>
+        <v>0.004256634592528542</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005211147926762093</v>
+        <v>0.005211147926762095</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004807904440165377</v>
+        <v>0.004807904440165379</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00486047399501748</v>
+        <v>0.004860473995017483</v>
       </c>
       <c r="C3" t="n">
         <v>0.003751060903693246</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00560107221133615</v>
+        <v>0.005601072211336151</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003930004832794484</v>
+        <v>0.003930004832794483</v>
       </c>
       <c r="F3" t="n">
         <v>0.003291059109657877</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005177951605307814</v>
+        <v>0.005177951605307817</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00614697103931491</v>
+        <v>0.006146971039314912</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004297685013722431</v>
+        <v>0.004297685013722434</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005039659496385177</v>
+        <v>0.005039659496385176</v>
       </c>
       <c r="K3" t="n">
         <v>0.006171875364348662</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008938458990379891</v>
+        <v>0.008938458990379894</v>
       </c>
     </row>
     <row r="4">
@@ -604,19 +604,19 @@
         <v>0.009864820948032779</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007750085765902653</v>
+        <v>0.007750085765902655</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007750085765902654</v>
+        <v>0.007750085765902655</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009187203934614648</v>
+        <v>0.009187203934614644</v>
       </c>
       <c r="H4" t="n">
         <v>0.01070754691361769</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007772755109578579</v>
+        <v>0.00777275510957858</v>
       </c>
       <c r="J4" t="n">
         <v>0.00898063683113578</v>
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04069247268031644</v>
+        <v>0.04069247268031646</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02418347271651898</v>
+        <v>0.02418347271651906</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06411072611997459</v>
+        <v>0.06411072611997458</v>
       </c>
       <c r="E5" t="n">
-        <v>0.024183473512857</v>
+        <v>0.02418347351285701</v>
       </c>
       <c r="F5" t="n">
-        <v>0.024183473512857</v>
+        <v>0.02418347351285701</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05215583184832505</v>
+        <v>0.05215583184832488</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08919754554157916</v>
+        <v>0.08919754554157915</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02418310606139151</v>
+        <v>0.0241831060613916</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0492591195103426</v>
+        <v>0.04925911951034262</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0296976914388331</v>
+        <v>0.02969769143883315</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1891360860179326</v>
+        <v>0.189136086017933</v>
       </c>
     </row>
     <row r="6">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.009059756121580165</v>
+        <v>0.009059756121580166</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008097806649529988</v>
+        <v>0.008097806649529993</v>
       </c>
       <c r="D6" t="n">
         <v>0.01027655295556058</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008068853032051272</v>
+        <v>0.008068853032051269</v>
       </c>
       <c r="F6" t="n">
-        <v>0.008137766997870579</v>
+        <v>0.008137766997870581</v>
       </c>
       <c r="G6" t="n">
         <v>0.01056423575431633</v>
@@ -696,13 +696,13 @@
         <v>0.01211858749309576</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009149786929280271</v>
+        <v>0.009149786929280269</v>
       </c>
       <c r="J6" t="n">
         <v>0.01036325374830739</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008418664900131706</v>
+        <v>0.008418664900131724</v>
       </c>
       <c r="L6" t="n">
         <v>0.01549869542043363</v>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.009496021632035235</v>
+        <v>0.00949602163203524</v>
       </c>
       <c r="C7" t="n">
         <v>0.008576952976258063</v>
@@ -724,13 +724,13 @@
         <v>0.01066862481231049</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008576147444639338</v>
+        <v>0.00857614744463934</v>
       </c>
       <c r="F7" t="n">
         <v>0.00857614744463934</v>
       </c>
       <c r="G7" t="n">
-        <v>0.009991035146166683</v>
+        <v>0.009991035146166687</v>
       </c>
       <c r="H7" t="n">
         <v>0.01151137812516973</v>
@@ -739,10 +739,10 @@
         <v>0.008576586321130619</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009784468042687818</v>
+        <v>0.00978446804268782</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008876009467633228</v>
+        <v>0.00887600946763323</v>
       </c>
       <c r="L7" t="n">
         <v>0.01588755920905081</v>
@@ -758,10 +758,10 @@
         <v>0.01104565752780206</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01175251753433258</v>
+        <v>0.01175251753433259</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01418186842746348</v>
+        <v>0.01418186842746349</v>
       </c>
       <c r="E8" t="n">
         <v>0.01130776549315569</v>
@@ -770,13 +770,13 @@
         <v>0.01017767765011141</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01316701781582189</v>
+        <v>0.01316701781582191</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01468736079482487</v>
+        <v>0.01468736079482488</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01175256899078583</v>
+        <v>0.01175256899078584</v>
       </c>
       <c r="J8" t="n">
         <v>0.01296077033600104</v>
@@ -785,7 +785,7 @@
         <v>0.01039543513711599</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02076239707685737</v>
+        <v>0.02076239707685738</v>
       </c>
     </row>
     <row r="9">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01198921646367784</v>
+        <v>0.01198921646367785</v>
       </c>
       <c r="C9" t="n">
         <v>0.01203896674657278</v>
@@ -804,16 +804,16 @@
         <v>0.01413066622381868</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01315696284994239</v>
+        <v>0.0131569628499424</v>
       </c>
       <c r="F9" t="n">
         <v>0.01203896636562039</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0134530489164814</v>
+        <v>0.01345304891648141</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01497339189548445</v>
+        <v>0.01497339189548446</v>
       </c>
       <c r="I9" t="n">
         <v>0.01203860009144534</v>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003731512726685843</v>
+        <v>0.003731512726685845</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003348149684531079</v>
+        <v>0.003348149684531082</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003746141162360489</v>
+        <v>0.00374614116236049</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003423145296892166</v>
+        <v>0.003423145296892165</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00313945065633407</v>
+        <v>0.003139450656334071</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003750955029176599</v>
+        <v>0.003750955029176598</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003741333138600976</v>
+        <v>0.003741333138600977</v>
       </c>
       <c r="I2" t="n">
         <v>0.003746739672235228</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003573709626722601</v>
+        <v>0.003573709626722602</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004739115102355512</v>
+        <v>0.004739115102355515</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003735112849133309</v>
+        <v>0.003735112849133282</v>
       </c>
     </row>
     <row r="3">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003524631207284798</v>
+        <v>0.003524631207284799</v>
       </c>
       <c r="C3" t="n">
         <v>0.002975756860390547</v>
@@ -960,28 +960,28 @@
         <v>0.003628483344180142</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003098702533401221</v>
+        <v>0.003098702533401222</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002630416358406574</v>
+        <v>0.002630416358406572</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003662927174273212</v>
+        <v>0.003662927174273211</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003600690430159077</v>
+        <v>0.003600690430159079</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003632806496192809</v>
+        <v>0.003632806496192811</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003385502142375546</v>
+        <v>0.003385502142375545</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005270109530697994</v>
+        <v>0.005270109530698004</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003555938943315706</v>
+        <v>0.003555938943315695</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006741070799962359</v>
+        <v>0.006741070799962355</v>
       </c>
       <c r="C4" t="n">
-        <v>0.006871366359934357</v>
+        <v>0.006871366359934355</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006906305710320309</v>
+        <v>0.006906305710320308</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006879132051031802</v>
+        <v>0.006879132051031798</v>
       </c>
       <c r="F4" t="n">
         <v>0.006879132051031799</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006957607683761963</v>
+        <v>0.006957607683761957</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006861889904463128</v>
+        <v>0.006861889904463125</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006892275642373216</v>
+        <v>0.006892275642373215</v>
       </c>
       <c r="J4" t="n">
-        <v>0.006990619851369397</v>
+        <v>0.006990619851369393</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00691210829267098</v>
+        <v>0.006912108292670975</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006790699328711648</v>
+        <v>0.006790699328711645</v>
       </c>
     </row>
     <row r="5">
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008966460674515286</v>
+        <v>0.008966460674515288</v>
       </c>
       <c r="C5" t="n">
         <v>0.01172854389294711</v>
@@ -1052,16 +1052,16 @@
         <v>0.01141188113496299</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01172848591186775</v>
+        <v>0.01172848591186776</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01345492239764987</v>
+        <v>0.01345492239764984</v>
       </c>
       <c r="K5" t="n">
         <v>0.01156181851670445</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01022949158302069</v>
+        <v>0.01022949158302067</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.006976672179273448</v>
+        <v>0.006976672179273444</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007120694341484981</v>
+        <v>0.00712069434148498</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007805098880796093</v>
+        <v>0.007805098880796092</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007099570112786855</v>
+        <v>0.007099570112786857</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007127917637280398</v>
+        <v>0.007127917637280397</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007851934436455621</v>
+        <v>0.007851934436455618</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007773812405427528</v>
+        <v>0.007773812405427525</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007127877021684307</v>
+        <v>0.007127877021684306</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00724691900252868</v>
+        <v>0.007246919002528677</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007148396269826663</v>
+        <v>0.007148396269826662</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0070264199634379</v>
+        <v>0.007026419963437896</v>
       </c>
     </row>
     <row r="7">
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007285092371397504</v>
+        <v>0.007285092371397501</v>
       </c>
       <c r="C7" t="n">
         <v>0.007436355194887715</v>
@@ -1129,19 +1129,19 @@
         <v>0.007501629255197107</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007405911475898273</v>
+        <v>0.007405911475898271</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007436297213808361</v>
+        <v>0.007436297213808359</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007534641422804542</v>
+        <v>0.007534641422804539</v>
       </c>
       <c r="K7" t="n">
         <v>0.007456129864106123</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007334720900146792</v>
+        <v>0.00733472090014679</v>
       </c>
     </row>
     <row r="8">
@@ -1163,25 +1163,25 @@
         <v>0.009493720991302598</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008668877549716097</v>
+        <v>0.008668877549716094</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00988426976393411</v>
+        <v>0.009884269763934108</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009788551984635333</v>
+        <v>0.009788551984635336</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009818937722545365</v>
+        <v>0.009818937722545367</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00991751524936038</v>
+        <v>0.009917515249360374</v>
       </c>
       <c r="K8" t="n">
         <v>0.0086295228400618</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01095748562847193</v>
+        <v>0.01095748562847194</v>
       </c>
     </row>
     <row r="9">
@@ -1191,34 +1191,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00838780938522468</v>
+        <v>0.008387809385224676</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009030158138385182</v>
+        <v>0.00903015813838518</v>
       </c>
       <c r="D9" t="n">
-        <v>0.009044130450056361</v>
+        <v>0.009044130450056366</v>
       </c>
       <c r="E9" t="n">
         <v>0.009596861759884584</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00903015883702421</v>
+        <v>0.009030158837024212</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009095432198694575</v>
+        <v>0.009095432198694579</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008999714419395743</v>
+        <v>0.008999714419395741</v>
       </c>
       <c r="I9" t="n">
         <v>0.009030100157305829</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009128444366302009</v>
+        <v>0.009128444366302016</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008765395785860799</v>
+        <v>0.008765395785860795</v>
       </c>
       <c r="L9" t="n">
         <v>0.008928523843644258</v>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004080067763402207</v>
+        <v>0.004080067763402211</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003325536295128344</v>
+        <v>0.003325536295128345</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004204917055951256</v>
+        <v>0.004204917055951259</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003422853713165743</v>
+        <v>0.003422853713165745</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003422848050184695</v>
+        <v>0.0034228480501847</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004152906820582435</v>
+        <v>0.004152906820582433</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00415307268750528</v>
+        <v>0.004153072687505282</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004096252722721213</v>
+        <v>0.004096252722721215</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004297741929978309</v>
+        <v>0.004297741929978317</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004786455297928078</v>
+        <v>0.004786455297928081</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004200500502878225</v>
+        <v>0.004200500502878228</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004239112342896161</v>
+        <v>0.004239112342896167</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003691448117312879</v>
+        <v>0.003691448117312881</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005129433167568509</v>
+        <v>0.005129433167568514</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003244160915033575</v>
+        <v>0.003244160915033577</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003244155252052536</v>
+        <v>0.003244155252052531</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004760072162258999</v>
+        <v>0.004760072162259001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004772360168441729</v>
+        <v>0.004772360168441736</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004355686325860917</v>
+        <v>0.004355686325860921</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005364954856330992</v>
+        <v>0.005364954856330991</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005516329008894818</v>
+        <v>0.005516329008894815</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00510724454344592</v>
+        <v>0.005107244543445921</v>
       </c>
     </row>
     <row r="4">
@@ -1387,28 +1387,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007100389967753606</v>
+        <v>0.007100389967753604</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008505230148742507</v>
+        <v>0.00850523014874251</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00851062016060722</v>
+        <v>0.008510620160607218</v>
       </c>
       <c r="E4" t="n">
         <v>0.007242075954449772</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007242075954449772</v>
+        <v>0.007242075954449771</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007919479933210171</v>
+        <v>0.007919479933210172</v>
       </c>
       <c r="H4" t="n">
         <v>0.007938518947853747</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007258497688006424</v>
+        <v>0.007258497688006422</v>
       </c>
       <c r="J4" t="n">
         <v>0.008674037244639905</v>
@@ -1417,7 +1417,7 @@
         <v>0.007327443957518645</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008462667660738346</v>
+        <v>0.008462667660738343</v>
       </c>
     </row>
     <row r="5">
@@ -1430,34 +1430,34 @@
         <v>0.01242990205404644</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03952254337585858</v>
+        <v>0.03952254337585857</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03828248394837134</v>
+        <v>0.03828248394837131</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01638949998596064</v>
+        <v>0.01638949998596066</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01638949998596064</v>
+        <v>0.01638949998596067</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02834753475998359</v>
+        <v>0.02834753475998355</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03069840435650492</v>
+        <v>0.030698404356505</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01638930185345791</v>
+        <v>0.01638930185345798</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04292423033887457</v>
+        <v>0.04292423033887455</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01715564385412096</v>
+        <v>0.01715564385412098</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04192075222085435</v>
+        <v>0.0419207522208544</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008209658390963456</v>
+        <v>0.008209658390963463</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008861564205952084</v>
+        <v>0.008861564205952088</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008849487510748348</v>
+        <v>0.008849487510748346</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007520493781330784</v>
+        <v>0.007520493781330616</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007567794547406051</v>
+        <v>0.007567794547406052</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008229503645768547</v>
+        <v>0.008229503645768552</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009084559683685673</v>
+        <v>0.009084559683685678</v>
       </c>
       <c r="I6" t="n">
         <v>0.007568521400564805</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009788056514966297</v>
+        <v>0.0097880565149663</v>
       </c>
       <c r="K6" t="n">
         <v>0.007624722575039909</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00878009533786455</v>
+        <v>0.008780095337864554</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007763031030300352</v>
+        <v>0.00776303103030035</v>
       </c>
       <c r="C7" t="n">
         <v>0.009195709462359423</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009173240290200332</v>
+        <v>0.00917324029020033</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007921226117563547</v>
+        <v>0.007921226117563551</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007921226117563547</v>
+        <v>0.007921226117563551</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008582120995756913</v>
+        <v>0.008582120995756917</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008601160010400486</v>
+        <v>0.008601160010400493</v>
       </c>
       <c r="I7" t="n">
         <v>0.007921138750553164</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009336678307186645</v>
+        <v>0.009336678307186654</v>
       </c>
       <c r="K7" t="n">
         <v>0.007990085020065386</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009125308723285092</v>
+        <v>0.009125308723285094</v>
       </c>
     </row>
     <row r="8">
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009116843845827796</v>
+        <v>0.009116843845827791</v>
       </c>
       <c r="C8" t="n">
         <v>0.0119386508828329</v>
@@ -1556,28 +1556,28 @@
         <v>0.01220401514552991</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01028439186833648</v>
+        <v>0.01028439186833647</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009319123240392748</v>
+        <v>0.009319123240392751</v>
       </c>
       <c r="G8" t="n">
         <v>0.01132486995968507</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01134390897432988</v>
+        <v>0.01134390897432989</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01066388771448132</v>
+        <v>0.01066388771448131</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01207970023680116</v>
+        <v>0.01207970023680117</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009318097633560231</v>
+        <v>0.009318097633560228</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01331891763511569</v>
+        <v>0.01331891763511568</v>
       </c>
     </row>
     <row r="9">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009378063864891737</v>
+        <v>0.009378063864891734</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01148752309909711</v>
+        <v>0.01148752309909712</v>
       </c>
       <c r="D9" t="n">
         <v>0.01146507517957267</v>
@@ -1602,10 +1602,10 @@
         <v>0.01021315003631805</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0108739346324946</v>
+        <v>0.01087393463249461</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01089297364713817</v>
+        <v>0.01089297364713818</v>
       </c>
       <c r="I9" t="n">
         <v>0.01021295238729085</v>
@@ -1614,10 +1614,10 @@
         <v>0.01162849194392433</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00988976933657279</v>
+        <v>0.009889769336572795</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01141712236002279</v>
+        <v>0.01141712236002278</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003956187071382694</v>
+        <v>0.003956187071382699</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003172957550628892</v>
+        <v>0.003172957550628894</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004042600026144846</v>
+        <v>0.004042600026144851</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003334971206519454</v>
+        <v>0.003334971206519459</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003334965591576239</v>
+        <v>0.003334965591576242</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003998993115391912</v>
+        <v>0.003998993115391918</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003994832228774507</v>
+        <v>0.003994832228774505</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003965834220688398</v>
+        <v>0.0039658342206884</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004160500902728752</v>
+        <v>0.004160500902728754</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004675926594509158</v>
+        <v>0.004675926594509152</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003983322075716175</v>
+        <v>0.003983322075716176</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004055649729367648</v>
+        <v>0.004055649729367649</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003177706383208643</v>
+        <v>0.003177706383208641</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004672303001874325</v>
+        <v>0.004672303001874327</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003084375030113715</v>
+        <v>0.003084375030113718</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003084369415170504</v>
+        <v>0.00308436941517051</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004362390578930947</v>
+        <v>0.004362390578930946</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004341295088015009</v>
+        <v>0.004341295088015007</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004125686811215153</v>
+        <v>0.004125686811215152</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004850170201301507</v>
+        <v>0.004850170201301511</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005254634299761486</v>
+        <v>0.005254634299761478</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004258562184380821</v>
+        <v>0.004258562184380817</v>
       </c>
     </row>
     <row r="4">
@@ -1786,34 +1786,34 @@
         <v>0.006947111712937395</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007768165776161694</v>
+        <v>0.007768165776161692</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007923185788899062</v>
+        <v>0.007923185788899056</v>
       </c>
       <c r="E4" t="n">
         <v>0.007039726238189532</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007039726238189533</v>
+        <v>0.007039726238189532</v>
       </c>
       <c r="G4" t="n">
         <v>0.007427257516871465</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007395306815699385</v>
+        <v>0.007395306815699383</v>
       </c>
       <c r="I4" t="n">
         <v>0.00703333350277402</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007884587637206897</v>
+        <v>0.007884587637206899</v>
       </c>
       <c r="K4" t="n">
-        <v>0.006967076808306139</v>
+        <v>0.006967076808306141</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007264151428013504</v>
+        <v>0.007264151428013498</v>
       </c>
     </row>
     <row r="5">
@@ -1823,25 +1823,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01053611768616335</v>
+        <v>0.01053611768616336</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02610853582436986</v>
+        <v>0.02610853582436988</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02775798830349049</v>
+        <v>0.02775798830349053</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01305484409436024</v>
+        <v>0.01305484409436025</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01305484409436024</v>
+        <v>0.01305484409436025</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01972293393635748</v>
+        <v>0.01972293393635746</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0202701426337783</v>
+        <v>0.02027014263377827</v>
       </c>
       <c r="I5" t="n">
         <v>0.01305470939450748</v>
@@ -1853,7 +1853,7 @@
         <v>0.0115242616442463</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01796941051907823</v>
+        <v>0.01796941051907824</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007936201657730379</v>
+        <v>0.007936201657730377</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008074358586261229</v>
+        <v>0.008074358586261232</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008919788373776877</v>
+        <v>0.008919788373776874</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00726840712447595</v>
+        <v>0.007268407124475952</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007305097336629118</v>
+        <v>0.007305097336629117</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008416347461664444</v>
+        <v>0.008416347461664447</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00842465068410472</v>
+        <v>0.008424650684104714</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007303965490354082</v>
+        <v>0.007303965490354079</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008183168388373808</v>
+        <v>0.008183168388373806</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007228058964141876</v>
+        <v>0.00722805896414187</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007535365004885597</v>
+        <v>0.007535365004885596</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007545197924851249</v>
+        <v>0.007545197924851245</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008395288242124464</v>
+        <v>0.008395288242124462</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008521253007928531</v>
+        <v>0.008521253007928529</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007632787435721589</v>
+        <v>0.007632787435721594</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007632787435721589</v>
+        <v>0.007632787435721594</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008025343728785323</v>
+        <v>0.008025343728785319</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007993393027613238</v>
+        <v>0.007993393027613233</v>
       </c>
       <c r="I7" t="n">
         <v>0.007631419714687876</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008482673849120756</v>
+        <v>0.008482673849120752</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007565163020219992</v>
+        <v>0.007565163020219989</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00786223763992736</v>
+        <v>0.007862237639927362</v>
       </c>
     </row>
     <row r="8">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008808139236342823</v>
+        <v>0.008808139236342835</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01093958652642842</v>
+        <v>0.01093958652642841</v>
       </c>
       <c r="D8" t="n">
         <v>0.01132951387450942</v>
@@ -1955,19 +1955,19 @@
         <v>0.009825652933042668</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008935813597149943</v>
+        <v>0.008935813597149941</v>
       </c>
       <c r="G8" t="n">
         <v>0.0105681891479578</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01053623844678898</v>
+        <v>0.01053623844678897</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01017426513386036</v>
+        <v>0.01017426513386035</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01102577080603782</v>
+        <v>0.01102577080603781</v>
       </c>
       <c r="K8" t="n">
         <v>0.008804329455813279</v>
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008827693216727519</v>
+        <v>0.00882769321672751</v>
       </c>
       <c r="C9" t="n">
         <v>0.01024027382138704</v>
@@ -1992,28 +1992,28 @@
         <v>0.01036625786106681</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01012564175728826</v>
+        <v>0.01012564175728825</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009476539709444568</v>
+        <v>0.009476539709444565</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009870329308047893</v>
+        <v>0.00987032930804789</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00983837860687582</v>
+        <v>0.009838378606875817</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009476405293950455</v>
+        <v>0.009476405293950444</v>
       </c>
       <c r="J9" t="n">
         <v>0.01032765942838333</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009084239636084976</v>
+        <v>0.009084239636084972</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009707223219189954</v>
+        <v>0.00970722321918995</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003817952508977043</v>
+        <v>0.003817952508977049</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003061288795418729</v>
+        <v>0.003061288795418726</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003879094091099378</v>
+        <v>0.003879094091099386</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003242188606768123</v>
+        <v>0.003242188606768132</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003242183453035409</v>
+        <v>0.003242183453035415</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003845237372752393</v>
+        <v>0.003845237372752403</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003847640851547409</v>
+        <v>0.003847640851547411</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003819029649198135</v>
+        <v>0.003819029649198141</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003948375471767198</v>
+        <v>0.003948375471767194</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004588655783779867</v>
+        <v>0.004588655783779872</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003825165116710765</v>
+        <v>0.003825165116710766</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003825932238166096</v>
+        <v>0.0038259322381661</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002857960303324849</v>
+        <v>0.00285796030332485</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00426272804429524</v>
+        <v>0.004262728044295245</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002882850688702533</v>
+        <v>0.00288285068870253</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002882845534969813</v>
+        <v>0.002882845534969811</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004021970525890218</v>
+        <v>0.004021970525890221</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004045560476111962</v>
+        <v>0.004045560476111963</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00383498716455088</v>
+        <v>0.003834987164550881</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004223814475071589</v>
+        <v>0.004223814475071608</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005107297285573206</v>
+        <v>0.005107297285573223</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003885127274694055</v>
+        <v>0.003885127274694058</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006768531995398325</v>
+        <v>0.006768531995398328</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007313419915145462</v>
+        <v>0.007313419915145464</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00745915429198749</v>
+        <v>0.007459154291987491</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00676825571694583</v>
+        <v>0.006768255716945832</v>
       </c>
       <c r="F4" t="n">
         <v>0.006768255716945832</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007074135484696071</v>
+        <v>0.007074135484696069</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007113004989916878</v>
+        <v>0.007113004989916882</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006763140230141268</v>
+        <v>0.00676314023014127</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007141068443276554</v>
+        <v>0.007141068443276557</v>
       </c>
       <c r="K4" t="n">
         <v>0.006784671545847895</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006860114005944808</v>
+        <v>0.006860114005944809</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008200728399879344</v>
+        <v>0.008200728399879348</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01897189253240772</v>
+        <v>0.01897189253240773</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02063591728868888</v>
+        <v>0.02063591728868885</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009107049045178006</v>
+        <v>0.009107049045178011</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009107049045178006</v>
+        <v>0.009107049045178011</v>
       </c>
       <c r="G5" t="n">
         <v>0.01432528343002451</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01573438732657526</v>
+        <v>0.01573438732657528</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00910694016213669</v>
+        <v>0.009106940162136689</v>
       </c>
       <c r="J5" t="n">
         <v>0.01564418695501132</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009180080010287806</v>
+        <v>0.009180080010287812</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01097308397666587</v>
+        <v>0.01097308397666588</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007018431767072088</v>
+        <v>0.00701843176707209</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00759496528511683</v>
+        <v>0.007594965285116832</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007723547633694204</v>
+        <v>0.007723547633694137</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006979451165124811</v>
+        <v>0.006979451165124814</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007013672468179545</v>
+        <v>0.007013672468179548</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008019224310181282</v>
+        <v>0.008019224310181284</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008096710773580084</v>
+        <v>0.008096710773580089</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007708229055626486</v>
+        <v>0.007708229055626489</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008088519756998444</v>
+        <v>0.008088519756998449</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007029416809835714</v>
+        <v>0.007029416809835685</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007109042095072461</v>
+        <v>0.007109042095072465</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00734300970433738</v>
+        <v>0.007343009704337384</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007917571183822936</v>
+        <v>0.007917571183822939</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008033612795415509</v>
+        <v>0.00803361279541551</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00733919145348807</v>
+        <v>0.007339191453488072</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00733919145348807</v>
+        <v>0.007339191453488072</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007648613193635122</v>
+        <v>0.007648613193635125</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007687482698855936</v>
+        <v>0.00768748269885594</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007337617939080322</v>
+        <v>0.007337617939080326</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007715546152215612</v>
+        <v>0.007715546152215613</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007359149254786949</v>
+        <v>0.007359149254786953</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007434591714883861</v>
+        <v>0.007434591714883865</v>
       </c>
     </row>
     <row r="8">
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008589915803616545</v>
+        <v>0.008589915803616547</v>
       </c>
       <c r="C8" t="n">
         <v>0.01041716988713767</v>
@@ -2348,25 +2348,25 @@
         <v>0.01079096901805893</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009495000909094962</v>
+        <v>0.009495000909094976</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008625173603485645</v>
+        <v>0.008625173603485648</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0101465424164496</v>
+        <v>0.01014654241644961</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01018541192167382</v>
+        <v>0.01018541192167383</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009835547161894807</v>
+        <v>0.009835547161894805</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01021372123681617</v>
+        <v>0.01021372123681618</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008582816957276737</v>
+        <v>0.008582816957276739</v>
       </c>
       <c r="L8" t="n">
         <v>0.01123931919899723</v>
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008444666800782643</v>
+        <v>0.00844466680078265</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009523570982001364</v>
+        <v>0.009523570982001373</v>
       </c>
       <c r="D9" t="n">
-        <v>0.009639632012993275</v>
+        <v>0.00963963201299328</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009525727305368494</v>
+        <v>0.009525727305368499</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008943726386468502</v>
+        <v>0.008943726386468507</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009254612991813554</v>
+        <v>0.009254612991813559</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009293482497034369</v>
+        <v>0.009293482497034374</v>
       </c>
       <c r="I9" t="n">
-        <v>0.008943617737258755</v>
+        <v>0.008943617737258762</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009321545950394044</v>
+        <v>0.00932154595039405</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008661075336655829</v>
+        <v>0.008661075336655831</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009040591513062293</v>
+        <v>0.009040591513062303</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003956375099927706</v>
+        <v>0.003956375099927701</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00302336130467126</v>
+        <v>0.003023361304671262</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004026802378484844</v>
+        <v>0.004026802378484839</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003285992832889491</v>
+        <v>0.003285992832889498</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003285986717249747</v>
+        <v>0.003285986717249751</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004008138678585024</v>
+        <v>0.004008138678585019</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004026023850752633</v>
+        <v>0.004026023850752638</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003960733207294655</v>
+        <v>0.003960733207294664</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004186388452354118</v>
+        <v>0.004186388452354116</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004668563813693619</v>
+        <v>0.004668563813693623</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004084933937655134</v>
+        <v>0.00408493393765514</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004019976423241018</v>
+        <v>0.004019976423241015</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002464542119989882</v>
+        <v>0.002464542119989884</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004522892977425467</v>
+        <v>0.004522892977425465</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002938663485535814</v>
+        <v>0.002938663485535808</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002938657369896067</v>
+        <v>0.002938657369896062</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004390617026148741</v>
+        <v>0.004390617026148738</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00452595109095339</v>
+        <v>0.004525951090953396</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004052404091512583</v>
+        <v>0.004052404091512586</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005210913684166652</v>
+        <v>0.005210913684166645</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005313237085622952</v>
+        <v>0.005313237085622963</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004942165666733858</v>
+        <v>0.004942165666733862</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006799421538481407</v>
+        <v>0.006799421538481405</v>
       </c>
       <c r="C4" t="n">
         <v>0.006716751526611654</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007594930047933095</v>
+        <v>0.00759493004793309</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006817384578790457</v>
+        <v>0.00681738457879046</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006817384578790457</v>
+        <v>0.00681738457879046</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0073805242656175</v>
+        <v>0.007380524265617502</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007594925123984313</v>
+        <v>0.007594925123984314</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006824399282777705</v>
+        <v>0.006824399282777708</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008465379488523161</v>
+        <v>0.00846537948852316</v>
       </c>
       <c r="K4" t="n">
         <v>0.007039484723073888</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008247120445755349</v>
+        <v>0.008247120445755346</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00864372946692982</v>
+        <v>0.008643729466929826</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008747264092601643</v>
+        <v>0.008747264092601655</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02360358094069256</v>
+        <v>0.02360358094069255</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01026031899275281</v>
+        <v>0.01026031899275288</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01026031899275281</v>
+        <v>0.01026031899275288</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02018281907590002</v>
+        <v>0.02018281907590005</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02570407785194039</v>
+        <v>0.02570407785194043</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01026014532011695</v>
+        <v>0.01026014532011701</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04079646992028756</v>
+        <v>0.04079646992028757</v>
       </c>
       <c r="K5" t="n">
         <v>0.0136933721062096</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03946220552897665</v>
+        <v>0.03946220552897668</v>
       </c>
     </row>
     <row r="6">
@@ -2655,34 +2655,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007054822760295436</v>
+        <v>0.007054822760295441</v>
       </c>
       <c r="C6" t="n">
-        <v>0.006991598208490173</v>
+        <v>0.006991598208489991</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007864000751623097</v>
+        <v>0.0078640007516231</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007038170480288998</v>
+        <v>0.007038170480289006</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007079054233684432</v>
+        <v>0.007079054233684437</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00763592548743153</v>
+        <v>0.007635925487431533</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008628807616040733</v>
+        <v>0.008628807616040738</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007825194896369526</v>
+        <v>0.007825194896369533</v>
       </c>
       <c r="J6" t="n">
         <v>0.008751765061105329</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007287967947488455</v>
+        <v>0.007287967947488458</v>
       </c>
       <c r="L6" t="n">
         <v>0.008510369398947103</v>
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007425453554556752</v>
+        <v>0.007425453554556755</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007387614894981521</v>
+        <v>0.007387614894981524</v>
       </c>
       <c r="D7" t="n">
         <v>0.008220942702541744</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007452842748378172</v>
+        <v>0.007452842748378177</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007452842748378172</v>
+        <v>0.007452842748378177</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008006556281692849</v>
+        <v>0.008006556281692853</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008220957140059659</v>
+        <v>0.008220957140059668</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00745043129885305</v>
+        <v>0.007450431298853056</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009091411504598506</v>
+        <v>0.009091411504598509</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007665516739149235</v>
+        <v>0.007665516739149236</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008873152461830692</v>
+        <v>0.008873152461830694</v>
       </c>
     </row>
     <row r="8">
@@ -2738,16 +2738,16 @@
         <v>0.008750475252113671</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01005464625098533</v>
+        <v>0.01005464625098534</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01116334080644275</v>
+        <v>0.01116334080644276</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009751012457825798</v>
+        <v>0.009751012457825801</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008819435947381134</v>
+        <v>0.008819435947381139</v>
       </c>
       <c r="G8" t="n">
         <v>0.01067116328449767</v>
@@ -2759,13 +2759,13 @@
         <v>0.01011503830165788</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01175628177424882</v>
+        <v>0.01175628177424883</v>
       </c>
       <c r="K8" t="n">
         <v>0.008965654951920992</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01293706833022613</v>
+        <v>0.01293706833022614</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008853231338806975</v>
+        <v>0.008853231338806989</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009426869338492003</v>
+        <v>0.009426869338492013</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01026021683507603</v>
+        <v>0.01026021683507604</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0101954904371543</v>
+        <v>0.01019549043715432</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009489859116330128</v>
+        <v>0.009489859116330143</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01004581072520332</v>
+        <v>0.01004581072520333</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01026021158357013</v>
+        <v>0.01026021158357014</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009489685742363524</v>
+        <v>0.009489685742363536</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01113066594810899</v>
+        <v>0.011130665948109</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009350479342599419</v>
+        <v>0.009350479342599425</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01091240690534116</v>
+        <v>0.01091240690534117</v>
       </c>
     </row>
   </sheetData>
@@ -2891,34 +2891,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003816930897811843</v>
+        <v>0.003816930897811844</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002947319883782824</v>
+        <v>0.002947319883782822</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003820787189516518</v>
+        <v>0.003820787189516511</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003205446723180878</v>
+        <v>0.003205446723180882</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003205440422833044</v>
+        <v>0.003205440422833046</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003822844560128456</v>
+        <v>0.003822844560128455</v>
       </c>
       <c r="H2" t="n">
         <v>0.003822784108374739</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003821696490148409</v>
+        <v>0.003821696490148412</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003980745275553596</v>
+        <v>0.003980745275553593</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004551656690170038</v>
+        <v>0.004551656690170043</v>
       </c>
       <c r="L2" t="n">
         <v>0.003832102252584894</v>
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003844032734700637</v>
+        <v>0.003844032734700631</v>
       </c>
       <c r="C3" t="n">
         <v>0.002411078103686942</v>
@@ -2940,28 +2940,28 @@
         <v>0.003872855973412887</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002862187392625538</v>
+        <v>0.002862187392625531</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002862181092277697</v>
+        <v>0.002862181092277689</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00388763126870824</v>
+        <v>0.003887631268708239</v>
       </c>
       <c r="H3" t="n">
         <v>0.003892066856613109</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003879377528733864</v>
+        <v>0.003879377528733859</v>
       </c>
       <c r="J3" t="n">
         <v>0.004345802121655386</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005066934795834681</v>
+        <v>0.005066934795834683</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003957085871858708</v>
+        <v>0.003957085871858709</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006698711940845476</v>
+        <v>0.006698711940845474</v>
       </c>
       <c r="C4" t="n">
         <v>0.006665943111873125</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006742270529631531</v>
+        <v>0.006742270529631529</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006747330350597596</v>
+        <v>0.006747330350597595</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006747330350597596</v>
+        <v>0.006747330350597595</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006762370544441593</v>
+        <v>0.006762370544441592</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006772783492105617</v>
+        <v>0.006772783492105614</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006731329708418512</v>
+        <v>0.006731329708418511</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007171640447105748</v>
+        <v>0.007171640447105746</v>
       </c>
       <c r="K4" t="n">
-        <v>0.006716734812371399</v>
+        <v>0.006716734812371397</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006874420088471949</v>
+        <v>0.006874420088471948</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007739515550846759</v>
+        <v>0.007739515550846756</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008494304268488212</v>
+        <v>0.008494304268488214</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009183972060254472</v>
+        <v>0.009183972060254463</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009360966066758646</v>
+        <v>0.009360966066758647</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009360966066758646</v>
+        <v>0.009360966066758647</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009639393506159074</v>
+        <v>0.009639393506159116</v>
       </c>
       <c r="H5" t="n">
         <v>0.01005305894732822</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009360915114009792</v>
+        <v>0.00936091511400979</v>
       </c>
       <c r="J5" t="n">
         <v>0.01696201716204373</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008757192630227036</v>
+        <v>0.008757192630227034</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01209924715866745</v>
+        <v>0.01209924715866744</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0069253188719053</v>
+        <v>0.006925318871905296</v>
       </c>
       <c r="C6" t="n">
-        <v>0.006915105269556856</v>
+        <v>0.006915105269556851</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007632642755655535</v>
+        <v>0.007632642755655538</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006934118870719197</v>
+        <v>0.0069341188707192</v>
       </c>
       <c r="F6" t="n">
         <v>0.006959924665957859</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006988977475501417</v>
+        <v>0.006988977475501416</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007693279040604497</v>
+        <v>0.007693279040604496</v>
       </c>
       <c r="I6" t="n">
         <v>0.007620481387956123</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008059979042536389</v>
+        <v>0.008059979042536384</v>
       </c>
       <c r="K6" t="n">
-        <v>0.006941878946252607</v>
+        <v>0.006941878946252584</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007100865233811399</v>
+        <v>0.007100865233811397</v>
       </c>
     </row>
     <row r="7">
@@ -3091,13 +3091,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007250764133814526</v>
+        <v>0.007250764133814523</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007251397116063146</v>
+        <v>0.007251397116063144</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007294304496233984</v>
+        <v>0.007294304496233983</v>
       </c>
       <c r="E7" t="n">
         <v>0.007286413282236641</v>
@@ -3106,22 +3106,22 @@
         <v>0.007286413282236641</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007314422737410643</v>
+        <v>0.007314422737410639</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007324835685074665</v>
+        <v>0.007324835685074662</v>
       </c>
       <c r="I7" t="n">
         <v>0.007283381901387561</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007723692640074797</v>
+        <v>0.007723692640074792</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007268787005340448</v>
+        <v>0.007268787005340445</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007426472281440996</v>
+        <v>0.007426472281440997</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008475575181751955</v>
+        <v>0.008475575181751953</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009694911616934787</v>
+        <v>0.009694911616934783</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009986789695760879</v>
+        <v>0.009986789695760877</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009394161263899407</v>
+        <v>0.009394161263899411</v>
       </c>
       <c r="F8" t="n">
         <v>0.008548565213338284</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009754828274404848</v>
+        <v>0.009754828274404843</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009765241222071263</v>
+        <v>0.009765241222071262</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009723787438381776</v>
+        <v>0.009723787438381773</v>
       </c>
       <c r="J8" t="n">
         <v>0.01016433707617147</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008471017761558893</v>
+        <v>0.00847101776155889</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01113666790858079</v>
+        <v>0.01113666790858078</v>
       </c>
     </row>
     <row r="9">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008354002697465427</v>
+        <v>0.008354002697465428</v>
       </c>
       <c r="C9" t="n">
         <v>0.008850105823947341</v>
@@ -3180,28 +3180,28 @@
         <v>0.008893031624095219</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009453903643828948</v>
+        <v>0.00945390364382895</v>
       </c>
       <c r="F9" t="n">
         <v>0.008882141454826593</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008913131445294842</v>
+        <v>0.008913131445294839</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008923544392958862</v>
+        <v>0.008923544392958865</v>
       </c>
       <c r="I9" t="n">
-        <v>0.008882090609271765</v>
+        <v>0.008882090609271764</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009322401347958989</v>
+        <v>0.009322401347958994</v>
       </c>
       <c r="K9" t="n">
         <v>0.008580418447226257</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009025180989325187</v>
+        <v>0.00902518098932519</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003726155158101856</v>
+        <v>0.003726155158101849</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002926435745892544</v>
+        <v>0.002926435745892542</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003729536091746911</v>
+        <v>0.003729536091746907</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0031771243736685</v>
+        <v>0.003177124373668507</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003177118740043063</v>
+        <v>0.003177118740043062</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003728377243031046</v>
+        <v>0.003728377243031044</v>
       </c>
       <c r="H2" t="n">
         <v>0.003728944098891649</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003728940574055952</v>
+        <v>0.003728940574055946</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003837940493275847</v>
+        <v>0.003837940493275842</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004518333021130028</v>
+        <v>0.004518333021130026</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003727192202286597</v>
+        <v>0.003727192202286598</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003717061248478548</v>
+        <v>0.00371706124847854</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002402395977536614</v>
+        <v>0.002402395977536613</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00374250204134676</v>
+        <v>0.003742502041346747</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002827469880092272</v>
+        <v>0.002827469880092267</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002827464246466839</v>
+        <v>0.00282746424646685</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003734329517758377</v>
+        <v>0.003734329517758378</v>
       </c>
       <c r="H3" t="n">
         <v>0.00374291626357854</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003738298175341962</v>
+        <v>0.003738298175341958</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003930743584608936</v>
+        <v>0.003930743584608929</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005027280044546564</v>
+        <v>0.005027280044546576</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003729494670342284</v>
+        <v>0.003729494670342285</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006688419016294469</v>
+        <v>0.00668841901629446</v>
       </c>
       <c r="C4" t="n">
-        <v>0.006665487482839351</v>
+        <v>0.006665487482839342</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006726608217121672</v>
+        <v>0.006726608217121666</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006714922032355942</v>
+        <v>0.00671492203235594</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006714922032355942</v>
+        <v>0.00671492203235594</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006711115465887264</v>
+        <v>0.006711115465887164</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00672750673135826</v>
+        <v>0.006727506731358264</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006703588693901366</v>
+        <v>0.006703588693901384</v>
       </c>
       <c r="J4" t="n">
-        <v>0.006745321485588087</v>
+        <v>0.00674532148558808</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00669091893611792</v>
+        <v>0.006690918936117918</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006705990708696714</v>
+        <v>0.006705990708696717</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007681975989765722</v>
+        <v>0.007681975989765704</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008544421089388668</v>
+        <v>0.008544421089388667</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009036756218838071</v>
+        <v>0.009036756218838069</v>
       </c>
       <c r="E5" t="n">
-        <v>0.008925562375334737</v>
+        <v>0.008925562375334718</v>
       </c>
       <c r="F5" t="n">
-        <v>0.008925562375334737</v>
+        <v>0.008925562375334718</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00885374881378739</v>
+        <v>0.008853748813787324</v>
       </c>
       <c r="H5" t="n">
-        <v>0.009321106079509896</v>
+        <v>0.009321106079509891</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008925523368097824</v>
+        <v>0.008925523368097809</v>
       </c>
       <c r="J5" t="n">
-        <v>0.009477040544816916</v>
+        <v>0.00947704054481692</v>
       </c>
       <c r="K5" t="n">
         <v>0.008436139444355712</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008951126200277781</v>
+        <v>0.008951126200277774</v>
       </c>
     </row>
     <row r="6">
@@ -3447,34 +3447,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007573974745316055</v>
+        <v>0.007573974745316056</v>
       </c>
       <c r="C6" t="n">
-        <v>0.006911380674056197</v>
+        <v>0.006911380674056194</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00695069428113698</v>
+        <v>0.006950694281136986</v>
       </c>
       <c r="E6" t="n">
         <v>0.006904926203134265</v>
       </c>
       <c r="F6" t="n">
-        <v>0.006930435511966955</v>
+        <v>0.006930435511966951</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007596671194908746</v>
+        <v>0.007596671194908761</v>
       </c>
       <c r="H6" t="n">
-        <v>0.006951847994695337</v>
+        <v>0.006951847994695332</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007589144422922984</v>
+        <v>0.007589144422922983</v>
       </c>
       <c r="J6" t="n">
-        <v>0.006990102491955845</v>
+        <v>0.006990102491955841</v>
       </c>
       <c r="K6" t="n">
-        <v>0.006915796931127221</v>
+        <v>0.00691579693112722</v>
       </c>
       <c r="L6" t="n">
         <v>0.006930016529079115</v>
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007231455045354314</v>
+        <v>0.007231455045354313</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007238270675876745</v>
+        <v>0.00723827067587674</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007269625208827729</v>
+        <v>0.00726962520882773</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007249031139054306</v>
+        <v>0.007249031139054304</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007249031139054306</v>
+        <v>0.007249031139054304</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007254151494947013</v>
+        <v>0.007254151494947007</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007270542760418116</v>
+        <v>0.007270542760418115</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007246624722961238</v>
+        <v>0.007246624722961237</v>
       </c>
       <c r="J7" t="n">
         <v>0.007288357514647932</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007233954965177766</v>
+        <v>0.00723395496517777</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007249026737756566</v>
+        <v>0.007249026737756572</v>
       </c>
     </row>
     <row r="8">
@@ -3527,34 +3527,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008452064849338279</v>
+        <v>0.008452064849338282</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009666668351532293</v>
+        <v>0.009666668351532284</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009945438540492133</v>
+        <v>0.00994543854049214</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009345161276093885</v>
+        <v>0.009345161276093883</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008506902203099392</v>
+        <v>0.00850690220309939</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009680026250069758</v>
+        <v>0.009680026250069763</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009696417515543565</v>
+        <v>0.00969641751554356</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009672499478083985</v>
+        <v>0.00967249947808398</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009714469138827311</v>
+        <v>0.009714469138827309</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008432176353911667</v>
+        <v>0.00843217635391167</v>
       </c>
       <c r="L8" t="n">
         <v>0.01093390151693304</v>
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008253689902982383</v>
+        <v>0.008253689902982385</v>
       </c>
       <c r="C9" t="n">
         <v>0.008730239615603154</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008761613362740454</v>
+        <v>0.008761613362740462</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009280695871793514</v>
+        <v>0.009280695871793516</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008738632566921388</v>
+        <v>0.008738632566921391</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008746120434673418</v>
+        <v>0.008746120434673425</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008762511700144528</v>
+        <v>0.008762511700144523</v>
       </c>
       <c r="I9" t="n">
         <v>0.008738593662687649</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00878032645437434</v>
+        <v>0.008780326454374342</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008453758207323376</v>
+        <v>0.008453758207323372</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008740995677482977</v>
+        <v>0.008740995677482976</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003883129747760744</v>
+        <v>0.003883129747760767</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002975370379296849</v>
+        <v>0.002975370379296875</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003894487040968758</v>
+        <v>0.003894487040968744</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003230641202455751</v>
+        <v>0.003230641202455785</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003230634632967916</v>
+        <v>0.003230634632967939</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00390094997033942</v>
+        <v>0.003900949970339408</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003941732393931791</v>
+        <v>0.003941732393931811</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003888068261895571</v>
+        <v>0.003888068261895559</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003963276602282183</v>
+        <v>0.003963276602282191</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004582876796063852</v>
+        <v>0.004582876796063868</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003986564384655869</v>
+        <v>0.003986564384655865</v>
       </c>
     </row>
     <row r="3">
@@ -3723,34 +3723,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003943762139274014</v>
+        <v>0.003943762139274018</v>
       </c>
       <c r="C3" t="n">
         <v>0.002437080340896509</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004025987527020761</v>
+        <v>0.004025987527020747</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002895164921885453</v>
+        <v>0.002895164921885442</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00289515835239761</v>
+        <v>0.002895158352397599</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004072288016102173</v>
+        <v>0.004072288016102171</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004367660662310556</v>
+        <v>0.004367660662310558</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003980326680087698</v>
+        <v>0.003980326680087705</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00412634567249809</v>
+        <v>0.004126345672498086</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005120903091061629</v>
+        <v>0.005120903091061632</v>
       </c>
       <c r="L3" t="n">
         <v>0.004683957075797851</v>
@@ -3763,13 +3763,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006743669150381812</v>
+        <v>0.006743669150381808</v>
       </c>
       <c r="C4" t="n">
-        <v>0.006681704158357704</v>
+        <v>0.006681704158357702</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006871955001778911</v>
+        <v>0.006871955001778907</v>
       </c>
       <c r="E4" t="n">
         <v>0.006775422876862678</v>
@@ -3778,22 +3778,22 @@
         <v>0.006775422876862678</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006941602339848129</v>
+        <v>0.006941602339848126</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007409242479107331</v>
+        <v>0.007409242479107321</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006776794716846194</v>
+        <v>0.006776794716846192</v>
       </c>
       <c r="J4" t="n">
-        <v>0.006843993166390228</v>
+        <v>0.006843993166390231</v>
       </c>
       <c r="K4" t="n">
-        <v>0.006786448189699431</v>
+        <v>0.006786448189699433</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007904653364664093</v>
+        <v>0.007904653364664102</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008265800580575191</v>
+        <v>0.008265800580575192</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008649512994826112</v>
+        <v>0.008649512994826114</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0112930747699587</v>
+        <v>0.01129307476995869</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01000292630687521</v>
+        <v>0.0100029263068752</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01000292630687521</v>
+        <v>0.0100029263068752</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01274414362818752</v>
+        <v>0.01274414362818759</v>
       </c>
       <c r="H5" t="n">
         <v>0.02266847901327628</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01000284241827964</v>
+        <v>0.01000284241827963</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01098579663344308</v>
+        <v>0.0109857966334431</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009774560871955818</v>
+        <v>0.009774560871955815</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0331488303138449</v>
+        <v>0.03314883031384488</v>
       </c>
     </row>
     <row r="6">
@@ -3846,34 +3846,34 @@
         <v>0.006975308595516887</v>
       </c>
       <c r="C6" t="n">
-        <v>0.006937945979991742</v>
+        <v>0.006937945979991741</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00710320315165441</v>
+        <v>0.007103203151654406</v>
       </c>
       <c r="E6" t="n">
         <v>0.006978304013350561</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007008725105924588</v>
+        <v>0.007008725105924591</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007173241784983203</v>
+        <v>0.007173241784983206</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008391139254821912</v>
+        <v>0.008391139254821914</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00700843416198127</v>
+        <v>0.007008434161981271</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007095877178415928</v>
+        <v>0.007095877178415922</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007012799631361828</v>
+        <v>0.00701279963136185</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008142453533836712</v>
+        <v>0.008142453533836721</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007338546188835588</v>
+        <v>0.007338546188835587</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007316525787381386</v>
+        <v>0.007316525787381388</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007466812803647983</v>
+        <v>0.007466812803647985</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007374508329284962</v>
+        <v>0.007374508329284966</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007374508329284962</v>
+        <v>0.007374508329284966</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007536479378301913</v>
+        <v>0.007536479378301907</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008004119517561109</v>
+        <v>0.0080041195175611</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007371671755299971</v>
+        <v>0.007371671755299974</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007438870204844018</v>
+        <v>0.007438870204844013</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007381325228153207</v>
+        <v>0.007381325228153214</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008499530403117881</v>
+        <v>0.008499530403117886</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008640840238607441</v>
+        <v>0.008640840238607447</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009921127403646167</v>
+        <v>0.009921127403646174</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01033796403158211</v>
+        <v>0.01033796403158212</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009620672781310399</v>
+        <v>0.009620672781310402</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008716892224061868</v>
+        <v>0.008716892224061875</v>
       </c>
       <c r="G8" t="n">
         <v>0.01013817250603784</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01060581264529779</v>
+        <v>0.0106058126452978</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009973364883035905</v>
+        <v>0.009973364883035908</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01004081870168525</v>
+        <v>0.01004081870168524</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008659482272942847</v>
+        <v>0.00865948227294285</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01245855452173335</v>
+        <v>0.01245855452173336</v>
       </c>
     </row>
     <row r="9">
@@ -3963,34 +3963,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008634406306056296</v>
+        <v>0.008634406306056297</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009176174516993896</v>
+        <v>0.009176174516993898</v>
       </c>
       <c r="D9" t="n">
-        <v>0.009326480891743172</v>
+        <v>0.00932648089174317</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009882004236787964</v>
+        <v>0.009882004236787967</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009231404092417015</v>
+        <v>0.009231404092417019</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009396128107914428</v>
+        <v>0.009396128107914421</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009863768247173627</v>
+        <v>0.009863768247173617</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009231320484912485</v>
+        <v>0.009231320484912488</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00929851893445653</v>
+        <v>0.009298518934456528</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008914312672846991</v>
+        <v>0.008914312672846985</v>
       </c>
       <c r="L9" t="n">
         <v>0.01035917913273039</v>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003783088986929623</v>
+        <v>0.003783088986929588</v>
       </c>
       <c r="C2" t="n">
         <v>0.00294684284799187</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003786028452744919</v>
+        <v>0.003786028452744878</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003199323313751635</v>
+        <v>0.003199323313751624</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003199316944566683</v>
+        <v>0.003199316944566677</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003785042019952169</v>
+        <v>0.003785042019952131</v>
       </c>
       <c r="H2" t="n">
         <v>0.003785519679265241</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003787194558402486</v>
+        <v>0.00378719455840245</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003926054799002718</v>
+        <v>0.00392605479900271</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004551187533618565</v>
+        <v>0.004551187533618559</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003783509086558918</v>
+        <v>0.003783509086558919</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003799304493199651</v>
+        <v>0.00379930449319964</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002420758729357627</v>
+        <v>0.002420758729357628</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003821592401201853</v>
+        <v>0.003821592401201843</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002859595246192708</v>
+        <v>0.002859595246192723</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002859588877007753</v>
+        <v>0.002859588877007769</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003814651284229669</v>
+        <v>0.003814651284229662</v>
       </c>
       <c r="H3" t="n">
         <v>0.003822620457564754</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00382994172818797</v>
+        <v>0.003829941728187957</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004064595525836902</v>
+        <v>0.004064595525836903</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005073719387504243</v>
+        <v>0.005073719387504245</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00380737296774127</v>
+        <v>0.003807372967741272</v>
       </c>
     </row>
     <row r="4">
@@ -4159,13 +4159,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006695010342583777</v>
+        <v>0.006695010342583779</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00666164857046185</v>
+        <v>0.006661648570461848</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00672821296118862</v>
+        <v>0.006728212961188625</v>
       </c>
       <c r="E4" t="n">
         <v>0.006738851791399179</v>
@@ -4174,22 +4174,22 @@
         <v>0.006738851791399179</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006713956991061852</v>
+        <v>0.006713956991061859</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006730070396168246</v>
+        <v>0.006730070396168248</v>
       </c>
       <c r="I4" t="n">
         <v>0.006720339353839852</v>
       </c>
       <c r="J4" t="n">
-        <v>0.006752195465955241</v>
+        <v>0.006752195465955244</v>
       </c>
       <c r="K4" t="n">
-        <v>0.006705665397897653</v>
+        <v>0.006705665397897642</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006705684999429502</v>
+        <v>0.006705684999429498</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007799481571630862</v>
+        <v>0.007799481571630865</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00853180662461884</v>
+        <v>0.008531806624618832</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009064973988485154</v>
+        <v>0.009064973988485157</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009290808912555871</v>
+        <v>0.009290808912555869</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009290808912555871</v>
+        <v>0.009290808912555869</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008916149465825276</v>
+        <v>0.008916149465825326</v>
       </c>
       <c r="H5" t="n">
         <v>0.009371266101932181</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009290766243550434</v>
+        <v>0.009290766243550432</v>
       </c>
       <c r="J5" t="n">
-        <v>0.009600748668403903</v>
+        <v>0.009600748668403887</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008688736370982044</v>
+        <v>0.008688736370982051</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008946280929576441</v>
+        <v>0.008946280929576432</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007577292751305959</v>
+        <v>0.007577292751305963</v>
       </c>
       <c r="C6" t="n">
-        <v>0.006907608057741107</v>
+        <v>0.006907608057741097</v>
       </c>
       <c r="D6" t="n">
-        <v>0.006951021601254586</v>
+        <v>0.00695102160125458</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006921072644985883</v>
+        <v>0.006921072644985884</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00694551507928235</v>
+        <v>0.006945515079282353</v>
       </c>
       <c r="G6" t="n">
         <v>0.006936973684254243</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007642845544257667</v>
+        <v>0.007642845544257679</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007602621762562032</v>
+        <v>0.007602621762562036</v>
       </c>
       <c r="J6" t="n">
         <v>0.006994625027141222</v>
       </c>
       <c r="K6" t="n">
-        <v>0.006927808805396694</v>
+        <v>0.006927808805396699</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006927636108405042</v>
+        <v>0.006927636108405038</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007239187979343887</v>
+        <v>0.007239187979343879</v>
       </c>
       <c r="C7" t="n">
         <v>0.007238614467723785</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007272372406209349</v>
+        <v>0.007272372406209348</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007268149096807075</v>
+        <v>0.007268149096807076</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007268149096807075</v>
+        <v>0.007268149096807076</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007258134627821961</v>
+        <v>0.007258134627821959</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007274248032928355</v>
+        <v>0.007274248032928347</v>
       </c>
       <c r="I7" t="n">
         <v>0.007264516990599961</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007296373102715351</v>
+        <v>0.007296373102715355</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007249843034657761</v>
+        <v>0.007249843034657759</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00724986263618961</v>
+        <v>0.007249862636189612</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008458141900797588</v>
+        <v>0.0084581419007976</v>
       </c>
       <c r="C8" t="n">
         <v>0.009666347822670673</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009946318418317271</v>
+        <v>0.009946318418317278</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009362318408772476</v>
+        <v>0.009362318408772474</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008523865215793753</v>
+        <v>0.008523865215793751</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009682179076861948</v>
+        <v>0.009682179076861943</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009698292481970692</v>
+        <v>0.009698292481970686</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009688561439639949</v>
+        <v>0.009688561439639951</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009720654386534503</v>
+        <v>0.009720654386534499</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008446411780869223</v>
+        <v>0.008446411780869217</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01093272490929715</v>
+        <v>0.01093272490929716</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008333188463023705</v>
+        <v>0.008333188463023706</v>
       </c>
       <c r="C9" t="n">
         <v>0.008822578203368282</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008856354513026117</v>
+        <v>0.008856354513026111</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009413930640906419</v>
+        <v>0.009413930640906423</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008848523298917792</v>
+        <v>0.008848523298917796</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008842098363466456</v>
+        <v>0.008842098363466458</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008858211768572849</v>
+        <v>0.008858211768572846</v>
       </c>
       <c r="I9" t="n">
-        <v>0.008848480726244454</v>
+        <v>0.008848480726244458</v>
       </c>
       <c r="J9" t="n">
-        <v>0.008880336838359844</v>
+        <v>0.008880336838359851</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008216855531442484</v>
+        <v>0.008216855531442474</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008833826371834108</v>
+        <v>0.008833826371834115</v>
       </c>
     </row>
   </sheetData>
@@ -4475,34 +4475,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003657626204325555</v>
+        <v>0.003657626204325551</v>
       </c>
       <c r="C2" t="n">
         <v>0.00292780443312991</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003660273138562132</v>
+        <v>0.003660273138562128</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003167118841056874</v>
+        <v>0.003167118841056872</v>
       </c>
       <c r="F2" t="n">
         <v>0.003167113141832204</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003659361785915642</v>
+        <v>0.003659361785915641</v>
       </c>
       <c r="H2" t="n">
         <v>0.00365986889192071</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003660148080426166</v>
+        <v>0.003660148080426164</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003822715021149343</v>
+        <v>0.003822715021149341</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004512743441904507</v>
+        <v>0.004512743441904505</v>
       </c>
       <c r="L2" t="n">
         <v>0.003658318258557143</v>
@@ -4518,31 +4518,31 @@
         <v>0.003618594591365513</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002417773200699951</v>
+        <v>0.00241777320069995</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003638804665619747</v>
+        <v>0.003638804665619742</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002824161553180458</v>
+        <v>0.002824161553180457</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002824155853955788</v>
+        <v>0.002824155853955787</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003632392119367234</v>
+        <v>0.003632392119367228</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003640488634527538</v>
+        <v>0.003640488634527537</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003637951300876745</v>
+        <v>0.003637951300876743</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003918745502295612</v>
+        <v>0.003918745502295604</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005035873795838512</v>
+        <v>0.00503587379583851</v>
       </c>
       <c r="L3" t="n">
         <v>0.003628542625315323</v>
@@ -4564,28 +4564,28 @@
         <v>0.006715095558055334</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006710635420250783</v>
+        <v>0.006710635420250785</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006710635420250783</v>
+        <v>0.006710635420250785</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006702407909534557</v>
+        <v>0.006702407909534558</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00671801856056791</v>
+        <v>0.006718018560567912</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006697450898432191</v>
+        <v>0.006697450898432193</v>
       </c>
       <c r="J4" t="n">
-        <v>0.006738972992183945</v>
+        <v>0.006738972992183944</v>
       </c>
       <c r="K4" t="n">
         <v>0.006694240305387717</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006698837690925204</v>
+        <v>0.006698837690925205</v>
       </c>
     </row>
     <row r="5">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007724277321894954</v>
+        <v>0.007724277321894956</v>
       </c>
       <c r="C5" t="n">
         <v>0.008532288003071362</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008936499331643488</v>
+        <v>0.008936499331643496</v>
       </c>
       <c r="E5" t="n">
         <v>0.008915626775490095</v>
@@ -4610,7 +4610,7 @@
         <v>0.008915626775490095</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008799621801335169</v>
+        <v>0.008799621801335219</v>
       </c>
       <c r="H5" t="n">
         <v>0.009247356273709338</v>
@@ -4619,13 +4619,13 @@
         <v>0.00891558806571225</v>
       </c>
       <c r="J5" t="n">
-        <v>0.009464093338996298</v>
+        <v>0.009464093338996305</v>
       </c>
       <c r="K5" t="n">
         <v>0.008588642308959563</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008921571889131183</v>
+        <v>0.00892157188913118</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007567337360668175</v>
+        <v>0.007567337360668176</v>
       </c>
       <c r="C6" t="n">
-        <v>0.006904582427363614</v>
+        <v>0.006904582427363613</v>
       </c>
       <c r="D6" t="n">
-        <v>0.006938384915604574</v>
+        <v>0.006938384915604575</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006898848172010746</v>
+        <v>0.006898848172010739</v>
       </c>
       <c r="F6" t="n">
-        <v>0.006923914056305277</v>
+        <v>0.006923914056305278</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00692718383966599</v>
+        <v>0.006927183839665989</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007630285806475892</v>
+        <v>0.007630285806475893</v>
       </c>
       <c r="I6" t="n">
-        <v>0.006922226828563623</v>
+        <v>0.006922226828563627</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007619594954954237</v>
+        <v>0.007619594954954235</v>
       </c>
       <c r="K6" t="n">
         <v>0.006918847564720836</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006922385354436224</v>
+        <v>0.006922385354436225</v>
       </c>
     </row>
     <row r="7">
@@ -4678,34 +4678,34 @@
         <v>0.00722272270273676</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007226429136589566</v>
+        <v>0.007226429136589568</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007252602015554293</v>
+        <v>0.007252602015554292</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007237909349200298</v>
+        <v>0.0072379093492003</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007237909349200298</v>
+        <v>0.0072379093492003</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007239933394068017</v>
+        <v>0.007239933394068015</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00725554404510137</v>
+        <v>0.007255544045101371</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007234976382965651</v>
+        <v>0.007234976382965653</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007276498476717404</v>
+        <v>0.007276498476717402</v>
       </c>
       <c r="K7" t="n">
         <v>0.007231765789921176</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007236363175458665</v>
+        <v>0.007236363175458664</v>
       </c>
     </row>
     <row r="8">
@@ -4715,19 +4715,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008438041542729676</v>
+        <v>0.008438041542729674</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009641209468649842</v>
+        <v>0.009641209468649846</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009912465508797352</v>
+        <v>0.009912465508797359</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009322256634551603</v>
+        <v>0.009322256634551607</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008489997043259352</v>
+        <v>0.008489997043259354</v>
       </c>
       <c r="G8" t="n">
         <v>0.00965168891949258</v>
@@ -4736,13 +4736,13 @@
         <v>0.009667299570528668</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009646731908390209</v>
+        <v>0.009646731908390212</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009688489136214447</v>
+        <v>0.009688489136214449</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0084248602042299</v>
+        <v>0.008424860204229896</v>
       </c>
       <c r="L8" t="n">
         <v>0.01089789686321996</v>
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008245329896729195</v>
+        <v>0.008245329896729199</v>
       </c>
       <c r="C9" t="n">
-        <v>0.008716494096395948</v>
+        <v>0.008716494096395952</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008742686175925088</v>
+        <v>0.008742686175925097</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009264516435612971</v>
+        <v>0.009264516435612982</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008725079953471606</v>
+        <v>0.008725079953471614</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008729998353874399</v>
+        <v>0.008729998353874401</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008745609004907746</v>
+        <v>0.008745609004907754</v>
       </c>
       <c r="I9" t="n">
-        <v>0.008725041342772027</v>
+        <v>0.008725041342772036</v>
       </c>
       <c r="J9" t="n">
-        <v>0.008766563436523784</v>
+        <v>0.008766563436523793</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008439995353814941</v>
+        <v>0.00843999535381495</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008726428135265042</v>
+        <v>0.008726428135265052</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004136414776232878</v>
+        <v>0.004136414776232876</v>
       </c>
       <c r="C2" t="n">
         <v>0.003692487761913996</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004257103846703021</v>
+        <v>0.004257103846703023</v>
       </c>
       <c r="E2" t="n">
         <v>0.003797849570680465</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00342701323540648</v>
+        <v>0.003427013235406481</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004194763102314828</v>
+        <v>0.004194763102314827</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004199936200026776</v>
+        <v>0.004199936200026775</v>
       </c>
       <c r="I2" t="n">
         <v>0.00405561024144127</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004142904766567265</v>
+        <v>0.004142904766567261</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005104006514874671</v>
+        <v>0.005104006514874669</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004543686217217129</v>
+        <v>0.004543686217217127</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0045776589791491</v>
+        <v>0.004577658979149095</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003406815200936064</v>
+        <v>0.003406815200936062</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005437504616504725</v>
+        <v>0.005437504616504728</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003577971930448521</v>
+        <v>0.00357797193044852</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002965841439655827</v>
+        <v>0.002965841439655826</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004995456962880187</v>
+        <v>0.004995456962880183</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005049184123335025</v>
+        <v>0.005049184123335024</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004003408841423297</v>
+        <v>0.004003408841423298</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004864132577128692</v>
+        <v>0.004864132577128691</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005938550209102435</v>
+        <v>0.005938550209102434</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007485998255408906</v>
+        <v>0.0074859982554089</v>
       </c>
     </row>
     <row r="4">
@@ -4951,34 +4951,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008243684122137336</v>
+        <v>0.008243684122137326</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007256661305895384</v>
+        <v>0.007256661305895386</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00960692269281303</v>
+        <v>0.009606922692813033</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00726754928965233</v>
+        <v>0.007267549289652332</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00726754928965233</v>
+        <v>0.007267549289652332</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00889840991623179</v>
+        <v>0.008898409916231783</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008979085391496253</v>
+        <v>0.008979085391496255</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007301617651559436</v>
+        <v>0.00730161765155944</v>
       </c>
       <c r="J4" t="n">
         <v>0.008803204475910752</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007752991316601957</v>
+        <v>0.007752991316601958</v>
       </c>
       <c r="L4" t="n">
         <v>0.0128009419432783</v>
@@ -4994,31 +4994,31 @@
         <v>0.03209676992185659</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01617596433307021</v>
+        <v>0.01617596433307023</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05702836247810567</v>
+        <v>0.05702836247810571</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01617596541492134</v>
+        <v>0.01617596541492136</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01617596541492134</v>
+        <v>0.01617596541492137</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04531215495252316</v>
+        <v>0.04531215495252321</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05069863370083588</v>
+        <v>0.05069863370083585</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01617555167910678</v>
+        <v>0.01617555167910679</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04489719243459605</v>
+        <v>0.04489719243459603</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02395360081134728</v>
+        <v>0.0239536008113473</v>
       </c>
       <c r="L5" t="n">
         <v>0.05162191906789763</v>
@@ -5031,22 +5031,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008560525662066975</v>
+        <v>0.008560525662066965</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007572089067396947</v>
+        <v>0.007572089067396952</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009968150915579605</v>
+        <v>0.009968150915579607</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007546683093995246</v>
+        <v>0.007546683093995247</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007614270371795408</v>
+        <v>0.00761427037179541</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009215251456161418</v>
+        <v>0.009215251456161422</v>
       </c>
       <c r="H6" t="n">
         <v>0.01022291856219195</v>
@@ -5055,10 +5055,10 @@
         <v>0.008520389717494661</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009154881653608338</v>
+        <v>0.009154881653608336</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008048704148392155</v>
+        <v>0.008048704148392181</v>
       </c>
       <c r="L6" t="n">
         <v>0.01316264729442995</v>
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008961037353382429</v>
+        <v>0.008961037353382419</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008019383536767967</v>
+        <v>0.008019383536767968</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01032425160520249</v>
+        <v>0.01032425160520248</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008018542655719456</v>
+        <v>0.008018542655719461</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008018542655719456</v>
+        <v>0.00801854265571946</v>
       </c>
       <c r="G7" t="n">
-        <v>0.009615763147476886</v>
+        <v>0.009615763147476881</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009696438622741346</v>
+        <v>0.009696438622741348</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008018970882804531</v>
+        <v>0.008018970882804533</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009520557707155843</v>
+        <v>0.009520557707155842</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008470344547847057</v>
+        <v>0.008470344547847055</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01351829517452338</v>
+        <v>0.01351829517452339</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01036922708037483</v>
+        <v>0.01036922708037482</v>
       </c>
       <c r="C8" t="n">
         <v>0.0108939412127866</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01350348292233478</v>
+        <v>0.01350348292233477</v>
       </c>
       <c r="E8" t="n">
         <v>0.01049281705413267</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009473583628518386</v>
+        <v>0.00947358362851838</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01249080814892621</v>
+        <v>0.0124908081489262</v>
       </c>
       <c r="H8" t="n">
         <v>0.01257148362419055</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01089401588425387</v>
+        <v>0.01089401588425386</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01239589098762846</v>
+        <v>0.01239589098762845</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009851286685038796</v>
+        <v>0.009851286685038787</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01792559316652088</v>
+        <v>0.01792559316652089</v>
       </c>
     </row>
     <row r="9">
@@ -5157,7 +5157,7 @@
         <v>0.01077061312267237</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01307550618507585</v>
+        <v>0.01307550618507584</v>
       </c>
       <c r="E9" t="n">
         <v>0.01168352215928168</v>
@@ -5166,10 +5166,10 @@
         <v>0.01077061354380458</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01236699273338129</v>
+        <v>0.01236699273338128</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01244766820864577</v>
+        <v>0.01244766820864576</v>
       </c>
       <c r="I9" t="n">
         <v>0.01077020046870895</v>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004095951640499756</v>
+        <v>0.00409595164049976</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003702369383265763</v>
+        <v>0.003702369383265764</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004228718555814593</v>
+        <v>0.004228718555814597</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003805906125996135</v>
+        <v>0.003805906125996137</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003440577032305455</v>
+        <v>0.003440577032305459</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00417195644070112</v>
+        <v>0.004171956440701123</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004167207492768601</v>
+        <v>0.004167207492768604</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004060946943723274</v>
+        <v>0.004060946943723279</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004069306914193725</v>
+        <v>0.004069306914193728</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005089497481270247</v>
+        <v>0.005089497481270249</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004496239952640421</v>
+        <v>0.004496239952640434</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004377782078179853</v>
+        <v>0.004377782078179856</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003538758017687572</v>
+        <v>0.003538758017687576</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005321520661056974</v>
+        <v>0.005321520661056977</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003707127092451615</v>
+        <v>0.003707127092451619</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003104087266082194</v>
+        <v>0.003104087266082197</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004919595900404533</v>
+        <v>0.004919595900404534</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004903132814959179</v>
+        <v>0.004903132814959186</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004128073387021959</v>
+        <v>0.004128073387021962</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004482059417016088</v>
+        <v>0.004482059417016092</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005922498545241191</v>
+        <v>0.005922498545241193</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007236283160802742</v>
+        <v>0.007236283160802757</v>
       </c>
     </row>
     <row r="4">
@@ -5350,31 +5350,31 @@
         <v>0.007928842574451991</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007469959131826111</v>
+        <v>0.007469959131826109</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00942850595873153</v>
+        <v>0.009428505958731535</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007479741700414105</v>
+        <v>0.007479741700414104</v>
       </c>
       <c r="F4" t="n">
         <v>0.007479741700414104</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008783352977783447</v>
+        <v>0.008783352977783446</v>
       </c>
       <c r="H4" t="n">
         <v>0.008752207718891238</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007506431634965857</v>
+        <v>0.007506431634965855</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008228787123062938</v>
+        <v>0.00822878712306294</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00773426192020181</v>
+        <v>0.007734261920201811</v>
       </c>
       <c r="L4" t="n">
         <v>0.01241077555525388</v>
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02577583285292867</v>
+        <v>0.02577583285292869</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0188189594558131</v>
+        <v>0.01881895945581314</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05031738054152301</v>
+        <v>0.05031738054152304</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01881896045511457</v>
+        <v>0.0188189604551146</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01881896045511458</v>
+        <v>0.0188189604551146</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04062627770321123</v>
+        <v>0.04062627770321126</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04383336152710027</v>
+        <v>0.04383336152710039</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01881862107907958</v>
+        <v>0.01881862107907962</v>
       </c>
       <c r="J5" t="n">
         <v>0.03241370670520304</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02191862284048524</v>
+        <v>0.02191862284048518</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05387310004853719</v>
+        <v>0.05387310004853711</v>
       </c>
     </row>
     <row r="6">
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008233072589996629</v>
+        <v>0.008233072589996631</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007775063452505639</v>
+        <v>0.00777506345250564</v>
       </c>
       <c r="D6" t="n">
         <v>0.009768631013408241</v>
@@ -5439,19 +5439,19 @@
         <v>0.007750858487630791</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007807575708397125</v>
+        <v>0.007807575708397124</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009087582993328087</v>
+        <v>0.009087582993328083</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009918887089316156</v>
+        <v>0.009918887089316163</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008652385860005312</v>
+        <v>0.008652385860005316</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008561996699609969</v>
+        <v>0.008561996699609971</v>
       </c>
       <c r="K6" t="n">
         <v>0.008020370431739442</v>
@@ -5470,34 +5470,34 @@
         <v>0.008584290168516775</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008162217605764159</v>
+        <v>0.008162217605764157</v>
       </c>
       <c r="D7" t="n">
         <v>0.01008393098829423</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008161070405668326</v>
+        <v>0.008161070405668328</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008161070405668326</v>
+        <v>0.008161070405668328</v>
       </c>
       <c r="G7" t="n">
-        <v>0.009438800571848229</v>
+        <v>0.009438800571848234</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00940765531295602</v>
+        <v>0.009407655312956021</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008161879229030644</v>
+        <v>0.008161879229030647</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008884234717127725</v>
+        <v>0.008884234717127727</v>
       </c>
       <c r="K7" t="n">
         <v>0.008389709514266595</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01306622314931867</v>
+        <v>0.01306622314931866</v>
       </c>
     </row>
     <row r="8">
@@ -5507,10 +5507,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009881295917060294</v>
+        <v>0.009881295917060296</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01080439745218171</v>
+        <v>0.0108043974521817</v>
       </c>
       <c r="D8" t="n">
         <v>0.01300603742814756</v>
@@ -5534,7 +5534,7 @@
         <v>0.01152748532523331</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009661712987048883</v>
+        <v>0.009661712987048886</v>
       </c>
       <c r="L8" t="n">
         <v>0.01711519824363131</v>
@@ -5550,34 +5550,34 @@
         <v>0.01024457163511156</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01050880694012646</v>
+        <v>0.01050880694012645</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0124305434926907</v>
+        <v>0.01243054349269072</v>
       </c>
       <c r="E9" t="n">
         <v>0.01130079254630949</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01050880740516156</v>
+        <v>0.01050880740516157</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01178538990621053</v>
+        <v>0.01178538990621054</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01175424464731831</v>
+        <v>0.01175424464731832</v>
       </c>
       <c r="I9" t="n">
         <v>0.01050846856339294</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01123082405149002</v>
+        <v>0.01123082405149003</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01033864962938985</v>
+        <v>0.01033864962938986</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01541281248368096</v>
+        <v>0.01541281248368098</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004051201717818829</v>
+        <v>0.004051201717818836</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003680347556236706</v>
+        <v>0.003680347556236705</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004161347237302088</v>
+        <v>0.004161347237302099</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003762579734028465</v>
+        <v>0.003762579734028473</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00346176804217681</v>
+        <v>0.003461768042176811</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004119127933441735</v>
+        <v>0.004119127933441749</v>
       </c>
       <c r="H2" t="n">
         <v>0.004129684961824139</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004063714495274927</v>
+        <v>0.004063714495274938</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003905901864257104</v>
+        <v>0.003905901864257105</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00505072870272704</v>
+        <v>0.005050728702727038</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004408670350461534</v>
+        <v>0.004408670350461535</v>
       </c>
     </row>
     <row r="3">
@@ -5703,34 +5703,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004251542813383948</v>
+        <v>0.004251542813383951</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003708985197072724</v>
+        <v>0.003708985197072726</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005033137326609444</v>
+        <v>0.00503313732660945</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003842635642788141</v>
+        <v>0.00384263564278814</v>
       </c>
       <c r="F3" t="n">
         <v>0.003346093746596634</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00473531422882689</v>
+        <v>0.004735314228826897</v>
       </c>
       <c r="H3" t="n">
         <v>0.004824285036038304</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004339667914947306</v>
+        <v>0.004339667914947297</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004019766600035593</v>
+        <v>0.004019766600035582</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005832973461913431</v>
+        <v>0.005832973461913436</v>
       </c>
       <c r="L3" t="n">
         <v>0.006802354745242691</v>
@@ -5743,13 +5743,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007768348131354503</v>
+        <v>0.007768348131354508</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007858228628864953</v>
+        <v>0.007858228628864952</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009012492443360243</v>
+        <v>0.009012492443360248</v>
       </c>
       <c r="E4" t="n">
         <v>0.007867482356117932</v>
@@ -5758,19 +5758,19 @@
         <v>0.007867482356117932</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008532161339360342</v>
+        <v>0.008532161339360344</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008669914686511926</v>
+        <v>0.008669914686511931</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007886402629941624</v>
+        <v>0.007886402629941626</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007778819994674042</v>
+        <v>0.007778819994674046</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007629509748416544</v>
+        <v>0.007629509748416551</v>
       </c>
       <c r="L4" t="n">
         <v>0.01177124144113409</v>
@@ -5783,13 +5783,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02258126341386269</v>
+        <v>0.02258126341386272</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02444686264135276</v>
+        <v>0.02444686264135275</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04224386607574084</v>
+        <v>0.04224386607574082</v>
       </c>
       <c r="E5" t="n">
         <v>0.02444686354754874</v>
@@ -5798,22 +5798,22 @@
         <v>0.02444686354754874</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03561873994915044</v>
+        <v>0.03561873994915057</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04081740352225807</v>
+        <v>0.04081740352225805</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02444667034690814</v>
+        <v>0.02444667034690812</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02431154223118627</v>
+        <v>0.02431154223118628</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01958888405793123</v>
+        <v>0.01958888405793129</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03976513271960812</v>
+        <v>0.03976513271960833</v>
       </c>
     </row>
     <row r="6">
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008074662770412185</v>
+        <v>0.008074662770412173</v>
       </c>
       <c r="C6" t="n">
         <v>0.008175256140958612</v>
@@ -5835,22 +5835,22 @@
         <v>0.008150728155162849</v>
       </c>
       <c r="F6" t="n">
-        <v>0.008194185478678057</v>
+        <v>0.008194185478678059</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00964675077683615</v>
+        <v>0.009646750776836174</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009805592410413401</v>
+        <v>0.009805592410413407</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008192717268999313</v>
+        <v>0.008192717268999304</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00889849424868821</v>
+        <v>0.008898494248688209</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007919342507425748</v>
+        <v>0.00791934250742575</v>
       </c>
       <c r="L6" t="n">
         <v>0.01210241724999039</v>
@@ -5866,10 +5866,10 @@
         <v>0.008412175654859463</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008530422447891204</v>
+        <v>0.008530422447891206</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009656297020288822</v>
+        <v>0.009656297020288836</v>
       </c>
       <c r="E7" t="n">
         <v>0.008529189410139623</v>
@@ -5878,19 +5878,19 @@
         <v>0.008529189410139623</v>
       </c>
       <c r="G7" t="n">
-        <v>0.009175988862865294</v>
+        <v>0.009175988862865315</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009313742210016889</v>
+        <v>0.009313742210016891</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008530230153446589</v>
+        <v>0.00853023015344659</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008422647518179</v>
+        <v>0.008422647518179002</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0082733372719215</v>
+        <v>0.008273337271921505</v>
       </c>
       <c r="L7" t="n">
         <v>0.01241506896463905</v>
@@ -5906,34 +5906,34 @@
         <v>0.009691638475757165</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01113320365913206</v>
+        <v>0.01113320365913207</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01253457673057045</v>
+        <v>0.01253457673057046</v>
       </c>
       <c r="E8" t="n">
         <v>0.01077113470914961</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009851139178372515</v>
+        <v>0.009851139178372513</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01177966199260694</v>
+        <v>0.01177966199260695</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0119174153397586</v>
+        <v>0.01191741533975861</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01113390328318821</v>
+        <v>0.01113390328318822</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01102658089314603</v>
+        <v>0.01102658089314604</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009528202206486402</v>
+        <v>0.009528202206486409</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01640199049059307</v>
+        <v>0.01640199049059309</v>
       </c>
     </row>
     <row r="9">
@@ -5943,10 +5943,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009909100648228144</v>
+        <v>0.009909100648228157</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0106638545163695</v>
+        <v>0.01066385451636951</v>
       </c>
       <c r="D9" t="n">
         <v>0.01178975247552581</v>
@@ -5958,10 +5958,10 @@
         <v>0.01066385493787647</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01130942093134361</v>
+        <v>0.01130942093134362</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0114471742784952</v>
+        <v>0.01144717427849521</v>
       </c>
       <c r="I9" t="n">
         <v>0.01066366222192489</v>
@@ -5970,10 +5970,10 @@
         <v>0.01055607958665731</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01003797482646409</v>
+        <v>0.01003797482646411</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01454850103311737</v>
+        <v>0.01454850103311738</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003810302007135876</v>
+        <v>0.003810302007135875</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003444433337606493</v>
+        <v>0.003444433337606492</v>
       </c>
       <c r="D2" t="n">
         <v>0.003858566422668415</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003539356336815676</v>
+        <v>0.003539356336815674</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003194028384268786</v>
+        <v>0.003194028384268785</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003845419595660118</v>
+        <v>0.003845419595660116</v>
       </c>
       <c r="H2" t="n">
         <v>0.003852518385483937</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003805415228404881</v>
+        <v>0.003805415228404878</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003779206270027398</v>
+        <v>0.003779206270027404</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004826087820460349</v>
+        <v>0.00482608782046035</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004298746806130244</v>
+        <v>0.004298746806130242</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003684935257111855</v>
+        <v>0.003684935257111851</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003055806153674161</v>
+        <v>0.003055806153674162</v>
       </c>
       <c r="D3" t="n">
         <v>0.004026590666558584</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003211210271274389</v>
+        <v>0.003211210271274392</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002641187045922013</v>
+        <v>0.00264118704592201</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00393449778262087</v>
+        <v>0.003934497782620866</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003991795965272399</v>
+        <v>0.003991795965272398</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003650342901890639</v>
+        <v>0.003650342901890635</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003915609583711478</v>
+        <v>0.003915609583711488</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005451089279469392</v>
+        <v>0.005451089279469393</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007148176314394711</v>
+        <v>0.007148176314394714</v>
       </c>
     </row>
     <row r="4">
@@ -6139,19 +6139,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006959523487654514</v>
+        <v>0.00695952348765451</v>
       </c>
       <c r="C4" t="n">
-        <v>0.006846224153244899</v>
+        <v>0.006846224153244898</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007504692263822656</v>
+        <v>0.007504692263822658</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006855679968392448</v>
+        <v>0.006855679968392449</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006855679968392448</v>
+        <v>0.006855679968392449</v>
       </c>
       <c r="G4" t="n">
         <v>0.007352534715877324</v>
@@ -6160,16 +6160,16 @@
         <v>0.007446140903799275</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006879616468928208</v>
+        <v>0.006879616468928206</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007538518838442972</v>
+        <v>0.007538518838442974</v>
       </c>
       <c r="K4" t="n">
         <v>0.007145334637238943</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01241164659198158</v>
+        <v>0.01241164659198157</v>
       </c>
     </row>
     <row r="5">
@@ -6179,13 +6179,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01216606639497793</v>
+        <v>0.01216606639497785</v>
       </c>
       <c r="C5" t="n">
         <v>0.01125623358556564</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0209112052692397</v>
+        <v>0.02091120526923967</v>
       </c>
       <c r="E5" t="n">
         <v>0.01125623461917702</v>
@@ -6194,10 +6194,10 @@
         <v>0.01125623461917702</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01906558975750385</v>
+        <v>0.01906558975750387</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02150898616366844</v>
+        <v>0.02150898616366842</v>
       </c>
       <c r="I5" t="n">
         <v>0.0112560792998184</v>
@@ -6206,10 +6206,10 @@
         <v>0.02354589410443003</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01521355485871349</v>
+        <v>0.01521355485871346</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1222331581089945</v>
+        <v>0.1222331581089944</v>
       </c>
     </row>
     <row r="6">
@@ -6219,13 +6219,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007992927156912211</v>
+        <v>0.007992927156912206</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007116219376706119</v>
+        <v>0.007116219376706121</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008545409975368302</v>
+        <v>0.0085454099753683</v>
       </c>
       <c r="E6" t="n">
         <v>0.007093765633624348</v>
@@ -6234,16 +6234,16 @@
         <v>0.007133619038129364</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008385938385135024</v>
+        <v>0.00838593838513502</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007704531736763733</v>
+        <v>0.007704531736763731</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007913020138185902</v>
+        <v>0.0079130201381859</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00857713592824403</v>
+        <v>0.008577135928244032</v>
       </c>
       <c r="K6" t="n">
         <v>0.007397958583543638</v>
@@ -6259,16 +6259,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007572250308331092</v>
+        <v>0.007572250308331093</v>
       </c>
       <c r="C7" t="n">
         <v>0.00749249757535203</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008117396200191862</v>
+        <v>0.008117396200191864</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007491443425128585</v>
+        <v>0.007491443425128586</v>
       </c>
       <c r="F7" t="n">
         <v>0.007491443425128586</v>
@@ -6277,16 +6277,16 @@
         <v>0.007965261536553907</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008058867724475857</v>
+        <v>0.008058867724475859</v>
       </c>
       <c r="I7" t="n">
         <v>0.007492343289604787</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008151245659119552</v>
+        <v>0.008151245659119555</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007758061457915521</v>
+        <v>0.007758061457915522</v>
       </c>
       <c r="L7" t="n">
         <v>0.01302437341265816</v>
@@ -6299,7 +6299,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008889636225254433</v>
+        <v>0.008889636225254429</v>
       </c>
       <c r="C8" t="n">
         <v>0.01013032355477694</v>
@@ -6308,13 +6308,13 @@
         <v>0.01102991805319466</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009769070348260606</v>
+        <v>0.009769070348260604</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008851147491498077</v>
+        <v>0.008851147491498079</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01060380904307921</v>
+        <v>0.0106038090430792</v>
       </c>
       <c r="H8" t="n">
         <v>0.01069741523100113</v>
@@ -6323,10 +6323,10 @@
         <v>0.01013089079613009</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01079005281174446</v>
+        <v>0.01079005281174447</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009050906120027475</v>
+        <v>0.00905090612002747</v>
       </c>
       <c r="L8" t="n">
         <v>0.01704298467325074</v>
@@ -6342,7 +6342,7 @@
         <v>0.009038050428492716</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009574382471234854</v>
+        <v>0.009574382471234853</v>
       </c>
       <c r="D9" t="n">
         <v>0.01019930418763296</v>
@@ -6357,16 +6357,16 @@
         <v>0.01004714643243673</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01014075262035869</v>
+        <v>0.01014075262035868</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009574228185487612</v>
+        <v>0.00957422818548761</v>
       </c>
       <c r="J9" t="n">
         <v>0.01023313055500238</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00948298450236278</v>
+        <v>0.009482984502362778</v>
       </c>
       <c r="L9" t="n">
         <v>0.01510625830854096</v>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003735753536495974</v>
+        <v>0.003735753536495972</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003384528166911628</v>
+        <v>0.003384528166911626</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003739432387533327</v>
+        <v>0.003739432387533326</v>
       </c>
       <c r="E2" t="n">
         <v>0.003476861830325041</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00313875611680517</v>
+        <v>0.003138756116805169</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003747047349860783</v>
+        <v>0.003747047349860782</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003734360170274652</v>
+        <v>0.00373436017027465</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003743277506314697</v>
+        <v>0.003743277506314696</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003667184582981156</v>
+        <v>0.003667184582981155</v>
       </c>
       <c r="K2" t="n">
         <v>0.004744657311391564</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003727234430228849</v>
+        <v>0.003727234430228848</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003566498846899688</v>
+        <v>0.003566498846899687</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003028595209732529</v>
+        <v>0.003028595209732527</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0035925479058863</v>
+        <v>0.003592547905886299</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003180180324548614</v>
+        <v>0.003180180324548615</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002622078861631235</v>
+        <v>0.002622078861631233</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003646699785423314</v>
+        <v>0.003646699785423316</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003562801657198942</v>
+        <v>0.003562801657198941</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00361990078536141</v>
+        <v>0.003619900785361409</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003591232694549591</v>
+        <v>0.003591232694549586</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005309101401927201</v>
+        <v>0.005309101401927199</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003511650252813211</v>
+        <v>0.003511650252813212</v>
       </c>
     </row>
     <row r="4">
@@ -6541,22 +6541,22 @@
         <v>0.00684782819101125</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006849027970140248</v>
+        <v>0.006849027970140249</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006855660403099944</v>
+        <v>0.006855660403099942</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006855660403099944</v>
+        <v>0.006855660403099942</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006931795928545541</v>
+        <v>0.006931795928545539</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006801888806083005</v>
+        <v>0.006801888806083004</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006870508968657384</v>
+        <v>0.006870508968657383</v>
       </c>
       <c r="J4" t="n">
         <v>0.00709190038661488</v>
@@ -6565,7 +6565,7 @@
         <v>0.006968065210892812</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006720753286281246</v>
+        <v>0.006720753286281245</v>
       </c>
     </row>
     <row r="5">
@@ -6575,7 +6575,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01010512053080406</v>
+        <v>0.01010512053080407</v>
       </c>
       <c r="C5" t="n">
         <v>0.01143244038869506</v>
@@ -6590,7 +6590,7 @@
         <v>0.01143244127007103</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01214899884514021</v>
+        <v>0.01214899884514018</v>
       </c>
       <c r="H5" t="n">
         <v>0.01038492558917362</v>
@@ -6599,13 +6599,13 @@
         <v>0.01143238167277667</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01501613228603872</v>
+        <v>0.01501613228603871</v>
       </c>
       <c r="K5" t="n">
         <v>0.01254151951975576</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01226198018706021</v>
+        <v>0.01226198018706022</v>
       </c>
     </row>
     <row r="6">
@@ -6615,22 +6615,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007711424471134552</v>
+        <v>0.007711424471134551</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007095683641938212</v>
+        <v>0.007095683641938206</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007080312080932169</v>
+        <v>0.007080312080932168</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007074780672843659</v>
+        <v>0.007074780672843658</v>
       </c>
       <c r="F6" t="n">
         <v>0.007103064201708674</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007835746744361879</v>
+        <v>0.007835746744361877</v>
       </c>
       <c r="H6" t="n">
         <v>0.007718828832827583</v>
@@ -6642,10 +6642,10 @@
         <v>0.007345821181932893</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007203006949618096</v>
+        <v>0.007203006949618097</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006992949930922</v>
+        <v>0.006992949930921999</v>
       </c>
     </row>
     <row r="7">
@@ -6655,34 +6655,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007348003680754683</v>
+        <v>0.007348003680754681</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007411097710012254</v>
+        <v>0.007411097710012251</v>
       </c>
       <c r="D7" t="n">
         <v>0.007389536477865758</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00741021721568927</v>
+        <v>0.007410217215689267</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00741021721568927</v>
+        <v>0.007410217215689267</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007472325953982015</v>
+        <v>0.007472325953982011</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007342418831519477</v>
+        <v>0.007342418831519476</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007411038994093858</v>
+        <v>0.007411038994093857</v>
       </c>
       <c r="J7" t="n">
         <v>0.007632430412051352</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007508595236329282</v>
+        <v>0.007508595236329283</v>
       </c>
       <c r="L7" t="n">
         <v>0.00726128331171772</v>
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008540675878361522</v>
+        <v>0.00854067587836152</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009785601351964549</v>
+        <v>0.009785601351964553</v>
       </c>
       <c r="D8" t="n">
         <v>0.01000982766273774</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009462279567394965</v>
+        <v>0.009462279567394963</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008640738598370957</v>
+        <v>0.008640738598370961</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009847413993581336</v>
+        <v>0.009847413993581335</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009717506871118662</v>
+        <v>0.009717506871118661</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009786127033693175</v>
+        <v>0.009786127033693177</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01000775083027343</v>
+        <v>0.01000775083027342</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008679303452615438</v>
+        <v>0.008679303452615441</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01087150357031028</v>
+        <v>0.01087150357031029</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008514272382451372</v>
+        <v>0.008514272382451369</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009084714865785245</v>
+        <v>0.009084714865785239</v>
       </c>
       <c r="D9" t="n">
-        <v>0.009063175377845158</v>
+        <v>0.009063175377845149</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009670185171114102</v>
+        <v>0.009670185171114096</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009084715635742582</v>
+        <v>0.009084715635742577</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009145943109755011</v>
+        <v>0.009145943109755004</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009016035987292474</v>
+        <v>0.009016035987292465</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009084656149866852</v>
+        <v>0.009084656149866848</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009306047567824353</v>
+        <v>0.009306047567824343</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008888252800562428</v>
+        <v>0.008888252800562423</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008934900467490717</v>
+        <v>0.00893490046749071</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003737615444589607</v>
+        <v>0.003737615444589611</v>
       </c>
       <c r="C2" t="n">
         <v>0.003342788710848094</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003730475728125117</v>
+        <v>0.003730475728125123</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003416666446528952</v>
+        <v>0.003416666446528955</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003136142066858155</v>
+        <v>0.003136142066858154</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003739822280076112</v>
+        <v>0.003739822280076115</v>
       </c>
       <c r="H2" t="n">
         <v>0.003728348532284278</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003741957444808305</v>
+        <v>0.003741957444808306</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003564310509476584</v>
+        <v>0.003564310509476585</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004732950260682894</v>
+        <v>0.004732950260682897</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003726667696897294</v>
+        <v>0.003726667696897293</v>
       </c>
     </row>
     <row r="3">
@@ -6891,34 +6891,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003614657699818411</v>
+        <v>0.003614657699818413</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002987421033690785</v>
+        <v>0.002987421033690786</v>
       </c>
       <c r="D3" t="n">
         <v>0.003563984849260444</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003108597237144886</v>
+        <v>0.003108597237144887</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002645544210529333</v>
+        <v>0.002645544210529337</v>
       </c>
       <c r="G3" t="n">
         <v>0.003630463931998158</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003554889596561755</v>
+        <v>0.003554889596561757</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003645501712322987</v>
+        <v>0.003645501712322992</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003393715016761663</v>
+        <v>0.003393715016761666</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005275317009966239</v>
+        <v>0.005275317009966242</v>
       </c>
       <c r="L3" t="n">
         <v>0.003542217060324726</v>
@@ -6940,13 +6940,13 @@
         <v>0.006809785336502626</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006906754233663093</v>
+        <v>0.006906754233663092</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006906754233663093</v>
+        <v>0.006906754233663092</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006912326993460898</v>
+        <v>0.006912326993460899</v>
       </c>
       <c r="H4" t="n">
         <v>0.006795596443184978</v>
@@ -6955,13 +6955,13 @@
         <v>0.006918962255065499</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007023887977277949</v>
+        <v>0.007023887977277947</v>
       </c>
       <c r="K4" t="n">
         <v>0.006927798886990097</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00677515831402089</v>
+        <v>0.006775158314020889</v>
       </c>
     </row>
     <row r="5">
@@ -6971,13 +6971,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01144067427000038</v>
+        <v>0.01144067427000037</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01221246783715798</v>
+        <v>0.01221246783715799</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01016131046257308</v>
+        <v>0.01016131046257307</v>
       </c>
       <c r="E5" t="n">
         <v>0.01221246864204486</v>
@@ -6986,19 +6986,19 @@
         <v>0.01221246864204486</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01190750946552327</v>
+        <v>0.01190750946552332</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01029438858006777</v>
+        <v>0.01029438858006778</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01221242630699553</v>
+        <v>0.01221242630699554</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01396027850029754</v>
+        <v>0.01396027850029756</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01185656339391463</v>
+        <v>0.01185656339391464</v>
       </c>
       <c r="L5" t="n">
         <v>0.01197865544414644</v>
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007127077789566903</v>
+        <v>0.007127077789566902</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007148843726609538</v>
+        <v>0.007148843726609541</v>
       </c>
       <c r="D6" t="n">
         <v>0.007041350515571317</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007127804282891653</v>
+        <v>0.007127804282891655</v>
       </c>
       <c r="F6" t="n">
         <v>0.007154713221510571</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007148973064626911</v>
+        <v>0.007148973064626908</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007700547471089657</v>
+        <v>0.00770054747108966</v>
       </c>
       <c r="I6" t="n">
         <v>0.00715560832623151</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007280057204633766</v>
+        <v>0.007280057204633765</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007164787530729669</v>
+        <v>0.007164787530729667</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007010614609783049</v>
+        <v>0.007010614609783048</v>
       </c>
     </row>
     <row r="7">
@@ -7051,13 +7051,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007428546964815861</v>
+        <v>0.007428546964815862</v>
       </c>
       <c r="C7" t="n">
         <v>0.007457119031642925</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007347878888491744</v>
+        <v>0.007347878888491745</v>
       </c>
       <c r="E7" t="n">
         <v>0.007456230496496782</v>
@@ -7066,22 +7066,22 @@
         <v>0.007456230496496782</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007450442239875869</v>
+        <v>0.007450442239875871</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007333711689599945</v>
+        <v>0.007333711689599946</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007457077501480471</v>
+        <v>0.00745707750148047</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007562003223692919</v>
+        <v>0.00756200322369292</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007465914133405067</v>
+        <v>0.007465914133405071</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007313273560435858</v>
+        <v>0.00731327356043586</v>
       </c>
     </row>
     <row r="8">
@@ -7091,34 +7091,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008618023756179597</v>
+        <v>0.008618023756179602</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009823970801030956</v>
+        <v>0.009823970801030958</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009959604136722273</v>
+        <v>0.009959604136722271</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009501866223177032</v>
+        <v>0.009501866223177035</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008683418786719996</v>
+        <v>0.008683418786719995</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00981788655407345</v>
+        <v>0.009817886554073453</v>
       </c>
       <c r="H8" t="n">
         <v>0.009701156003797323</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009824521815678054</v>
+        <v>0.009824521815678045</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009929679042304218</v>
+        <v>0.009929679042304225</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008633509573259012</v>
+        <v>0.008633509573259016</v>
       </c>
       <c r="L8" t="n">
         <v>0.01091120345231561</v>
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0085237802652121</v>
+        <v>0.008523780265212102</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009039003162572286</v>
+        <v>0.009039003162572288</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008929784922111409</v>
+        <v>0.008929784922111411</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009600588763433273</v>
+        <v>0.009600588763433277</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0090390038618085</v>
+        <v>0.009039003861808502</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009032326370805236</v>
+        <v>0.009032326370805241</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008915595820529313</v>
+        <v>0.008915595820529316</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009038961632409834</v>
+        <v>0.009038961632409841</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009143887354622281</v>
+        <v>0.00914388735462229</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008754391170902761</v>
+        <v>0.008754391170902763</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008895157691365221</v>
+        <v>0.008895157691365228</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004028374631516374</v>
+        <v>0.004028374631516372</v>
       </c>
       <c r="C2" t="n">
         <v>0.003619892575535576</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004187287227919269</v>
+        <v>0.004187287227919267</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003720803901266856</v>
+        <v>0.003720803901266849</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003361239772458639</v>
+        <v>0.003361239772458636</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004107935938732133</v>
+        <v>0.004107935938732129</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004136499608300662</v>
+        <v>0.00413649960830066</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003988367628291727</v>
+        <v>0.003988367628291724</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003991530573406901</v>
+        <v>0.003991530573406895</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005022797318668746</v>
+        <v>0.005022797318668747</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004413415793489512</v>
+        <v>0.004413415793489508</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004182437938525395</v>
+        <v>0.004182437938525393</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003292511871213023</v>
+        <v>0.003292511871213025</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005310413297572274</v>
+        <v>0.005310413297572278</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003456661533454264</v>
+        <v>0.003456661533454268</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002863138126713388</v>
+        <v>0.002863138126713394</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004749098521386684</v>
+        <v>0.004749098521386688</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004962622562226691</v>
+        <v>0.004962622562226696</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00389827958920196</v>
+        <v>0.003898279589201955</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004299256384882637</v>
+        <v>0.004299256384882624</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005777955149866461</v>
+        <v>0.005777955149866447</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006930280511294353</v>
+        <v>0.006930280511294358</v>
       </c>
     </row>
     <row r="4">
@@ -7327,13 +7327,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007647500148637592</v>
+        <v>0.00764750014863759</v>
       </c>
       <c r="C4" t="n">
         <v>0.007124070808957959</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009442491028414353</v>
+        <v>0.00944249102841435</v>
       </c>
       <c r="E4" t="n">
         <v>0.007134662669695885</v>
@@ -7342,22 +7342,22 @@
         <v>0.007134662669695885</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008541970569044231</v>
+        <v>0.008541970569044238</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008881848762017908</v>
+        <v>0.008881848762017917</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007167164444399385</v>
+        <v>0.007167164444399383</v>
       </c>
       <c r="J4" t="n">
         <v>0.008008106303602823</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007551906470692087</v>
+        <v>0.007551906470692085</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01195943593818989</v>
+        <v>0.01195943593818988</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02230195469674195</v>
+        <v>0.02230195469674193</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01449338897432505</v>
+        <v>0.01449338897432497</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05279790758202128</v>
+        <v>0.05279790758202137</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01449339005730329</v>
+        <v>0.01449339005730324</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01449339005730329</v>
+        <v>0.01449339005730324</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03863787749877247</v>
+        <v>0.03863787749877252</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0464269116632876</v>
+        <v>0.04642691166328768</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01449302743733431</v>
+        <v>0.01449302743733428</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03050215120127245</v>
+        <v>0.03050215120127242</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02075683578736856</v>
+        <v>0.02075683578736857</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0385878015544612</v>
+        <v>0.0385878015544614</v>
       </c>
     </row>
     <row r="6">
@@ -7407,34 +7407,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007945743878252047</v>
+        <v>0.007945743878252046</v>
       </c>
       <c r="C6" t="n">
         <v>0.007424585303704493</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00978896613401292</v>
+        <v>0.009788966134012929</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007400382674968257</v>
+        <v>0.007400382674968259</v>
       </c>
       <c r="F6" t="n">
         <v>0.007461725476325233</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009707997642401961</v>
+        <v>0.009707997642401966</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01007675724529168</v>
+        <v>0.01007675724529169</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008333191517757101</v>
+        <v>0.008333191517757103</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009185225587173267</v>
+        <v>0.009185225587173265</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007831777387791139</v>
+        <v>0.007831777387791153</v>
       </c>
       <c r="L6" t="n">
         <v>0.01229838575011835</v>
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008335392413422531</v>
+        <v>0.008335392413422535</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00785541824617508</v>
+        <v>0.007855418246175078</v>
       </c>
       <c r="D7" t="n">
         <v>0.0101303594921313</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007854430480674947</v>
+        <v>0.007854430480674949</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007854430480674947</v>
+        <v>0.007854430480674949</v>
       </c>
       <c r="G7" t="n">
-        <v>0.009229862833829183</v>
+        <v>0.009229862833829185</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009569741026802858</v>
+        <v>0.009569741026802865</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007855056709184328</v>
+        <v>0.007855056709184327</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008695998568387762</v>
+        <v>0.008695998568387769</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008239798735477031</v>
+        <v>0.008239798735477035</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01264732820297482</v>
+        <v>0.01264732820297483</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009718536994734467</v>
+        <v>0.009718536994734472</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01066434582741483</v>
+        <v>0.01066434582741482</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01323572456904879</v>
+        <v>0.01323572456904878</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01027429644568014</v>
+        <v>0.01027429644568015</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009283203503734287</v>
+        <v>0.009283203503734289</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01203942676519175</v>
+        <v>0.01203942676519174</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01237930495816533</v>
+        <v>0.01237930495816534</v>
       </c>
       <c r="I8" t="n">
         <v>0.01066462064054689</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01150584283196983</v>
+        <v>0.01150584283196984</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009596446845042574</v>
+        <v>0.009596446845042581</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01694690642065955</v>
+        <v>0.01694690642065956</v>
       </c>
     </row>
     <row r="9">
@@ -7530,34 +7530,34 @@
         <v>0.01018381572738609</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01045337032396028</v>
+        <v>0.01045337032396029</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01272833589903811</v>
+        <v>0.01272833589903813</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01131831138459765</v>
+        <v>0.01131831138459766</v>
       </c>
       <c r="F9" t="n">
         <v>0.0104533707664878</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01182781491161438</v>
+        <v>0.0118278149116144</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01216769310458807</v>
+        <v>0.01216769310458808</v>
       </c>
       <c r="I9" t="n">
         <v>0.01045300878696954</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01129395064617297</v>
+        <v>0.01129395064617298</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01040347112597467</v>
+        <v>0.01040347112597468</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01524528028076004</v>
+        <v>0.01524528028076005</v>
       </c>
     </row>
   </sheetData>
@@ -7646,34 +7646,34 @@
         <v>0.003862447508079034</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003500574923843658</v>
+        <v>0.003500574923843659</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004038339574608663</v>
+        <v>0.004038339574608665</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003597633712174273</v>
+        <v>0.003597633712174274</v>
       </c>
       <c r="F2" t="n">
         <v>0.003247945410882733</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003937195239389929</v>
+        <v>0.003937195239389931</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00388181693770135</v>
+        <v>0.003881816937701349</v>
       </c>
       <c r="I2" t="n">
         <v>0.003871011055767752</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003815344270494815</v>
+        <v>0.003815344270494817</v>
       </c>
       <c r="K2" t="n">
         <v>0.004858119373706295</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006615537072929692</v>
+        <v>0.00661553707292969</v>
       </c>
     </row>
     <row r="3">
@@ -7683,34 +7683,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003647825818789808</v>
+        <v>0.003647825818789809</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00309896816770809</v>
+        <v>0.003098968167708091</v>
       </c>
       <c r="D3" t="n">
         <v>0.004894171061129252</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00325758228117252</v>
+        <v>0.003257582281172522</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00268036113693667</v>
+        <v>0.002680361136936671</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00417888915048921</v>
+        <v>0.004178889150489213</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003797023889766907</v>
+        <v>0.00379702388976691</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003708795035121632</v>
+        <v>0.003708795035121634</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00378960138968354</v>
+        <v>0.003789601389683544</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005367856196690966</v>
+        <v>0.005367856196690965</v>
       </c>
       <c r="L3" t="n">
         <v>0.023145782198597</v>
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006831389147698159</v>
+        <v>0.006831389147698162</v>
       </c>
       <c r="C4" t="n">
-        <v>0.006872171943562039</v>
+        <v>0.00687217194356204</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00881817095349847</v>
+        <v>0.008818170953498473</v>
       </c>
       <c r="E4" t="n">
+        <v>0.006880976408213454</v>
+      </c>
+      <c r="F4" t="n">
         <v>0.006880976408213453</v>
       </c>
-      <c r="F4" t="n">
-        <v>0.006880976408213452</v>
-      </c>
       <c r="G4" t="n">
-        <v>0.007671989093756076</v>
+        <v>0.007671989093756078</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007069509060084763</v>
+        <v>0.007069509060084765</v>
       </c>
       <c r="I4" t="n">
         <v>0.006903042755593194</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007282824668393939</v>
+        <v>0.007282824668393943</v>
       </c>
       <c r="K4" t="n">
-        <v>0.006990126562676492</v>
+        <v>0.006990126562676497</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03750739791822223</v>
+        <v>0.0375073979182222</v>
       </c>
     </row>
     <row r="5">
@@ -7763,13 +7763,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009321860706411278</v>
+        <v>0.009321860706411271</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01093047686430523</v>
+        <v>0.01093047686430524</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03979465590689234</v>
+        <v>0.03979465590689233</v>
       </c>
       <c r="E5" t="n">
         <v>0.01093047781757015</v>
@@ -7778,7 +7778,7 @@
         <v>0.01093047781757015</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02299967817072803</v>
+        <v>0.02299967817072798</v>
       </c>
       <c r="H5" t="n">
         <v>0.01376832576984355</v>
@@ -7787,13 +7787,13 @@
         <v>0.0109302555553495</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01744066348140745</v>
+        <v>0.01744066348140744</v>
       </c>
       <c r="K5" t="n">
         <v>0.0118136131411662</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5922869579646353</v>
+        <v>0.592286957964634</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007993004371862827</v>
+        <v>0.007993004371862828</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007130411061838955</v>
+        <v>0.00713041106183895</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009115224914576867</v>
+        <v>0.009115224914576866</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007108830124472366</v>
+        <v>0.007108830124472368</v>
       </c>
       <c r="F6" t="n">
         <v>0.00715238329476292</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008833604317920749</v>
+        <v>0.008833604317920747</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008240744544853604</v>
+        <v>0.008240744544853598</v>
       </c>
       <c r="I6" t="n">
         <v>0.008064657979757859</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007557619267181833</v>
+        <v>0.007557619267181834</v>
       </c>
       <c r="K6" t="n">
         <v>0.007229020217068807</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03796794040399046</v>
+        <v>0.03796794040399045</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007416594298344295</v>
+        <v>0.007416594298344296</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007488469215195057</v>
+        <v>0.007488469215195058</v>
       </c>
       <c r="D7" t="n">
         <v>0.00940335458257092</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007487395931555766</v>
+        <v>0.007487395931555769</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007487395931555766</v>
+        <v>0.007487395931555769</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008257194244402213</v>
+        <v>0.008257194244402206</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007654714210730898</v>
+        <v>0.0076547142107309</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007488247906239327</v>
+        <v>0.007488247906239329</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007868029819040074</v>
+        <v>0.007868029819040077</v>
       </c>
       <c r="K7" t="n">
         <v>0.00757533171332263</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03809260306886824</v>
+        <v>0.03809260306886823</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008667371866934989</v>
+        <v>0.008667371866935001</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009996238946086923</v>
+        <v>0.009996238946086946</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01217270171653754</v>
+        <v>0.01217270171653755</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009652333086486864</v>
+        <v>0.009652333086486879</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008778488353079383</v>
+        <v>0.008778488353079391</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01076571799293111</v>
+        <v>0.01076571799293112</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01016323795925972</v>
+        <v>0.01016323795925974</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009996771654768217</v>
+        <v>0.009996771654768232</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01037680075072221</v>
+        <v>0.01037680075072223</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008802746000894477</v>
+        <v>0.008802746000894484</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04191494787336852</v>
+        <v>0.04191494787336848</v>
       </c>
     </row>
     <row r="9">
@@ -7923,10 +7923,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008775674650372817</v>
+        <v>0.008775674650372819</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009424939849017077</v>
+        <v>0.009424939849017079</v>
       </c>
       <c r="D9" t="n">
         <v>0.01133984663972226</v>
@@ -7944,16 +7944,16 @@
         <v>0.009591184844552915</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009424718540061347</v>
+        <v>0.00942471854006135</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009804500452862094</v>
+        <v>0.009804500452862092</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009177260108965699</v>
+        <v>0.009177260108965694</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04002907370269033</v>
+        <v>0.04002907370269031</v>
       </c>
     </row>
   </sheetData>
